--- a/gtm/mec/MEC_Outreach_Ready.xlsx
+++ b/gtm/mec/MEC_Outreach_Ready.xlsx
@@ -1211,30 +1211,29 @@
       </c>
       <c r="AT3" s="4" t="inlineStr">
         <is>
-          <t>Watercolor Forest, and the mural nobody's made</t>
+          <t>Watercolor Forest, and the mural nobody made</t>
         </is>
       </c>
       <c r="AU3" s="5" t="inlineStr">
         <is>
           <t>Geoffrey,
-Eazywallz has the upload path solved — crop tool, live strip preview, pricing as you go. Most of this industry still can't do that.
-It assumes the customer arrives with an image though. Someone browsing Wall Mural of the Month because they like Watercolor Forest but want it warmer, or wider, or with different foliage has nowhere to go but the contact form.
-We built the AI studio MEC Artworks runs. They describe that variation in words, get an original design, and see it on a photo of their own wall.
+Eazywallz has the upload path solved. Crop tool, live strip preview, pricing as you go. Most of this industry still cannot do that.
+It assumes the customer arrives with an image though. Someone browsing Mural of the Month who likes Watercolor Forest but wants it warmer, or wider, or with different foliage has nowhere to go except the contact form, and most people do not fill in contact forms.
+We built the AI design studio MEC Artworks runs. They describe that change in words, get an original design, and see it on a photo of their own wall.
 Want me to send you a walkthrough?</t>
         </is>
       </c>
       <c r="AV3" s="4" t="inlineStr">
         <is>
-          <t>'like that, but warmer'</t>
+          <t>like that, but warmer</t>
         </is>
       </c>
       <c r="AW3" s="5" t="inlineStr">
         <is>
           <t>Geoffrey,
-The specific: someone types "watercolour forest, warmer, less contrast, twelve feet wide" and gets an original design back — then previews it in their room.
-For Eazywallz that's the browser who likes a collection piece but not quite. Right now they either compromise or leave, and your customizer never sees them.
-ai.mecartworks.com — email code, five previews, no subscription.
-Two minutes tells you whether it's worth more of your time.</t>
+The specific. Someone types "watercolour forest, warmer, less contrast, twelve feet wide" and gets an original design back, then previews it in their room.
+For Eazywallz that is the browser who likes a collection piece but not quite. Right now they either settle for something they like less or leave, and your customizer never even sees them.
+It is at ai.mecartworks.com. Five previews, free, email code only.</t>
         </is>
       </c>
       <c r="AX3" s="4" t="inlineStr">
@@ -1245,10 +1244,10 @@
       <c r="AY3" s="5" t="inlineStr">
         <is>
           <t>Geoffrey,
-Last note from me.
-You've already built the harder half of this — a working customizer with live pricing is not a small thing, and plenty of bigger companies haven't managed it.
-If the design-generation step is ever interesting, ai.mecartworks.com is the working example.
-Either way, good luck with the next Mural of the Month.</t>
+I will step back here.
+You have already built the harder half of this. A working customizer with live pricing is not a small thing, and plenty of much bigger companies have not managed it.
+If the design generation step is ever interesting, ai.mecartworks.com is the working example.
+Good luck with the next Mural of the Month.</t>
         </is>
       </c>
     </row>
@@ -1823,24 +1822,23 @@
       <c r="AU6" s="5" t="inlineStr">
         <is>
           <t>Tony,
-Wallsauce offers a free wall preview — the customer emails a product code and a photo, and someone sends back a visual.
-That's a person in the loop on every one, and a wait in the middle of a buying decision. You built it because it works, which is the interesting part.
-We built the AI studio MEC Artworks runs. It does the same thing instantly, and it also generates the design when the customer doesn't have one.
+Wallsauce offers a free wall preview. The customer emails a product code and a photo, and someone sends back a visual.
+You built that because it works, which is the interesting part. It also means a person in the loop on every one, and a wait sitting in the middle of a buying decision.
+We are the studio that built MEC Artworks' AI tool. It does the same thing instantly, and it also creates the design when the customer does not have one yet.
 Want me to show you where it would fit?</t>
         </is>
       </c>
       <c r="AV6" s="4" t="inlineStr">
         <is>
-          <t>the same service, minus the person</t>
+          <t>the same service, without the person</t>
         </is>
       </c>
       <c r="AW6" s="5" t="inlineStr">
         <is>
           <t>Tony,
-To be concrete about the difference: your preview service needs a product code, so the customer has already chosen. This one starts a step earlier — they describe what they want, get an original design, then see it on their wall.
-Same outcome as Try Before You Buy, without the email round trip or your team's time.
-ai.mecartworks.com — five free previews, email code only.
-Two minutes and you'd know.</t>
+The difference, plainly. Your preview service needs a product code, so the customer has already chosen. This starts one step earlier. They describe what they want, get an original design, then see it on their wall.
+Same outcome as Try Before You Buy, without the email round trip or your team's time. And it works at two in the morning, which is when a lot of people decide about their living room.
+ai.mecartworks.com gives you five previews for an email code.</t>
         </is>
       </c>
       <c r="AX6" s="4" t="inlineStr">
@@ -1851,10 +1849,10 @@
       <c r="AY6" s="5" t="inlineStr">
         <is>
           <t>Tony,
-I'll stop here.
-Running a manual preview service says you already believe seeing it converts people — so this is a question of automation, not of principle.
-ai.mecartworks.com if it's ever worth an afternoon.
-Either way, the RHG hotel lobby work is a good reference to have.</t>
+Final message on this.
+Running a manual preview service says you already believe that seeing it converts people. So this is a question about automating something, not about whether it works.
+ai.mecartworks.com if it is ever worth an afternoon.
+The RHG hotel lobby work is a good reference to have.</t>
         </is>
       </c>
     </row>
@@ -2076,38 +2074,37 @@
       <c r="AU7" s="5" t="inlineStr">
         <is>
           <t>Stacy,
-Your "GO CUSTOM!" flow is one of the better ones I've seen — upload, crop, resize, live pricing, done.
-It only helps the customer who already has the image. The ones who know they want "something botanical, muted, for a north-facing room" have nothing to drop in the box, so they leave.
-We built the AI studio MEC Artworks runs. That customer describes it in words, gets an original design back, then sees it on a photo of their own wall.
-Want me to send you a walkthrough?</t>
+Your GO CUSTOM flow is better than most. Upload, crop, resize, live pricing, done.
+It only works for someone who already has the image. A customer who knows they want something botanical and muted for a north facing room has nothing to put in the box, so they close the tab. That visitor had money and intent. You just had no way to serve them.
+We built the AI studio that MEC Artworks runs. That same customer types what they want, gets an original design back, then sees it on a photo of their own wall.
+Want me to send you a short walkthrough?</t>
         </is>
       </c>
       <c r="AV7" s="4" t="inlineStr">
         <is>
-          <t>when there's nothing in the box</t>
+          <t>when there is nothing to put in the box</t>
         </is>
       </c>
       <c r="AW7" s="5" t="inlineStr">
         <is>
           <t>Stacy,
-The specific bit: someone types "brushed sage, large-scale botanical, low contrast" and gets an original mural concept — not a stock search result. Then they upload the room and see it hung.
-For Limitless that's the top of the funnel your crop tool can't reach: the visitor with an idea and no file.
-It's live at ai.mecartworks.com — email code, five previews, no subscription.
-Two minutes tells you if it fits.</t>
+Here is the part that matters for you. Someone types "brushed sage, large botanical, low contrast" and gets an original design. Not a stock search result. Then they upload their room and see it hanging there.
+One thing you can check today without me: pull your search log for the last month and count the queries that returned nothing. That number is the size of this gap, and it costs you nothing to find out.
+The tool is at ai.mecartworks.com. ai.mecartworks.com, five previews free, email verification only.</t>
         </is>
       </c>
       <c r="AX7" s="4" t="inlineStr">
         <is>
-          <t>how do you convert the no-image visitor?</t>
+          <t>how do you convert the no image visitor?</t>
         </is>
       </c>
       <c r="AY7" s="5" t="inlineStr">
         <is>
           <t>Stacy,
-Last note from me.
-If you're already converting the no-image visitor some other way, I'd genuinely like to hear how — that's the hard half of custom.
-If not, ai.mecartworks.com is the working example.
-Either way, your custom flow is better than most of what's out there.</t>
+I will stop emailing after this one.
+If you already have a way to convert the visitor who arrives without an image, I would honestly like to hear it. That is the hard half of selling custom, and most people in your category have not solved it.
+If you do not, the example is at ai.mecartworks.com.
+Your custom flow is still one of the better ones I have looked at this month.</t>
         </is>
       </c>
     </row>
@@ -2312,15 +2309,15 @@
       </c>
       <c r="AT8" s="4" t="inlineStr">
         <is>
-          <t>the step before the 48-inch panels</t>
+          <t>the step before the 48 inch panels</t>
         </is>
       </c>
       <c r="AU8" s="5" t="inlineStr">
         <is>
           <t>Tim,
-MegaPrint prints removable custom wallpaper on 48-inch panels, two to three week turnaround, and the customer supplies the artwork.
-That last part is the filter. A business that knows it wants a branded wall but has no file and no designer never reaches your order form.
-We built the AI studio MEC Artworks runs. It closes that gap: describe the design in plain words, get an original concept, see it on a photo of the actual space.
+MegaPrint prints removable custom wallpaper on 48 inch panels, two to three weeks, and the customer supplies the artwork.
+That last part quietly filters your market. A business that wants a branded wall but has no file and no designer never reaches your order form. They are not price shopping. They are stuck one step earlier.
+We built MEC Artworks' AI studio. It closes that step. Describe the design in plain words, get an original concept back, then see it on a photo of the real space.
 Want me to run your own lobby through it and send you the result?</t>
         </is>
       </c>
@@ -2332,10 +2329,10 @@
       <c r="AW8" s="5" t="inlineStr">
         <is>
           <t>Tim,
-The specific: it isn't stock search. Someone types "industrial, muted teal, hop vines" and gets an original design, then drops it into a photo of their space.
-For MegaPrint that's the customer who currently never arrives — the one with an idea and no artwork.
-ai.mecartworks.com, five free previews, email code only.
-If the output isn't print-grade for your panels, you'll know fast.</t>
+To be clear about what it does, since "AI design" means very little on its own.
+It is not stock search. Someone types "industrial, muted teal, hop vines" and gets an original design, then drops it into a photo of their space.
+Worth knowing either way: the businesses that ask you for design help are usually your best margin jobs, because they are buying a result and not comparing print prices. Right now you have to turn them away or hand them to a designer.
+ai.mecartworks.com. Email code, five previews, nothing to cancel.</t>
         </is>
       </c>
       <c r="AX8" s="4" t="inlineStr">
@@ -2346,10 +2343,10 @@
       <c r="AY8" s="5" t="inlineStr">
         <is>
           <t>Tim,
-I'll leave it here.
-If most orders arrive with artwork already sorted, this solves a problem you don't have — and that's a good position to be in.
-If you ever want the other half of that market, ai.mecartworks.com is the example.
-Good luck either way.</t>
+Last one from me.
+If most of your orders already arrive with artwork sorted, this fixes something you do not have. That is a good place to be and I would rather you tell me than keep reading.
+If you ever want the other half of that market, the working example is at ai.mecartworks.com.
+Thanks for the time.</t>
         </is>
       </c>
     </row>
@@ -2556,30 +2553,30 @@
       </c>
       <c r="AT9" s="4" t="inlineStr">
         <is>
-          <t>the commission your artists can't preview</t>
+          <t>the commission your artists cannot preview</t>
         </is>
       </c>
       <c r="AU9" s="5" t="inlineStr">
         <is>
           <t>James,
-FinerWorks is built around artists who already have the file — drag it in, live preview, COA on the way out. That's a clean pipeline.
-The gap is the commission. When a buyer asks an artist for "something like this, but for my dining room," there's nothing to drag in, and that conversation runs over email for weeks.
-We built the AI studio MEC Artworks runs, for exactly that stage: describe it, get an original concept, place it on a photo of the buyer's room.
+FinerWorks is built for the artist who already has the file. Drag it in, live preview, COA on the way out. That is a clean pipeline and it shows.
+The gap is the commission. When a buyer asks an artist for "something like this, but for my dining room", there is no file to drag in. That conversation then runs over email for weeks, and plenty of it dies there.
+We built the AI studio that MEC Artworks runs for exactly that stage. Describe it, get an original concept, place it on a photo of the buyer's room.
 Worth showing you?</t>
         </is>
       </c>
       <c r="AV9" s="4" t="inlineStr">
         <is>
-          <t>a COA for a piece that doesn't exist yet</t>
+          <t>a COA for a piece that does not exist yet</t>
         </is>
       </c>
       <c r="AW9" s="5" t="inlineStr">
         <is>
           <t>James,
-Concretely: the buyer types what they're after, gets an original concept, then sees it on their own wall before the artist starts.
-For FinerWorks that could sit ahead of the upload — the artist closes the commission faster, and the file that eventually gets dragged in is one the buyer already approved.
-ai.mecartworks.com — five previews, email code, no subscription.
-Curious what you'd make of the output quality.</t>
+The practical version. The buyer types what they want, gets an original concept, then sees it on their own wall before the artist starts painting.
+The part I think is useful for FinerWorks: it sits ahead of your upload, not against it. The artist closes the commission faster, and the file that eventually gets dragged in is one the buyer has already approved. Fewer reprints, fewer refunds.
+ai.mecartworks.com. One time code, five previews, free.
+I would value your read on the output quality.</t>
         </is>
       </c>
       <c r="AX9" s="4" t="inlineStr">
@@ -2590,10 +2587,10 @@
       <c r="AY9" s="5" t="inlineStr">
         <is>
           <t>James,
-Last one from me.
-You've clearly thought about the artist's workflow more than most print platforms have — the COA tool alone says that.
-If the commission stage ever comes up as something to solve, ai.mecartworks.com is the working example.
-Either way, good luck with it.</t>
+I will leave it here.
+You have thought about the artist's workflow more than most print platforms bother to. The COA tool on its own says that.
+If the commission stage ever becomes something you want to solve, the example is at ai.mecartworks.com.
+Thanks for reading this far.</t>
         </is>
       </c>
     </row>
@@ -2810,16 +2807,16 @@
       </c>
       <c r="AT10" s="4" t="inlineStr">
         <is>
-          <t>your simulator, for designs that don't exist yet</t>
+          <t>your simulator, for designs that do not exist yet</t>
         </is>
       </c>
       <c r="AU10" s="5" t="inlineStr">
         <is>
           <t>Jennifer,
-Photowall's "Try Before You Buy" simulator already does the hard half — the customer sees the design on their own wall before buying.
-What it can't do is invent the design. If someone wants "muted botanical, wide format, north-facing room" and nothing in the catalogue matches, the simulator has nothing to show them.
-We built the AI studio MEC Artworks runs. It generates the design from that sentence, then places it in the room.
-Want to see how the two stages fit together?</t>
+Photowall's Try Before You Buy simulator already does the hard half. The customer sees the design on their own wall before they buy.
+What it cannot do is invent the design. If someone wants "muted botanical, wide format, north facing room" and nothing in the catalogue is close, the simulator has nothing to show them and they leave.
+My team built the AI studio MEC Artworks uses. It creates the design from that sentence, then places it in the room.
+Want to see how the two steps fit together?</t>
         </is>
       </c>
       <c r="AV10" s="4" t="inlineStr">
@@ -2830,24 +2827,23 @@
       <c r="AW10" s="5" t="inlineStr">
         <is>
           <t>Jennifer,
-The specific: someone describes the design in ordinary words, gets an original back, then previews it in their own room — same last step as yours, different first step.
-For Photowall that's the visitor who searches, finds nothing close, and leaves. Right now the simulator never gets a chance with them.
-ai.mecartworks.com — free, five previews, email code.
-Worth two minutes of a marketing afternoon.</t>
+The mechanic in one line. Someone describes the design in ordinary words, gets an original back, then previews it in their own room. Same last step as yours. Different first step.
+Something you can test without talking to me: check your on site search for queries with no results, or with results nobody clicked. Those are customers who wanted to buy and could not find it. In most catalogues that number is much larger than people expect.
+ai.mecartworks.com, email code, five previews, no card.</t>
         </is>
       </c>
       <c r="AX10" s="4" t="inlineStr">
         <is>
-          <t>does 'no close match' show in your search data?</t>
+          <t>does no close match show in your search data?</t>
         </is>
       </c>
       <c r="AY10" s="5" t="inlineStr">
         <is>
           <t>Jennifer,
-I'll stop here.
-If catalogue depth already covers most searches, this is a smaller problem than I think, and that's fair.
-If "no close match" ever shows up in your search data, ai.mecartworks.com is the example to look at.
-Thanks for reading.</t>
+Last note from me.
+If your catalogue depth already covers most searches, then this is a smaller problem than I think it is, and that is fair.
+If "no close match" does show up in your data, the example is at ai.mecartworks.com.
+Thanks for the time.</t>
         </is>
       </c>
     </row>
@@ -3258,10 +3254,10 @@
       <c r="AU12" s="5" t="inlineStr">
         <is>
           <t>Ivars,
-Fancy Walls already white-labels — private label, dropship, one to two day turnaround. You sell your capability onward, not just your product.
-Which makes the bottleneck clear: your partners' customers still have to decide what they want before any of that speed matters. Printing in two days doesn't help if choosing took three weeks.
-We built the AI studio MEC Artworks runs. It compresses the choosing — describe it, get an original design, see it on your own wall.
-Want me to show you where it would sit in a private-label flow?</t>
+Fancy Walls already sells its capability onward. Private label, dropship, one to two day turnaround. That is a harder business to build than a shop.
+Which makes the slow point easy to spot. Your partners' customers still have to decide what they want before any of that speed helps. Printing in two days does nothing if choosing took three weeks.
+We are the studio behind MEC Artworks' AI tool. It shortens the choosing. Describe it, get an original design, see it on your own wall.
+Want me to show you where it would sit inside a private label flow?</t>
         </is>
       </c>
       <c r="AV12" s="4" t="inlineStr">
@@ -3272,24 +3268,23 @@
       <c r="AW12" s="5" t="inlineStr">
         <is>
           <t>Ivars,
-More concretely: a shopper types what they want, gets an original design back, and sees it on a photo of their room — no drawing, no designer.
-For a dropship partner that's the difference between a browser and an order. Your two-day turnaround only starts once someone decides.
-ai.mecartworks.com — five free previews, email code.
-Happy to talk through the embed side if it looks relevant.</t>
+More concrete. A shopper types what they want, gets an original design back, and sees it on a photo of their room. No drawing, no designer, no brief.
+The angle I think is actually yours: you already white label. A design step your partners can put their own name on is another thing to sell them, not just a feature on your site. That is a revenue line, not a cost.
+ai.mecartworks.com, five free previews, email code.</t>
         </is>
       </c>
       <c r="AX12" s="4" t="inlineStr">
         <is>
-          <t>is choosing actually your bottleneck?</t>
+          <t>is choosing really the slow part?</t>
         </is>
       </c>
       <c r="AY12" s="5" t="inlineStr">
         <is>
           <t>Ivars,
-Last note.
-If your private-label partners already convert well without a design step, then this isn't your bottleneck and I'd rather know that.
-If it is, ai.mecartworks.com shows what it looks like.
-Either way — 3,400 designs and two-day print is a genuinely strong setup.</t>
+I will stop here.
+If your private label partners convert fine without a design step, then this is not your problem and I would rather know that than keep guessing.
+If it is, ai.mecartworks.com shows what it looks like in practice.
+3,400 designs with a two day print run is a strong setup whatever you decide.</t>
         </is>
       </c>
     </row>
@@ -3709,9 +3704,9 @@
       <c r="AU14" s="5" t="inlineStr">
         <is>
           <t>Verena,
-Glamora offers a Bespoke Design Service to professionals — an architect brings a project, your studio designs to it.
-That process starts with a conversation and a lot of imagination. The client approving the budget usually can't picture the result, which is where bespoke work gets trimmed or delayed.
-We built the AI studio MEC Artworks runs. It puts a concept on screen in that first conversation — described in words, then placed on a photo of the actual space.
+Glamora offers a Bespoke Design Service to professionals. An architect brings a project, your studio designs to it.
+That process starts with a conversation and a lot of imagining. The person who signs off the budget usually cannot picture the result, and that is where bespoke work gets cut back or pushed to next quarter.
+We built the AI design tool MEC Artworks runs. It puts a concept on screen inside that first conversation. Described in words, then placed on a photo of the real space.
 Would it be useful to see it against one of your collections?</t>
         </is>
       </c>
@@ -3723,10 +3718,9 @@
       <c r="AW14" s="5" t="inlineStr">
         <is>
           <t>Verena,
-The detail worth adding: no CAD and no drawing. Someone describes the piece — colour, mood, scale — and gets an original concept, then sees it in the room.
-For a bespoke service selling into hotels like SILENA and Bellerive, that turns the first meeting into a decision instead of a brief.
-ai.mecartworks.com — free, five previews, email verification only.
-Two minutes and you'll know if it holds up next to Glamora's work.</t>
+Worth adding, because "AI" says nothing useful on its own. There is no CAD and no drawing. Someone describes the piece by colour, mood and scale, gets an original concept, then sees it in the room.
+For a bespoke service selling into hotels like SILENA and Bellerive, the value is simple. The first meeting ends with a direction instead of a brief, so your studio spends its hours on work someone has already said yes to.
+ai.mecartworks.com. Five free previews after a one time code.</t>
         </is>
       </c>
       <c r="AX14" s="4" t="inlineStr">
@@ -3737,10 +3731,10 @@
       <c r="AY14" s="5" t="inlineStr">
         <is>
           <t>Verena,
-I'll leave this with you.
-If your studio already shows clients something visual in that first meeting, you've solved the part most bespoke suppliers haven't.
-If not, ai.mecartworks.com is the working example.
-Either way, the hospitality work on your diary page is a strong showcase.</t>
+This is the last one.
+If your studio already puts something visual in front of a client in that first meeting, you have solved the part most bespoke suppliers have not, and I would take that as the answer.
+If not, the working example is at ai.mecartworks.com.
+The hospitality work in your diary section is a strong showcase.</t>
         </is>
       </c>
     </row>
@@ -3950,10 +3944,10 @@
       <c r="AU15" s="5" t="inlineStr">
         <is>
           <t>Paolo,
-Inkiostro Bianco offers progetti su misura — and with a 3D lead in the room, you're already producing visuals to sell them.
-That's the expensive part. Every bespoke enquiry that needs a render costs studio time before anyone has committed to anything.
-We built the AI studio MEC Artworks runs. It produces the first-pass version in seconds: describe the piece, get an original concept, place it on a photo of the room.
-Not a replacement for your 3D work — a filter in front of it. Worth a look?</t>
+Inkiostro Bianco offers progetti su misura, and with a 3D lead in the room you are already making visuals to sell them.
+That is the expensive part. Every custom request that needs a render costs studio time before anyone has committed to anything, and some of those requests were never going to close.
+MEC Artworks runs an AI studio. We built it. It makes the first pass in seconds. Describe the piece, get an original concept, place it on a photo of the room.
+Not a replacement for your 3D work. A filter in front of it. Worth a look?</t>
         </is>
       </c>
       <c r="AV15" s="4" t="inlineStr">
@@ -3964,10 +3958,10 @@
       <c r="AW15" s="5" t="inlineStr">
         <is>
           <t>Paolo,
-The part I'd want your read on specifically: output quality.
+You would judge this faster than anyone I could send it to, so I will be direct about what I want.
 Someone types "warm ochre, botanical, large scale" and gets an original concept, then drops it into a photo of the space. No CAD.
-You'd know within a minute whether it's good enough to put in front of a client, or only good enough to narrow a direction internally. Both are useful — I'd like to know which.
-ai.mecartworks.com, five free previews.</t>
+Within a minute you would know whether it is good enough to put in front of a client, or only good enough to narrow a direction in house. Both answers are useful to me, and the second one is still worth money to you, because it saves the render.
+ai.mecartworks.com, free, five previews, email code.</t>
         </is>
       </c>
       <c r="AX15" s="4" t="inlineStr">
@@ -3978,10 +3972,10 @@
       <c r="AY15" s="5" t="inlineStr">
         <is>
           <t>Paolo,
-I'll stop here.
-If your 3D pipeline already turns bespoke enquiries around fast enough, this solves nothing for you and that's a good place to be.
-If it's ever a queue, ai.mecartworks.com is the example.
-Either way, the Hotel La Gemma work is a strong reference.</t>
+I will let this go.
+If your 3D pipeline already turns custom requests around fast enough, this solves nothing for you. That is a good position and I am glad to hear it.
+If it ever backs up, the example is at ai.mecartworks.com.
+The Hotel La Gemma work is a strong reference to have.</t>
         </is>
       </c>
     </row>
@@ -4195,9 +4189,9 @@
       <c r="AU16" s="5" t="inlineStr">
         <is>
           <t>Giulia,
-Real Wall and Live Room put Instabilelab ahead of most of this industry — most wallcovering brands still ship a static gallery.
-Both configurators start from your existing collections, though. The visitor who wants something that isn't in them has no path, and a laboratorio di sperimentazione is exactly the brand that customer came looking for.
-We built the AI studio MEC Artworks runs. It generates the design first, described in words, then places it in the room.
+Real Wall and Live Room put Instabilelab ahead of most of this industry. Plenty of wallcovering brands still ship a static gallery and call it a tool.
+Both start from your existing collections though. A visitor who wants something that is not in them has nowhere to go, and a laboratorio di sperimentazione is exactly the brand that customer came looking for.
+We built the AI mosaic studio MEC Artworks uses. It creates the design first, from words, then places it in the room.
 Would it be useful to see how it sits in front of Real Wall?</t>
         </is>
       </c>
@@ -4209,24 +4203,23 @@
       <c r="AW16" s="5" t="inlineStr">
         <is>
           <t>Giulia,
-To be concrete: someone types "ochre, oversized botanical, matte" and gets an original design, then sees it on their wall. Your configurators handle everything after that.
-For Instabilelab it's a first step, not a replacement — it feeds Real Wall the customers who currently leave.
-ai.mecartworks.com — five previews, email code, no subscription.
-Two minutes will tell you whether the output is up to your standard.</t>
+To be concrete. Someone types "ochre, oversized botanical, matte" and gets an original design, then sees it on their wall. Your configurators handle everything after that.
+The value for you is not a new tool. It is more traffic reaching the tools you already paid to build. Right now the customer without a collection in mind never gets as far as Real Wall.
+You will find it at ai.mecartworks.com. Five previews, no cost.</t>
         </is>
       </c>
       <c r="AX16" s="4" t="inlineStr">
         <is>
-          <t>you've built configurators — what did you learn?</t>
+          <t>you built configurators. what did you learn?</t>
         </is>
       </c>
       <c r="AY16" s="5" t="inlineStr">
         <is>
           <t>Giulia,
-I'll leave it here.
-You've already invested in configurators, so you know what they cost and what they return better than I do. If the gap I'm describing isn't real for you, that's genuinely useful to hear.
+Final email from me.
+You have already invested in configurators, so you know better than I do what they cost and what they return. If the gap I am describing is not real for you, that is genuinely worth hearing.
 ai.mecartworks.com if it ever is.
-Either way, the Hotel Feldhof project is a good showcase.</t>
+The Hotel Feldhof project is a good showcase.</t>
         </is>
       </c>
     </row>
@@ -4449,10 +4442,10 @@
       <c r="AU17" s="5" t="inlineStr">
         <is>
           <t>Michael,
-Your "Create a Mosaic" service is why I'm writing — a homeowner or builder describes what they want in the pool, and your team turns it into a design.
-Between that conversation and an approved drawing is where custom pool work slows down, and pool budgets move fast.
-Being upfront: we built the AI studio MEC Artworks runs, and they're in mosaics too. It takes a plain-words description and puts the design on a photo of the actual pool.
-Happy to walk you through it rather than send a link — worth 15 minutes?</t>
+Your Create a Mosaic service is why I am writing. A homeowner or a builder describes what they want in the pool, and your team turns it into a design.
+The gap between that conversation and an approved drawing is where custom pool work stalls. Pool budgets move fast, and a client who cannot picture the result often takes the plain tile instead.
+Straight with you: MEC Artworks runs an AI studio we built, and they work in mosaics too. It takes a plain description and puts the design on a photo of the actual pool.
+I would rather walk you through it than send you a competitor's link. Can I book fifteen minutes?</t>
         </is>
       </c>
       <c r="AV17" s="4" t="inlineStr">
@@ -4463,10 +4456,9 @@
       <c r="AW17" s="5" t="inlineStr">
         <is>
           <t>Michael,
-The specific mechanic: someone types "deep blue, geometric, Mediterranean" and gets an original mosaic concept back, then it's placed on a photo of the real pool.
-At a Ritz-Carlton level of spec, that's the difference between selling a drawing and selling a picture of the finished pool.
-I'd rather show you than have you register on a competitor's site — 15 minutes, screen share, no deck.
-Want me to send a couple of times?</t>
+How it works. Someone types "deep blue, geometric, Mediterranean" and gets an original mosaic concept, then it is placed on a photo of the real pool.
+The difference is what you are selling. A drawing asks the client to trust you. A picture of their own pool asks them to approve something they can already see. At a Ritz-Carlton level of spec that changes which option gets picked.
+Fifteen minutes on a screen share, no deck. Shall I send two or three times that suit you?</t>
         </is>
       </c>
       <c r="AX17" s="4" t="inlineStr">
@@ -4477,10 +4469,10 @@
       <c r="AY17" s="5" t="inlineStr">
         <is>
           <t>Michael,
-I'll stop here.
-If your team already gets clients to a yes quickly on custom pools, that's the whole game and you've got it.
-If concept-to-approval is ever the slow part, the offer to walk you through it stands.
-Either way, good luck with the season.</t>
+That is me done.
+If your team already gets clients to yes quickly on custom work, that is the whole game and you have it.
+If the stretch between concept and approval is ever the slow part, the offer to walk you through it stands.
+Good luck with the season.</t>
         </is>
       </c>
     </row>
@@ -4679,9 +4671,9 @@
       <c r="AU18" s="5" t="inlineStr">
         <is>
           <t>Chad,
-Mosaics Lab offers a free design consultation on custom work — a customer sends a photo or a painting, and your team turns it into a mosaic concept.
-That's real staff time on every enquiry, spent before anyone has committed to buying.
-Straight with you: we built the AI studio MEC Artworks runs, and they're in your industry. It does the first pass — a description or an uploaded image in, concept out, placed on a photo of the space.
+Mosaics Lab offers a free design consultation on custom work. A customer sends a photo or a painting, and your team turns it into a mosaic concept.
+That is real staff time on every request, spent before anyone has agreed to buy anything. It works, which is why you do it, but it does not scale past the hours your artists have.
+Straight with you: we built the AI studio that MEC Artworks runs, and they are in your industry. It does that first pass from a description or an uploaded image, and places it on a photo of the space.
 Rather than point you at a competitor's site, can I walk you through it?</t>
         </is>
       </c>
@@ -4693,9 +4685,9 @@
       <c r="AW18" s="5" t="inlineStr">
         <is>
           <t>Chad,
-The number I'd be curious about: how many free consultations turn into paid mosaics?
-If it's high, ignore me. If it's the usual, the consultation is doing sales work a first-pass visual could do in seconds — leaving your artists for the customers who are serious.
-Fifteen minutes on a screen share and you'd know whether it fits.
+The number I would want if I ran your business: what share of free consultations become paid mosaics?
+If it is high, ignore me. If it is the usual, then the consultation is doing sales work that a first draft could do in seconds, and your artists are spending their best hours on people who were never going to buy.
+That is the case for it in one line. Fifteen minutes on a screen share and you would know if it holds up.
 Want a couple of times?</t>
         </is>
       </c>
@@ -4707,10 +4699,10 @@
       <c r="AY18" s="5" t="inlineStr">
         <is>
           <t>Chad,
-Last one from me.
-Owner-run studios usually know exactly where their time leaks, so if the consultation isn't one of them, I'll take your word for it.
+No more from me after this.
+Owner run studios usually know exactly where their time leaks. If the consultation is not one of yours, I will take your word for it.
 The walkthrough offer stands if it ever is.
-Good luck with the year.</t>
+Thanks for the time.</t>
         </is>
       </c>
     </row>
@@ -4870,29 +4862,28 @@
       </c>
       <c r="AT19" s="4" t="inlineStr">
         <is>
-          <t>your artists, working step-by-step</t>
+          <t>your artists, working step by step</t>
         </is>
       </c>
       <c r="AU19" s="5" t="inlineStr">
         <is>
           <t>Sal,
-Blue Water's own copy says your ceramic artists work with the customer step-by-step to create the custom piece — logos, mascots, family crests.
-That's a person on every enquiry. The design software sits with your team, so the customer only sees a result after someone has already spent the hours.
-Being direct: we built the AI studio MEC Artworks runs — same industry as you. It puts a first version on screen from a description, on a photo of the actual pool.
-Happy to walk you through it. Worth 15 minutes?</t>
+Your own site says your ceramic artists work with the customer step by step to create the custom piece. Logos, mascots, family crests.
+That means a person on every request. The design software sits with your team, so the customer sees nothing until someone has already spent the hours. The ones who go quiet after that took those hours with them.
+Being direct: we built the AI studio that MEC Artworks runs, same industry as you. It puts a first version on screen from a description, on a photo of the actual pool.
+Happy to show you myself. Would fifteen minutes work?</t>
         </is>
       </c>
       <c r="AV19" s="4" t="inlineStr">
         <is>
-          <t>software for your artists vs software for your customer</t>
+          <t>software for your artists, software for your customer</t>
         </is>
       </c>
       <c r="AW19" s="5" t="inlineStr">
         <is>
           <t>Sal,
-The difference in one line: your software is a tool for your artists. This one is a tool for your customer.
-They type "navy, school mascot, six feet across", see a version on the pool photo, and arrive at your artists already knowing what they want.
-Same step-by-step outcome, minus the hours spent before the customer is serious.
+The difference in one line. Your software is a tool for your artists. This one is a tool for your customer.
+They type "navy, school mascot, six feet across", see a version on the pool photo, and arrive at your artists already knowing what they want. Same step by step service. The unpaid hours at the front of it go away.
 Screen share, 15 minutes, no deck. Want me to send times?</t>
         </is>
       </c>
@@ -4904,10 +4895,10 @@
       <c r="AY19" s="5" t="inlineStr">
         <is>
           <t>Sal,
-I'll close this off.
-Twenty years in the pool industry means you've seen a lot of tools promise this. Fair to be sceptical.
-The walkthrough offer stands if it's ever worth an afternoon.
-Good luck with the season.</t>
+I will close this off.
+Twenty years in the pool business means you have watched a lot of tools promise this exact thing. Being sceptical is the right call.
+The walkthrough offer stands if it is ever worth an afternoon.
+Best of luck with the rest of the year.</t>
         </is>
       </c>
     </row>
@@ -5123,10 +5114,10 @@
       <c r="AU20" s="5" t="inlineStr">
         <is>
           <t>Stephenie,
-New Ravenna's bespoke route starts with photographs, fabric swatches, sometimes a magazine clipping — and your team turning that into a mosaic concept before anything is cut.
-You have a manager for that step, which tells me it carries real weight and real hours.
-Being upfront: we built the AI studio MEC Artworks runs, and they're in mosaics too. It produces a first-pass concept from a description and places it on a photo of the room.
-I'd rather show you than send a competitor's link. Worth 15 minutes?</t>
+New Ravenna's bespoke route starts with photographs, fabric swatches, sometimes a magazine clipping, and your team turning that into a mosaic concept before anything is cut.
+You have a manager dedicated to that step. That tells me it carries real weight and real hours, and that it happens before the client has committed.
+Being upfront: we built the AI studio that MEC Artworks runs, and they are in mosaics too. It makes a first pass concept from a description and places it on a photo of the room.
+I would rather show you than send a competitor's link. Free for fifteen minutes this week?</t>
         </is>
       </c>
       <c r="AV20" s="4" t="inlineStr">
@@ -5137,10 +5128,9 @@
       <c r="AW20" s="5" t="inlineStr">
         <is>
           <t>Stephenie,
-The mechanic specifically: someone types "warm terracotta, geometric, Moorish influence" and gets an original concept back, then sees it on a photo of the actual wall.
-It doesn't replace a concept board. It gets the client to a direction before the board is worth making — which is where your team's hours go.
-Fifteen minutes on a screen share and you'd know.
-Want me to send a couple of times?</t>
+How it actually works. Someone types "warm terracotta, geometric, Moorish influence" and gets an original concept, then sees it on a photo of the real wall.
+It does not replace a concept board. It gets the client to a direction before the board is worth making, which is where your team's hours currently go. The boards you do make are then for clients who have already chosen.
+Fifteen minutes on a screen share and you would know. Want me to propose a time?</t>
         </is>
       </c>
       <c r="AX20" s="4" t="inlineStr">
@@ -5151,9 +5141,9 @@
       <c r="AY20" s="5" t="inlineStr">
         <is>
           <t>Stephenie,
-I'll leave this alone now.
-If your first pass is already fast enough at the volume you run, that's a good place to be and I'm glad I asked.
-If it's ever the bottleneck — usually when volume climbs, not when the work changes — the walkthrough offer stands.
+I will leave this alone now.
+If your first pass is already fast enough at the volume you run, that is a good place to be and I am glad I asked.
+If it ever becomes the slow part, and that usually happens when volume climbs rather than when the work changes, the offer to walk you through it stands.
 Thanks for reading this far.</t>
         </is>
       </c>
@@ -5359,10 +5349,10 @@
       <c r="AU21" s="5" t="inlineStr">
         <is>
           <t>Christina,
-Hakatai does custom designed glass tile installations — mosaic murals and uncut custom patterns, not just stock series.
-That work asks the client to picture a whole wall from a sample board and a photo of somebody else's project. Some of them shrink the scope rather than commit.
-Being straight: we built the AI studio MEC Artworks runs — same industry. It generates a concept from a description and places it on a photo of the actual space.
-Happy to walk you through it — worth 15 minutes?</t>
+Hakatai does custom designed glass tile installations. Mosaic murals and uncut custom patterns, not only stock series.
+That work asks a client to picture a whole wall from a sample board and a photo of someone else's project. Plenty of them shrink the job rather than commit to the version they cannot see.
+Being straight: we built the AI studio that MEC Artworks runs, same industry. It creates a concept from a description and places it on a photo of the actual space.
+Happy to walk you through it instead. Fifteen minutes on a call?</t>
         </is>
       </c>
       <c r="AV21" s="4" t="inlineStr">
@@ -5373,10 +5363,9 @@
       <c r="AW21" s="5" t="inlineStr">
         <is>
           <t>Christina,
-The commercial version of this: clients who can see the finished wall approve the bigger piece, and they approve it sooner.
-Someone types "sea glass blues, organic, twelve feet" and sees it on the real wall — before the layout work starts.
-I'd rather demo it than send you to a competitor's site. Fifteen minutes, screen share.
-Want a couple of times?</t>
+The money point, plainly. A client who can see the finished wall does not need to hedge. The ones who cannot see it protect themselves by ordering less.
+Someone types "sea glass blues, organic, twelve feet" and sees it on the real wall, before any layout work starts.
+I would rather demo it than send you to a competitor's site. Fifteen minutes, screen share. Want a couple of times?</t>
         </is>
       </c>
       <c r="AX21" s="4" t="inlineStr">
@@ -5388,9 +5377,9 @@
         <is>
           <t>Christina,
 Closing this out.
-As CEO you'll have a clearer view than I do on whether custom enquiries convert well enough already. If they do, ignore me entirely.
-The offer to walk through it stands.
-Good luck with the year.</t>
+As CEO you have a clearer view than I do on whether custom requests already convert well enough. If they do, ignore me completely.
+The offer to show you stands.
+Thanks for the time.</t>
         </is>
       </c>
     </row>
@@ -5569,9 +5558,9 @@
         <is>
           <t>Sean,
 Oceanside's Special Order Program and the Uniquely Oceanside collaboration both let a client customise before the tile ships.
-Both still ask them to commit to a combination they've only seen as separate samples. Your own site makes the point — liners, decos and trim combine for "unlimited possibilities", which is a lot to hold in your head.
-Being upfront: we built the AI studio MEC Artworks runs, same industry. It puts the combination on a photo of the real space.
-Worth 15 minutes to walk through?</t>
+Both still ask them to commit to a combination they have only seen as separate samples. Your own site makes the point: liners, decos and trim combine for unlimited possibilities. That is a lot to hold in your head while deciding how to spend money.
+Being upfront: we built the AI studio that MEC Artworks runs, same industry. It puts the combination on a photo of the real space.
+Can I walk you through it? Fifteen minutes.</t>
         </is>
       </c>
       <c r="AV22" s="4" t="inlineStr">
@@ -5582,10 +5571,9 @@
       <c r="AW22" s="5" t="inlineStr">
         <is>
           <t>Sean,
-Where it fits Oceanside specifically: unlimited combinations is a selling point right up until the client has to choose one.
-Someone describes what they're after, sees it rendered on the actual pool or wall, and the special order gets placed instead of postponed.
-I'd rather show you directly than send a competitor's link. Fifteen minutes on a screen share.
-Want me to send times?</t>
+Where it fits Oceanside. Unlimited combinations is a great selling line right up to the moment a client has to pick one, and then it becomes the reason they delay.
+Someone describes what they are after, sees it on the actual pool or wall, and the special order gets placed instead of postponed to next season.
+I would rather show you directly than send a competitor's link. A quick screen share is all it takes. Want me to send times?</t>
         </is>
       </c>
       <c r="AX22" s="4" t="inlineStr">
@@ -5596,10 +5584,10 @@
       <c r="AY22" s="5" t="inlineStr">
         <is>
           <t>Sean,
-Last one from me.
-Thirty-plus years and a recycled-glass process that predates everyone else doing it — you've built something durable, and you don't need a tool to prove it.
+Final note.
+Thirty plus years and a recycled glass process that predates everyone else doing it. You have built something durable and you do not need a tool to prove it.
 The walkthrough offer stands if the special order flow ever needs help.
-Good luck with it.</t>
+Thanks for reading.</t>
         </is>
       </c>
     </row>
@@ -5816,10 +5804,10 @@
       <c r="AU23" s="5" t="inlineStr">
         <is>
           <t>Colleen,
-"Tailored To" is a proper bespoke programme — custom cutting and finishing, not just a size option.
-The client approving it is looking at slabs and gallery photos and imagining the result. At Artistic Tile's price point, imagination is doing a lot of expensive work.
-Being upfront: we built the AI studio MEC Artworks runs — they're in tile and mosaic too. It renders a described design onto a photo of the actual room.
-I'd rather walk you through it than send a competitor's link. Worth 15 minutes?</t>
+Tailored To is a real bespoke programme. Custom cutting and finishing, not a size option with a nicer name.
+The client approving it is looking at slabs and gallery photos and imagining the rest. At Artistic Tile's price point, that imagining is doing very expensive work, and it usually argues for the safer choice.
+Being upfront: we built the AI studio that MEC Artworks runs, and they are in tile and mosaic too. It renders a described design onto a photo of the actual room.
+I would rather walk you through it than send a competitor's link. Open to a short call?</t>
         </is>
       </c>
       <c r="AV23" s="4" t="inlineStr">
@@ -5830,10 +5818,9 @@
       <c r="AW23" s="5" t="inlineStr">
         <is>
           <t>Colleen,
-From a marketing angle: this is content as much as it is a tool.
-A visitor describes what they want, sees it on their own wall, and hands you their intent — which is a better lead than a sample request.
-Fifteen minutes on a screen share and you'd know if it's worth a conversation internally.
-Want me to send a couple of times?</t>
+From a marketing seat there is a second angle here. This is content as much as it is a tool.
+A visitor describes what they want, sees it on their own wall, and hands you their intent while doing it. That is a far better lead than a sample request, because you learn the room, the style and the scale before anyone calls them.
+Fifteen minutes on a screen share and you would know whether it is worth raising internally. Want me to send a couple of times?</t>
         </is>
       </c>
       <c r="AX23" s="4" t="inlineStr">
@@ -5844,10 +5831,10 @@
       <c r="AY23" s="5" t="inlineStr">
         <is>
           <t>Colleen,
-I'll stop here.
-If Tailored To is already converting the way you want, this is noise and I'd rather not add to your inbox.
+Last one, then I am out of your inbox.
+If Tailored To already converts the way you want, this is noise and I would rather not add to your inbox.
 The offer to walk through it stands.
-Either way, good luck with the season's launches.</t>
+Best of luck with the season's launches.</t>
         </is>
       </c>
     </row>
@@ -6270,24 +6257,23 @@
       <c r="AU25" s="5" t="inlineStr">
         <is>
           <t>Andrea,
-Sicis runs a design service for architects — soluzioni su misura across mosaic, glass and interiors.
-An architect specifying that has to sell it onward to their own client, usually from a sample and a portfolio of someone else's project. Work like Paradis Latin or the Benetti yacht is hard to translate into a different room.
-We built the AI studio MEC Artworks runs — same industry. It renders a described design onto a photo of the actual space.
+Sicis runs a design service for architects, soluzioni su misura across mosaic, glass and interiors.
+An architect specifying that has to sell it onward to their own client, usually from a sample and a portfolio of a different project. Work like Paradis Latin or the Benetti yacht is beautiful and almost impossible to translate into someone else's room.
+We built the AI studio that MEC Artworks runs, same industry. It renders a described design onto a photo of the actual space.
 Worth walking you through?</t>
         </is>
       </c>
       <c r="AV25" s="4" t="inlineStr">
         <is>
-          <t>an image that works as a proposal and as content</t>
+          <t>one image that works as a proposal and as content</t>
         </is>
       </c>
       <c r="AW25" s="5" t="inlineStr">
         <is>
           <t>Andrea,
-For your side of the business specifically: this makes shareable content as easily as it makes proposals.
-Someone describes a space, sees a Sicis-style treatment placed in it, and that image is both a sales asset and a social one.
-Fifteen minutes on a screen share and you'd see whether the output is up to the brand.
-Want me to send a couple of times?</t>
+For your side of the business specifically. The output is shareable, not just usable.
+Someone describes a space, sees a Sicis style treatment placed in it, and that single image is a sales asset and a social asset at the same time. You currently need a finished project to get an image like that, which means waiting months to post about work you sold last year.
+Fifteen minutes on a screen share and you would see whether the quality is up to the brand.</t>
         </is>
       </c>
       <c r="AX25" s="4" t="inlineStr">
@@ -6298,10 +6284,10 @@
       <c r="AY25" s="5" t="inlineStr">
         <is>
           <t>Andrea,
-I'll leave it here.
-Sicis has a stronger visual archive than almost anyone in this category, so you may simply not need generated imagery.
-If it's ever useful, the walkthrough offer stands.
-Either way, the Flora Springs project is a great piece of work.</t>
+I will leave it there.
+Sicis has a stronger visual archive than nearly anyone in this category, so you may simply not need generated images. That is a reasonable answer.
+If it is ever useful, the walkthrough offer stands.
+The Flora Springs project is a great piece of work.</t>
         </is>
       </c>
     </row>
@@ -6515,9 +6501,9 @@
       <c r="AU26" s="5" t="inlineStr">
         <is>
           <t>Paolo,
-Bisazza already runs a space configurator and a free Design Studio consultation for custom mosaic work — further along than most of this industry.
-The consultation is the interesting part. It's staffed, it's free, and it exists because the app configures existing products rather than generating new ones.
-We built the AI studio MEC Artworks runs. It takes a plain-words brief and returns an original design, placed on a photo of the real space.
+Bisazza already runs a space configurator and a free Design Studio consultation for custom mosaic work. That is further along than most of this industry.
+The consultation is the interesting bit. It is staffed, it is free, and it exists because the app configures existing products rather than creating new ones. Every custom idea still lands on a person.
+We put together the AI studio MEC Artworks runs. It takes a plain description and returns an original design, placed on a photo of the real space.
 Worth a look as a front end to the Design Studio?</t>
         </is>
       </c>
@@ -6529,24 +6515,23 @@
       <c r="AW26" s="5" t="inlineStr">
         <is>
           <t>Paolo,
-Framing it for your side: the app handles configuration, the studio handles creation, and the gap between them is human hours.
-Someone types "Novembre-scale geometry, warm metallics" and gets an original concept placed in the room. The consultation then starts from something instead of nothing.
-I'd rather show you than send a link — 15 minutes on a screen share.
-Want a couple of times?</t>
+Framing it for your side. The app handles configuration. The studio handles creation. The gap between them is paid human time, and it scales linearly with demand.
+Someone types "Novembre scale geometry, warm metallics" and gets an original concept placed in the room. The consultation then starts from something instead of from nothing, which shortens it.
+I would rather show you than send a link. Fifteen minutes on a screen share. Want a couple of times?</t>
         </is>
       </c>
       <c r="AX26" s="4" t="inlineStr">
         <is>
-          <t>have you looked at generative tooling already?</t>
+          <t>have you looked at generated design already?</t>
         </is>
       </c>
       <c r="AY26" s="5" t="inlineStr">
         <is>
           <t>Paolo,
 Closing this off.
-At Bisazza's scale you'll have looked at generative tooling already, and possibly built some. If so, I'd genuinely like to know what you concluded.
-The walkthrough offer stands either way.
-Good luck with the season.</t>
+At Bisazza's scale you have almost certainly looked at this kind of tooling already, and possibly built some. If so, I would rather hear what you concluded than pitch you.
+The walkthrough offer stands.
+Thanks for the time.</t>
         </is>
       </c>
     </row>
@@ -6767,24 +6752,23 @@
       <c r="AU27" s="5" t="inlineStr">
         <is>
           <t>Samantha,
-Fireclay's Mosaic Visualizer is one of the few real ones in this industry — most tile brands still ship a photo gallery and call it a tool.
-It visualises patterns you've already designed, though. The customer who wants something that isn't in the system still ends up in a custom enquiry queue.
-We built the AI studio MEC Artworks runs: describe a design in plain words, get an original back, see it on a photo of the actual room.
+Fireclay's Mosaic Visualizer is one of the few real ones in this industry. Most tile brands still ship a photo gallery and call it a tool.
+It visualises patterns you have already designed though. The customer who wants something that is not in the system still ends up in a custom request queue, waiting on a person.
+The AI studio MEC Artworks runs is ours. Describe a design in plain words, get an original back, see it on a photo of the actual room.
 Would it be useful to see how it sits in front of the Visualizer?</t>
         </is>
       </c>
       <c r="AV27" s="4" t="inlineStr">
         <is>
-          <t>the Foundry launch and the 'like that, but…' requests</t>
+          <t>the Foundry launch and the like that but requests</t>
         </is>
       </c>
       <c r="AW27" s="5" t="inlineStr">
         <is>
           <t>Samantha,
-The Foundry Collection is a good example of the gap. A launch creates demand for a look, and the requests that follow are always "like that, but…".
-This handles the "but" — original concept from a description, placed in the customer's own space, before it reaches your custom team.
-ai.mecartworks.com, five free previews, email code.
-Two minutes will tell you whether the output clears Fireclay's bar.</t>
+The Foundry Collection is a good example of the gap. A launch creates demand for a look, and the requests that follow are always "like that, but".
+This handles the "but". Original concept from a description, placed in the customer's own space, before it reaches your custom team. The requests that do reach them are then real ones.
+It is at ai.mecartworks.com. Five previews, no cost, code by email. You would know inside two minutes whether the output clears Fireclay's bar.</t>
         </is>
       </c>
       <c r="AX27" s="4" t="inlineStr">
@@ -6795,10 +6779,10 @@
       <c r="AY27" s="5" t="inlineStr">
         <is>
           <t>Samantha,
-I'll stop here.
-You've already built visualisation tooling in-house, so you know the cost and the payoff better than I can argue it.
-If the generative step is ever on the roadmap, ai.mecartworks.com is a working reference.
-Either way, the Foundry launch looks great.</t>
+This is my last email on it.
+You have already built visualisation tooling in house, so you know the cost and the payoff better than I can argue it.
+If the design generation step ever lands on the roadmap, ai.mecartworks.com is a working reference.
+The Foundry launch looks great.</t>
         </is>
       </c>
     </row>
@@ -7582,24 +7566,23 @@
       <c r="AU31" s="5" t="inlineStr">
         <is>
           <t>Randi,
-"Create Your Blend" lets a customer pick colours for diamond tiles — and you have a director of design consultants, which suggests plenty of custom work starts as a conversation rather than a selector.
-Those first conversations are where the hours go: translating "something warm, sort of organic" into an actual layout.
-We built the AI studio MEC Artworks runs. It turns that sentence into an original concept and puts it on a photo of the customer's room.
+Create Your Blend lets a customer pick colours for diamond tiles, and you have a director of design consultants. That combination tells me plenty of custom work still starts as a conversation rather than a selector.
+Those first conversations are where the hours go. Turning "something warm, sort of organic" into an actual layout is skilled work, and most of it happens before anyone has paid.
+We built MEC Artworks the AI studio they run today. It turns that sentence into an original concept and puts it on a photo of the customer's room.
 Would it help your consultants to see it?</t>
         </is>
       </c>
       <c r="AV31" s="4" t="inlineStr">
         <is>
-          <t>refining instead of interpreting</t>
+          <t>refining instead of guessing</t>
         </is>
       </c>
       <c r="AW31" s="5" t="inlineStr">
         <is>
           <t>Randi,
-Specifically for a consulting team: it changes what the first call starts from.
-Instead of describing options, your consultant opens with a concept already placed in the customer's room, and spends the call refining rather than interpreting.
-ai.mecartworks.com — free, five previews, email code only.
-Two minutes and you'd know whether it's useful to the team or just to the marketing page.</t>
+For a consulting team, the value is in what the first call starts from.
+Right now your consultant describes options and the customer tries to picture them. With this, the call opens with a concept already placed in the customer's room, and the whole conversation becomes refining instead of guessing. Shorter calls, and more of them ending in a decision.
+ai.mecartworks.com. Free, five previews, code by email.</t>
         </is>
       </c>
       <c r="AX31" s="4" t="inlineStr">
@@ -7611,9 +7594,9 @@
         <is>
           <t>Randi,
 Last note.
-If your consultants already get customers to a clear direction quickly, then this solves something you don't have.
-If the first ten minutes are ever the slow part, ai.mecartworks.com is the example.
-Either way — the Whitney commission is a remarkable credit.</t>
+If your consultants already get customers to a clear direction quickly, this solves something you do not have.
+If those first ten minutes are ever the slow part, the example is at ai.mecartworks.com.
+The Whitney commission is a remarkable credit to have.</t>
         </is>
       </c>
     </row>
@@ -7830,10 +7813,10 @@
       <c r="AU32" s="5" t="inlineStr">
         <is>
           <t>Justin,
-Project Tile is a smart piece of work — customers planning a backsplash or fireplace with your patterns instead of guessing.
-It starts once they've chosen the pattern, though. The customer who knows the room but not the tile has nothing to plan with, and that's usually where an art director's time gets spent.
-We built the AI studio MEC Artworks runs. It generates an original design from a description and places it on a photo of the actual room.
-Worth seeing how it sits in front of Project Tile?</t>
+Project Tile is a smart piece of work. Customers planning a backsplash or a fireplace with your patterns instead of guessing at them.
+It starts once they have chosen the pattern though. The customer who knows their room but not the tile has nothing to plan with, and sorting that out is usually where an art director's time disappears.
+We are the team behind MEC Artworks' AI studio. It creates an original design from a description and places it on a photo of the actual room.
+Worth seeing how it might sit in front of Project Tile?</t>
         </is>
       </c>
       <c r="AV32" s="4" t="inlineStr">
@@ -7844,10 +7827,10 @@
       <c r="AW32" s="5" t="inlineStr">
         <is>
           <t>Justin,
-As an art director you'd judge this faster than anyone: does the generated output look like something you'd let out under your name?
-Someone types "arts and crafts, muted green, botanical" and gets an original concept, placed in the room. Two minutes will answer it.
-ai.mecartworks.com — five free previews, email code.
-Genuinely interested in your verdict either way.</t>
+As an art director you will spot the flaws faster than I could list them, so here is the honest ask.
+Someone types "arts and crafts, muted green, botanical" and gets an original concept, placed in the room. Two minutes will tell you whether the output is something you would let out under the Motawi name.
+Either answer is useful to me. A no from an art director is worth more than a maybe from anyone else.
+Find it at ai.mecartworks.com. One code by email unlocks five previews.</t>
         </is>
       </c>
       <c r="AX32" s="4" t="inlineStr">
@@ -7858,10 +7841,10 @@
       <c r="AY32" s="5" t="inlineStr">
         <is>
           <t>Justin,
-I'll leave this here.
-Motawi's patterns are distinctive enough that generated design may be exactly the wrong fit — that's a legitimate answer and I'd rather hear it than not.
-ai.mecartworks.com if you're curious.
-Either way, Project Tile is better than most of what this industry ships.</t>
+I will leave this here.
+Motawi's patterns are distinctive enough that generated design may be exactly the wrong fit. That is a fair answer and I would rather hear it than not.
+ai.mecartworks.com if you are curious.
+Project Tile is better than most of what this industry ships.</t>
         </is>
       </c>
     </row>
@@ -8075,9 +8058,9 @@
       <c r="AU33" s="5" t="inlineStr">
         <is>
           <t>Susanne,
-Your InLine Design Cards are a genuinely good idea — physical cards so someone can experiment and let serendipity do its work.
-They also require shipping, handling, and a customer patient enough to play. Plenty of people who'd have bought after experimenting never start.
-We built the AI studio MEC Artworks runs. Same experimentation, on screen: describe a direction, get an original concept, see it on a photo of the actual room.
+Your InLine Design Cards are a genuinely good idea. Physical cards so someone can experiment and let serendipity do its work.
+They also need shipping, handling, and a customer patient enough to play. Plenty of people who would have bought after experimenting never get as far as starting.
+We made the AI studio MEC Artworks runs on their site. Same experimenting, on screen. Describe a direction, get an original concept, see it on a photo of the real room.
 Worth showing you the parallel?</t>
         </is>
       </c>
@@ -8089,10 +8072,9 @@
       <c r="AW33" s="5" t="inlineStr">
         <is>
           <t>Susanne,
-The commercial version: customers who experiment buy more confidently and specify bigger. Your cards prove you already believe that — this just removes the postage and the wait.
-Describe it, see it on the wall, adjust, decide.
-ai.mecartworks.com — five previews, free, email code only.
-Two minutes will tell you whether it belongs next to the cards or nowhere near them.</t>
+What it is worth to you. Customers who experiment buy with more confidence and specify larger areas. Your cards prove you already believe that, or you would not have made them.
+This removes the postage and the wait. Describe it, see it on the wall, adjust, decide, all in one sitting while they are still interested.
+Find it at ai.mecartworks.com. An email code gets you five previews. Two minutes will tell you whether it belongs next to the cards or nowhere near them.</t>
         </is>
       </c>
       <c r="AX33" s="4" t="inlineStr">
@@ -8103,10 +8085,10 @@
       <c r="AY33" s="5" t="inlineStr">
         <is>
           <t>Susanne,
-I'll stop here.
-If the cards are converting the way you hoped, that's a better result than most digital tools produce and I'd leave well alone.
-ai.mecartworks.com if the digital version is ever interesting.
-Either way, the Cedar &amp; Moss collaboration is lovely work.</t>
+I will stop chasing this.
+If the cards are converting the way you hoped, that is a better result than most digital tools manage and I would leave well alone.
+ai.mecartworks.com if a digital version is ever interesting.
+The Cedar and Moss collaboration is lovely work.</t>
         </is>
       </c>
     </row>
@@ -8871,10 +8853,10 @@
       <c r="AU37" s="5" t="inlineStr">
         <is>
           <t>Connie,
-Seneca brought back the Handmold Mini Panels by popular demand — which tells me your specifiers respond to seeing the real thing in front of them.
-That's the whole difficulty with tile: panels and samples travel slowly, and the architect's client is usually the one who needs convincing.
-We built the AI studio MEC Artworks runs. It puts a described design onto a photo of the actual space, in seconds.
-I couldn't tell from your site how much custom work Seneca takes on — worth a short conversation?</t>
+Seneca brought the Handmold Mini Panels back by popular demand. That tells me your specifiers respond to seeing the real thing in front of them, which is worth knowing about your own market.
+It is also the difficulty with tile. Panels and samples travel slowly, and the architect's client is usually the person who needs convincing, sitting one step further away from the sample.
+MEC Artworks uses an AI studio we built for them. It puts a described design onto a photo of the actual space in seconds.
+I could not tell from your site how much custom work Seneca takes on. Open to a short call?</t>
         </is>
       </c>
       <c r="AV37" s="4" t="inlineStr">
@@ -8885,10 +8867,10 @@
       <c r="AW37" s="5" t="inlineStr">
         <is>
           <t>Connie,
-Being honest about why I'm asking: your site is clear on collections but not on how far you'll go on a custom request.
-If the answer is "quite far", this is relevant — it shortens the distance between an enquiry and an approved design.
-If the answer is "we're a manufacturer, not a design studio", tell me and I'll stop.
-Either way, ai.mecartworks.com shows what I mean in two minutes.</t>
+Being honest about why I am asking. Your site is clear on collections and quiet on how far you will go on a custom request.
+If the answer is "quite far", this is relevant, because it shortens the distance between a request and an approved design.
+If the answer is "we are a manufacturer, not a design studio", tell me and I will stop. That is useful to me and costs you one line.
+ai.mecartworks.com shows what I mean in two minutes.</t>
         </is>
       </c>
       <c r="AX37" s="4" t="inlineStr">
@@ -8899,9 +8881,9 @@
       <c r="AY37" s="5" t="inlineStr">
         <is>
           <t>Connie,
-Last note from me.
-A general manager's time is the wrong thing to spend on a cold email, so I'll leave it.
-If Seneca does take custom design work and it ever slows things down, ai.mecartworks.com is the example.
+One more and then I am done.
+A general manager's time is the wrong thing to spend on a cold email, so I will leave it.
+If Seneca does take on custom design work and it ever slows things down, the example is at ai.mecartworks.com.
 Good luck with the Mini Panels run.</t>
         </is>
       </c>
@@ -9088,9 +9070,9 @@
       <c r="AU38" s="5" t="inlineStr">
         <is>
           <t>Mark,
-Making the New Orleans letter and number tiles for the city since 2003 is a hard credential to argue with.
-The rest of the range is where I'm curious — Victorian patterns with traditional and specialty glazing, ordered by people who've only seen a photo of somebody else's floor.
-We built the AI studio MEC Artworks runs. Someone describes what they want and sees it laid into a photo of their own room.
+Making the city's letter and number tiles since 2003 is a hard credential to argue with.
+The rest of the range is what I am curious about. Victorian patterns with traditional and specialty glazing, ordered by people who have only seen a photo of somebody else's floor. Some of them buy less than they wanted because they are not sure.
+We built an AI studio for MEC Artworks. Someone describes what they want and sees it laid into a photo of their own room.
 Worth two minutes of an owner's time?</t>
         </is>
       </c>
@@ -9102,10 +9084,10 @@
       <c r="AW38" s="5" t="inlineStr">
         <is>
           <t>Mark,
-More useful detail: no drawing, no software to learn. A customer types "Victorian, deep green, geometric border" and sees it on their own floor.
-For a studio your size that's the difference between answering the same questions by email for a week and getting to a yes.
-ai.mecartworks.com — five free previews, email code.
-If it doesn't do your glazes justice, I'd want to know that too.</t>
+The useful detail. No drawing, no software to learn. A customer types "Victorian, deep green, geometric border" and sees it on their own floor.
+For a studio your size that is the difference between answering the same three questions by email all week and getting to a yes. Your time is the scarce thing here, not the tile.
+ai.mecartworks.com. Five free previews after a one time code.
+If it does not do your glazes justice, I would want to know that too.</t>
         </is>
       </c>
       <c r="AX38" s="4" t="inlineStr">
@@ -9116,10 +9098,10 @@
       <c r="AY38" s="5" t="inlineStr">
         <is>
           <t>Mark,
-I'll leave it here.
+Signing off on this one.
 Running a studio means the last thing you need is another tool to evaluate. Fair enough.
-ai.mecartworks.com if it's ever a slow week.
-Either way, twenty-plus years making the city's own tiles is a good thing to have built.</t>
+ai.mecartworks.com if it is ever a slow week.
+Twenty plus years making the city's own tiles is a good thing to have built.</t>
         </is>
       </c>
     </row>
@@ -9490,9 +9472,9 @@
       <c r="AU40" s="5" t="inlineStr">
         <is>
           <t>Josh,
-Clay Squared runs three distinct directions at once — the Cosmic Collection, Medieval Floral, and the 1920s–50s mid-century reproductions. That's a lot of range for one studio.
-It also means a customer has to work out which one belongs in their room, from photos of other people's rooms. Most of them ask you instead, and that's an artist's afternoon.
-We built the AI studio MEC Artworks runs. They describe the space, see a treatment placed in a photo of it, and arrive already decided.
+Clay Squared runs three quite different directions at once. The Cosmic Collection, Medieval Floral, and the 1920s to 50s mid century reproductions. That is a lot of range for one studio.
+It also means a customer has to work out which one belongs in their room, using photos of other people's rooms. Most of them ask you instead, and that is an artist's afternoon.
+We built that tool for MEC Artworks. They describe the space, see a treatment placed in a photo of it, and arrive already decided.
 Worth a couple of minutes of an owner's time?</t>
         </is>
       </c>
@@ -9504,10 +9486,10 @@
       <c r="AW40" s="5" t="inlineStr">
         <is>
           <t>Josh,
-The practical version: they type "mid-century, warm rust, geometric" and see it on their own wall before they email you.
-For a studio where the owner is also the artist, that afternoon is the whole point.
-ai.mecartworks.com — free, five previews, email code.
-If it doesn't do your glazes justice, that's worth knowing too.</t>
+The practical version. They type "mid century, warm rust, geometric" and see it on their own wall before they ever email you.
+For a studio where the owner is also the artist, that afternoon is the entire point. Every hour spent helping someone choose is an hour not spent making tile.
+ai.mecartworks.com. An email code, then five previews, free.
+If it does not do your glazes justice, that is worth knowing too.</t>
         </is>
       </c>
       <c r="AX40" s="4" t="inlineStr">
@@ -9518,10 +9500,10 @@
       <c r="AY40" s="5" t="inlineStr">
         <is>
           <t>Josh,
-Last one from me.
-If customers already find their way between the three collections without much help, then I've invented a problem you don't have.
+I will leave you to it.
+If customers already find their way between the three collections without much help from you, then I have invented a problem you do not have.
 ai.mecartworks.com if the choosing ever eats your studio time.
-Either way, the David Heide collaboration is a good credit to have.</t>
+The David Heide collaboration is a good credit to have.</t>
         </is>
       </c>
     </row>
@@ -10037,9 +10019,9 @@
       <c r="AU43" s="5" t="inlineStr">
         <is>
           <t>Neil,
-Nineteen design collections in the Molding &amp; Trim series is a lot of choice — and choice is exactly what stalls a tile decision.
-A customer looking at stunning patterns and rich glazes across nineteen options usually needs someone to narrow it for them. That someone is you.
-We built the AI studio MEC Artworks runs. They describe the room, see a combination placed on a photo of it, and arrive at you already decided.
+Nineteen design collections in the Molding and Trim series is a lot of choice, and choice is exactly what stalls a tile decision.
+Someone looking at rich glazes across nineteen options usually needs a person to narrow it down for them. That person is you, and it happens before they have bought anything.
+The AI studio on MEC Artworks' site is our build. They describe the room, see a combination placed on a photo of it, and arrive at you already decided.
 Worth a couple of minutes?</t>
         </is>
       </c>
@@ -10051,10 +10033,9 @@
       <c r="AW43" s="5" t="inlineStr">
         <is>
           <t>Neil,
-The practical version: the customer does the narrowing themselves, on screen, before they contact you.
-They type what they're after, see it on their own wall, and the conversation you get is about ordering rather than choosing.
-ai.mecartworks.com — free, five previews, email code only.
-Two minutes will tell you whether it handles your glazes properly.</t>
+The practical version. The customer narrows it themselves, on screen, before they contact you.
+They type what they are after, see it on their own wall, and the conversation you get is about ordering rather than choosing. Same sale, minus the unpaid consulting in the middle.
+ai.mecartworks.com, no cost, five previews, code by email. Two minutes will tell you whether it handles your glazes properly.</t>
         </is>
       </c>
       <c r="AX43" s="4" t="inlineStr">
@@ -10065,10 +10046,10 @@
       <c r="AY43" s="5" t="inlineStr">
         <is>
           <t>Neil,
-Last one from me.
-Owner-run means your time is the scarce thing, so I won't keep asking for it.
+Ending it here.
+Owner run means your time is the scarce thing, so I will not keep asking for it.
 ai.mecartworks.com if the choosing stage ever eats a week.
-Good luck with the season.</t>
+Thanks for the time.</t>
         </is>
       </c>
     </row>
@@ -10447,30 +10428,29 @@
       </c>
       <c r="AT45" s="4" t="inlineStr">
         <is>
-          <t>your simulators, and the pattern that isn't in them</t>
+          <t>your simulators, and the pattern that is not in them</t>
         </is>
       </c>
       <c r="AU45" s="5" t="inlineStr">
         <is>
           <t>Caitlin,
-Popham runs two live simulators — concrete and zellige — which puts you further ahead than almost anyone in tile. BACKGAMMON, BRASILIA, KELLY Relief: a customer can play with all of them.
-They can only play with patterns you've already drawn, though. The one who wants something adjacent has to describe it to a person and wait.
-We built the AI studio MEC Artworks runs. It generates the pattern from a description, then places it in a photo of the actual room.
-Worth seeing how it sits in front of the simulators?</t>
+Popham runs two live simulators, concrete and zellige, which puts you further ahead than almost anyone in tile. BACKGAMMON, BRASILIA, KELLY Relief. A customer can play with all of them.
+They can only play with patterns you have already drawn though. The one who wants something close but not quite has to describe it to a person and then wait.
+MEC Artworks runs a tool we built for exactly this. It creates the pattern from a description, then places it in a photo of the actual room.
+Worth seeing how it might sit in front of the simulators?</t>
         </is>
       </c>
       <c r="AV45" s="4" t="inlineStr">
         <is>
-          <t>generating the pattern, not just colouring it</t>
+          <t>creating the pattern, not just colouring it</t>
         </is>
       </c>
       <c r="AW45" s="5" t="inlineStr">
         <is>
           <t>Caitlin,
-The distinction: your simulators handle colour and layout on existing patterns. This generates the pattern itself, from a sentence, then puts it in the room.
-Feeding your simulators customers who arrive knowing what they want seems more useful than replacing anything.
-ai.mecartworks.com — five free previews, email code.
-You'd judge the output quality faster than I could explain it.</t>
+The distinction that matters. Your simulators handle colour and layout on patterns that exist. This creates the pattern itself from a sentence, then puts it in the room.
+Feeding your simulators customers who already know what they want seems more useful than replacing anything you have built. More people reaching a tool you paid for is the cheapest win available.
+The link is ai.mecartworks.com. Five previews, no subscription.</t>
         </is>
       </c>
       <c r="AX45" s="4" t="inlineStr">
@@ -10481,10 +10461,10 @@
       <c r="AY45" s="5" t="inlineStr">
         <is>
           <t>Caitlin,
-I'll leave it here.
-You've built two of these already, so you know the cost and the return better than any pitch of mine — and I'd genuinely rather hear what you learned than argue the case.
-ai.mecartworks.com if you're curious.
-Either way, the simulators are the best thing in this category.</t>
+Done chasing after this one.
+You have built two of these already, so you know the cost and the return better than any pitch of mine. I would rather hear what you learned than argue the case.
+ai.mecartworks.com if you are curious.
+The simulators are the best thing in this category.</t>
         </is>
       </c>
     </row>
@@ -10678,9 +10658,9 @@
         <is>
           <t>Carli,
 Kibak offers custom tile and custom murals, and the site invites people to book a meeting to talk the project through.
-That meeting is doing a lot of work — the customer arrives with a vague idea and you turn it into something concrete, one conversation at a time.
-We built the AI studio MEC Artworks runs. Someone describes the mural in plain words, gets an original concept, and sees it on a photo of the actual wall.
-Would that be useful before the meeting rather than during it?</t>
+That meeting is doing a lot of work. The customer arrives with a vague idea and you turn it into something concrete, one conversation at a time. Some of those meetings were never going to become orders.
+We built the AI tool MEC Artworks runs for their clients. Someone describes the mural in plain words, gets an original concept, and sees it on a photo of the actual wall.
+Would that be more useful before the meeting than during it?</t>
         </is>
       </c>
       <c r="AV46" s="4" t="inlineStr">
@@ -10691,10 +10671,9 @@
       <c r="AW46" s="5" t="inlineStr">
         <is>
           <t>Carli,
-Concretely: the customer books the meeting already holding a picture of what they want, placed in their own space.
-You spend the call refining instead of interpreting — and the ones who were never serious don't book at all.
-ai.mecartworks.com — five free previews, email code.
-Two minutes and you'd know whether it fits how Kibak works.</t>
+Concretely. The customer books the meeting already holding a picture of what they want, placed in their own space.
+Two things change. You spend the call refining instead of interpreting, and the people who were never serious do not book at all. For a studio where the owner takes the calls, that second one is the real saving.
+ai.mecartworks.com, five previews, email code, no subscription.</t>
         </is>
       </c>
       <c r="AX46" s="4" t="inlineStr">
@@ -10705,10 +10684,10 @@
       <c r="AY46" s="5" t="inlineStr">
         <is>
           <t>Carli,
-I'll leave this with you.
-If your booked meetings already convert well, this is a solution looking for a problem and I'd rather admit that.
-ai.mecartworks.com if the vague-idea stage is ever the slow one.
-Good luck with the year.</t>
+I will leave this with you.
+If your booked meetings already convert well, this is a solution looking for a problem and I would rather admit that than push.
+ai.mecartworks.com if the vague idea stage is ever the slow one.
+Thanks for reading.</t>
         </is>
       </c>
     </row>
@@ -10922,9 +10901,9 @@
       <c r="AU47" s="5" t="inlineStr">
         <is>
           <t>Emma,
-The Custom Rug Designer put you ahead of the category — a hundred designs, colour and size, all self-serve.
-Bespoke still goes to the studio though. When someone wants a design that isn't in the portal, a person picks it up, and that's before a sixteen to twenty-four week weave even starts.
-We built the AI studio MEC Artworks runs. It generates an original design from a plain-words brief and places it in a photo of the room.
+The Custom Rug Designer put you ahead of the category. A hundred designs, colour and size, all self serve.
+Bespoke still goes to the studio though. When someone wants a design that is not in the portal, a person picks it up, and that happens before a sixteen to twenty four week weave even begins.
+We designed and built MEC Artworks' AI studio. It creates an original design from a plain description and places it in a photo of the room.
 Worth seeing as a front end to the bespoke route?</t>
         </is>
       </c>
@@ -10936,10 +10915,9 @@
       <c r="AW47" s="5" t="inlineStr">
         <is>
           <t>Emma,
-To be specific about where it fits: your portal configures, your studio creates, and the gap between them is people.
-A client types "Wearstler-scale geometry, bone and rust" and sees it on their own floor. The studio conversation then starts from an image instead of a description.
-Happy to walk you through it — 20 minutes, screen share.
-Want a couple of times?</t>
+Where it fits, plainly. Your portal configures. Your studio creates. The gap between them is people, and it grows with demand rather than shrinking.
+A client types "Wearstler scale geometry, bone and rust" and sees it on their own floor. The studio conversation then starts from an image instead of a description, which cuts the rounds before a sample is even commissioned.
+Glad to show you how it works. Twenty minutes, screen share.</t>
         </is>
       </c>
       <c r="AX47" s="4" t="inlineStr">
@@ -10950,10 +10928,10 @@
       <c r="AY47" s="5" t="inlineStr">
         <is>
           <t>Emma,
-I'll leave it here.
-You've built a configurator already, so you know exactly what these tools cost and return — if the bespoke gap isn't worth closing, that's genuinely useful for me to hear.
+Wrapping this up.
+You have built a configurator already, so you know exactly what these tools cost and return. If the bespoke gap is not worth closing, that is genuinely useful for me to hear.
 The walkthrough offer stands.
-Either way, the DvF collaboration is great brand work.</t>
+The DvF collaboration is great brand work.</t>
         </is>
       </c>
     </row>
@@ -11173,10 +11151,10 @@
       <c r="AU48" s="5" t="inlineStr">
         <is>
           <t>Kayla,
-"Any size, any shape, any colour — we'll bring your vision to life" is a strong promise, and your pickers cover size, material and weave well.
-The vision part is the gap. A customer with a specific idea can't see it until someone in production makes it visible, which puts you in the middle of every custom enquiry.
-We built the AI studio MEC Artworks runs. Describe it in words, get an original design, see it in a photo of the room.
-Worth two minutes?</t>
+"Any size, any shape, any colour, we will bring your vision to life" is a strong promise, and your pickers cover size, material and weave well.
+The vision part is the gap. A customer with a specific idea cannot see it until someone in production makes it visible, which puts your team in the middle of every custom request.
+MEC Artworks came to us for an AI studio. We built it. Describe it in words, get an original design, see it in a photo of the room.
+Can I send it over?</t>
         </is>
       </c>
       <c r="AV48" s="4" t="inlineStr">
@@ -11187,10 +11165,9 @@
       <c r="AW48" s="5" t="inlineStr">
         <is>
           <t>Kayla,
-From a production side specifically: fewer rounds.
-If the customer approves a visual before anything is sampled, the brief that reaches production is settled rather than still moving.
-ai.mecartworks.com — free, five previews, email code only.
-Two minutes will tell you whether the output is precise enough to work from.</t>
+From a production seat the value is simple: fewer rounds.
+If the customer approves a visual before anything is sampled, the brief that reaches production is settled rather than still moving. Every change after sampling costs material and time, and most of those changes come from a customer who never really saw it in the first place.
+ai.mecartworks.com, free, five previews, email code only.</t>
         </is>
       </c>
       <c r="AX48" s="4" t="inlineStr">
@@ -11201,10 +11178,10 @@
       <c r="AY48" s="5" t="inlineStr">
         <is>
           <t>Kayla,
-Last note.
-If custom briefs already arrive clear, this fixes something that isn't broken and I'd rather leave you to it.
-ai.mecartworks.com if the back-and-forth ever gets long.
-Good luck with the season.</t>
+That is the last of it from me.
+If custom briefs already arrive clear, this fixes something that is not broken and I would rather leave you to it.
+ai.mecartworks.com if the back and forth ever gets long.
+Thanks for the time.</t>
         </is>
       </c>
     </row>
@@ -11409,30 +11386,29 @@
       </c>
       <c r="AT49" s="4" t="inlineStr">
         <is>
-          <t>300 colourways, and the design nobody's drawn</t>
+          <t>300 colourways, and the design nobody drew</t>
         </is>
       </c>
       <c r="AU49" s="5" t="inlineStr">
         <is>
           <t>Kruthika,
 Rug Artisan's customisation software with 300 preset colourways per design is further than most of this industry has got.
-Your own process describes what happens after: for a fully bespoke request, your designers create the design and send it for approval. That's a person, and a round trip.
-We built the AI studio MEC Artworks runs. It generates an original design from a plain-words brief and places it in the room.
+Your own process describes what happens next. For a fully bespoke request, your designers create the design and send it for approval. That is a person, and a round trip, on every one.
+We are behind the AI studio MEC Artworks runs. It creates an original design from a plain description and places it in the room.
 Worth seeing where it sits before your designers pick it up?</t>
         </is>
       </c>
       <c r="AV49" s="4" t="inlineStr">
         <is>
-          <t>variation vs designs that don't exist yet</t>
+          <t>variation, versus designs that do not exist yet</t>
         </is>
       </c>
       <c r="AW49" s="5" t="inlineStr">
         <is>
           <t>Kruthika,
-Put simply: your software handles variation on existing designs. This handles designs that don't exist yet.
-The client arrives at your design team having already seen and approved a direction, so the round trip becomes confirmation rather than discovery.
-Happy to walk you through it — 20 minutes.
-Want a couple of times?</t>
+Put simply. Your software handles variation on designs you already have. This handles designs that do not exist yet.
+The client reaches your design team having already seen and approved a direction, so the round trip becomes a confirmation rather than a discovery. Your designers draw once instead of twice.
+Happy to walk you through it. Twenty minutes.</t>
         </is>
       </c>
       <c r="AX49" s="4" t="inlineStr">
@@ -11443,10 +11419,10 @@
       <c r="AY49" s="5" t="inlineStr">
         <is>
           <t>Kruthika,
-I'll stop here.
-As design manager you'll know whether the bespoke round trip is actually a cost or just how the work goes. If it's the latter, fair enough.
+Last one, promise.
+As design manager you know whether that bespoke round trip is actually a cost or simply how the work goes. If it is the latter, fair enough.
 The walkthrough offer stands.
-Either way, the personalise tool is well built.</t>
+The personalise tool is well built.</t>
         </is>
       </c>
     </row>
@@ -11654,16 +11630,16 @@
       </c>
       <c r="AT50" s="4" t="inlineStr">
         <is>
-          <t>custom prices vs everyday prices</t>
+          <t>custom prices versus everyday prices</t>
         </is>
       </c>
       <c r="AU50" s="5" t="inlineStr">
         <is>
           <t>Hope,
-The Perfect Rug's whole positioning is custom at everyday prices rather than custom prices — and you back it with free design consultations.
-Free consultations are the expensive part of that promise. They're staff hours attached to every undecided customer, which is exactly what a value position can't afford to scale.
-We built the AI studio MEC Artworks runs. A customer describes the rug, sees it on a photo of their own floor, and decides before a consultation is needed.
-Worth two minutes?</t>
+The Perfect Rug's whole position is custom at everyday prices rather than custom prices, and you back it with free design consultations.
+Those consultations are the expensive part of the promise. They are staff hours attached to every undecided customer, and a value position is exactly the business model that cannot afford them to grow.
+We built the AI studio MEC Artworks now runs. A customer describes the rug, sees it on a photo of their own floor, and decides before a consultation is needed.
+Shall I send you the link?</t>
         </is>
       </c>
       <c r="AV50" s="4" t="inlineStr">
@@ -11674,10 +11650,9 @@
       <c r="AW50" s="5" t="inlineStr">
         <is>
           <t>Hope,
-For a content and partnerships role there's a second angle: the output is shareable.
-Someone describes a room, gets an image of their own space with the rug in it, and that's content your customers make for you.
-ai.mecartworks.com — free, five previews, email code.
-Two minutes and you'd know if it fits the brand.</t>
+For a content and partnerships role there is a second angle worth more than the first.
+Someone describes a room, gets an image of their own space with the rug in it, and that image is content they made themselves and will happily share. You get social proof from customers who have not even bought yet.
+ai.mecartworks.com. Five free previews, no signup wall.</t>
         </is>
       </c>
       <c r="AX50" s="4" t="inlineStr">
@@ -11688,10 +11663,10 @@
       <c r="AY50" s="5" t="inlineStr">
         <is>
           <t>Hope,
-I'll leave it here.
-If the consultations are converting well enough to justify themselves, that's the answer and it's a good one.
-ai.mecartworks.com if they ever stop scaling.
-Either way, good luck with the partnerships work.</t>
+I will park this now.
+If the consultations convert well enough to pay for themselves, that is the answer and it is a good one.
+ai.mecartworks.com if they ever stop scaling with the orders.
+Best of luck with the partnerships work.</t>
         </is>
       </c>
     </row>
@@ -11909,24 +11884,23 @@
       <c r="AU51" s="5" t="inlineStr">
         <is>
           <t>Cassie,
-Jubi runs both a real-time customizer with 1,200 shades and The Rug Plan, where your studio replies by hand with rugs chosen for someone's room.
-That you staff the second one despite having the first is the interesting bit — it says plenty of customers arrive without a starting point, and a colour picker can't give them one.
-We built the AI studio MEC Artworks runs. It generates the starting point from a sentence, then places it in the room.
+Jubi runs both a real time customizer with 1,200 shades and The Rug Plan, where your studio replies by hand with rugs chosen for someone's room.
+That you staff the second one despite having the first is the interesting part. It says plenty of customers arrive with no starting point, and a colour picker cannot give them one.
+That is what we built for MEC Artworks. It creates the starting point from a sentence, then places it in the room.
 Worth a look as a front end to The Rug Plan?</t>
         </is>
       </c>
       <c r="AV51" s="4" t="inlineStr">
         <is>
-          <t>what does The Rug Plan cost per enquiry?</t>
+          <t>what does The Rug Plan cost per request?</t>
         </is>
       </c>
       <c r="AW51" s="5" t="inlineStr">
         <is>
           <t>Cassie,
-As a founder you'll price this instantly: what does The Rug Plan cost you per enquiry, and what share convert?
-If someone arrives having already described their room and seen a design in it, your studio's reply becomes a shorter, better-qualified conversation.
-ai.mecartworks.com — free, five previews, email code.
-Two minutes will tell you whether it clears Jubi's bar.</t>
+As a founder you will price this in about ten seconds. What does The Rug Plan cost you per request, and what share convert?
+If someone arrives having already described their room and seen a design in it, your studio's reply becomes shorter and better qualified. Same service, less of it spent on browsers.
+The tool is ai.mecartworks.com. Email code, five previews, free.</t>
         </is>
       </c>
       <c r="AX51" s="4" t="inlineStr">
@@ -11937,10 +11911,10 @@
       <c r="AY51" s="5" t="inlineStr">
         <is>
           <t>Cassie,
-Last one from me.
-You've already built the tooling most of this industry hasn't, so you're the wrong person to sell a visualiser to — I'd rather ask what you learned building yours.
-ai.mecartworks.com if you're curious.
-Either way, The Rug Plan is lovely service design.</t>
+Final one from me.
+You have already built the tooling most of this industry has not, so you are the wrong person to sell a visualiser to. I would rather ask what you learned building yours.
+ai.mecartworks.com if you are curious.
+The Rug Plan is lovely service design.</t>
         </is>
       </c>
     </row>
@@ -12140,38 +12114,37 @@
       <c r="AU52" s="5" t="inlineStr">
         <is>
           <t>David,
-The piece calling stained glass a renaissance and naming Judson as the studio fuelling it is a good problem to have — more enquiries from people who've never commissioned glass before.
-Those clients approve a window they cannot picture, from drawings, and at Judson's scale that's a long, careful conversation every time.
-We built the AI studio MEC Artworks runs. It renders a described design into a photo of the actual opening.
-Worth a short conversation?</t>
+The press piece calling stained glass a renaissance and naming Judson as the studio fuelling it is a good problem to have. It brings people who have never ordered stained glass before.
+Those clients approve a window they cannot picture, from drawings. At Judson's scale that is a long, careful conversation every single time, and it happens before anyone signs.
+We built exactly that for MEC Artworks. It renders a described design into a photo of the actual opening.
+Would ten minutes be useful?</t>
         </is>
       </c>
       <c r="AV52" s="4" t="inlineStr">
         <is>
-          <t>triage as much as sales</t>
+          <t>sorting the serious from the curious</t>
         </is>
       </c>
       <c r="AW52" s="5" t="inlineStr">
         <is>
           <t>David,
-To be clear about what it is and isn't: it won't design a Judson window. It gets a client to a direction — palette, subject, density — before your designers invest hours.
-For a studio doing both new commissions and restoration, that's triage as much as sales.
-ai.mecartworks.com — five free previews, email code.
-Two minutes and you'd know.</t>
+To be clear about what it is and is not. It will not design a Judson window. It gets a client to a direction on palette, subject and density before your designers invest hours.
+For a studio doing both new commissions and restoration, the value is sorting. The serious ones reach your designers. The curious ones sort themselves out on screen.
+ai.mecartworks.com, free, five previews, email code.</t>
         </is>
       </c>
       <c r="AX52" s="4" t="inlineStr">
         <is>
-          <t>Unity Temple doesn't need my help</t>
+          <t>Unity Temple does not need my help</t>
         </is>
       </c>
       <c r="AY52" s="5" t="inlineStr">
         <is>
           <t>David,
-I'll leave this with you.
-A studio that's worked on Unity Temple doesn't need a generative tool to sell its work, and I'm aware of that.
-ai.mecartworks.com if enquiry volume ever outpaces the design team.
-Either way, good luck with the renaissance.</t>
+I will stop bothering you.
+A studio that has worked on Unity Temple does not need a new tool to sell its work, and I am aware of that.
+ai.mecartworks.com if the volume ever outpaces your design team.
+Best of luck with the renaissance.</t>
         </is>
       </c>
     </row>
@@ -12386,9 +12359,9 @@
         <is>
           <t>Kathy,
 Windows in more than 15,000 buildings is a number very few studios can put on a page.
-Most of those commissions get approved by a committee — a church board, a hospital board — and committees approve what they can see. Drawings ask each member to imagine the same thing, which is where these decisions stall for months.
-We built the AI studio MEC Artworks runs. It puts a described design into a photo of the actual window opening.
-Worth 15 minutes?</t>
+Most of those commissions get approved by a committee. A church board, a hospital board. Committees approve what they can see, and drawings ask every member to imagine the same thing separately. That is why these decisions slip from one meeting to the next.
+We built one of these for MEC Artworks. It puts a described design into a photo of the actual window opening.
+Would fifteen minutes be useful?</t>
         </is>
       </c>
       <c r="AV53" s="4" t="inlineStr">
@@ -12399,10 +12372,9 @@
       <c r="AW53" s="5" t="inlineStr">
         <is>
           <t>Kathy,
-The committee point is the one I'd stand behind commercially: when everyone in the room sees the same image, the decision happens in that meeting instead of the next one.
-Describe the design, place it in the real opening, discuss the actual thing.
-ai.mecartworks.com — free, five previews, email code only.
-Two minutes will tell you whether it's usable at your standard.</t>
+The committee point is the one I would stand behind. When everyone in the room looks at the same image, the decision happens in that meeting rather than the one after it.
+Describe the design, place it in the real opening, discuss the actual thing instead of five different mental versions of it.
+ai.mecartworks.com, free, five previews, email code only. Two minutes will tell you whether it is usable at your standard.</t>
         </is>
       </c>
       <c r="AX53" s="4" t="inlineStr">
@@ -12413,9 +12385,9 @@
       <c r="AY53" s="5" t="inlineStr">
         <is>
           <t>Kathy,
-Last note from me.
-As creative director you'd be the one deciding whether generated imagery belongs anywhere near Willet's work — and no is a perfectly reasonable answer for a studio with your history.
-ai.mecartworks.com if it's ever worth a look.
+Leaving this alone now.
+As creative director you would be the one deciding whether generated images belong anywhere near Willet's work, and no is a perfectly reasonable answer for a studio with your history.
+ai.mecartworks.com if it is ever worth a look.
 Good luck with the current commissions.</t>
         </is>
       </c>
@@ -12611,10 +12583,10 @@
       <c r="AU54" s="5" t="inlineStr">
         <is>
           <t>Gary,
-A hundred and one years and four generations — Franklin has outlasted most of the industry it started in.
-The custom side is what I'm writing about: working directly with homeowners, architects and designers on one-of-a-kind projects. Those clients approve from sketches, and sketches take your people's time before anyone has committed.
-We built the AI studio MEC Artworks runs. It renders a described design into a photo of the actual window.
-Worth a short conversation?</t>
+A hundred and one years and four generations. Franklin has outlasted most of the industry it started in.
+The custom side is what I am writing about. Working directly with homeowners, architects and designers on one of a kind projects. Those clients approve from sketches, and sketches take your people's time before anyone has committed to anything.
+MEC Artworks asked us to build one. We did. It renders a described design into a photo of the actual window.
+Worth a quick call to find out?</t>
         </is>
       </c>
       <c r="AV54" s="4" t="inlineStr">
@@ -12625,10 +12597,9 @@
       <c r="AW54" s="5" t="inlineStr">
         <is>
           <t>Gary,
-Being realistic about your business: most of Franklin's revenue is supply, and custom sits alongside it.
-Which is precisely why a faster first pass might matter — it makes custom work cheaper to quote without pulling more people onto it.
-ai.mecartworks.com — five free previews, email code.
-Two minutes is all it takes to judge.</t>
+Being realistic about your business. Most of Franklin's revenue is supply, and custom sits alongside it.
+That is exactly why a faster first pass might matter. It makes custom work cheaper to quote without putting more people on it, so the side of the business with the better margin stops being limited by your staff hours.
+ai.mecartworks.com, five free previews, email code only.</t>
         </is>
       </c>
       <c r="AX54" s="4" t="inlineStr">
@@ -12639,10 +12610,10 @@
       <c r="AY54" s="5" t="inlineStr">
         <is>
           <t>Gary,
-I'll stop here.
-A business that's lasted since 1924 doesn't need advice from a cold email, and I won't pretend otherwise.
+Last email on this.
+A business that has lasted since 1924 does not need advice from a cold email, and I am not going to pretend otherwise.
 ai.mecartworks.com if the custom side ever needs a faster front end.
-Good luck with the next generation of it.</t>
+Best of luck with the next generation of it.</t>
         </is>
       </c>
     </row>
@@ -13214,9 +13185,9 @@
       <c r="AU57" s="5" t="inlineStr">
         <is>
           <t>Anna,
-Heath built a set builder for dinnerware — start building, save 10%, see it come together.
-Tile doesn't have one. It has over a hundred glazes and an inquiry form, which means the customer choosing between them is doing it in their head while the dinnerware customer gets a tool.
-We built the AI studio MEC Artworks runs. Someone describes a room, sees a tile treatment placed in a photo of it, and chooses with their eyes.
+Heath built a set builder for dinnerware. Start building, save 10%, watch it come together.
+Tile does not have one. It has over a hundred glazes and a contact form, which means the customer choosing between them is doing it in their head, while the dinnerware customer gets a tool that does it for them.
+We built the AI studio running on MEC Artworks' site. Someone describes a room, sees a tile treatment placed in a photo of it, and chooses with their eyes.
 Worth seeing the parallel?</t>
         </is>
       </c>
@@ -13228,10 +13199,9 @@
       <c r="AW57" s="5" t="inlineStr">
         <is>
           <t>Anna,
-Seeds of Summer is the case in point — moodier pinks and reds, launched in April, and the hard part is getting someone to imagine a whole wall of it.
-Described in words, rendered into their own room, decided in a minute.
-ai.mecartworks.com — free, five previews, email code only.
-Two minutes will tell you whether the glazes survive the translation.</t>
+Seeds of Summer is the case in point. Moodier pinks and reds, launched in April, and the hard part is getting someone to picture a whole wall of it from a swatch.
+Described in words, rendered into their own room, decided in a minute. A seasonal collection has a short window, and anything that shortens the decision inside that window is worth more than it looks.
+ai.mecartworks.com, free, five previews, email code only.</t>
         </is>
       </c>
       <c r="AX57" s="4" t="inlineStr">
@@ -13242,10 +13212,10 @@
       <c r="AY57" s="5" t="inlineStr">
         <is>
           <t>Anna,
-I'll leave this here.
-Heath's design standards are the reason to say no to a tool like this, and I'd take that answer seriously.
+I will drop it here.
+Heath's design standards are the best reason to say no to a tool like this, and I would take that answer seriously.
 ai.mecartworks.com if the tile side ever wants what the dinnerware side has.
-Either way, Seeds of Summer is a beautiful collection.</t>
+Seeds of Summer is a beautiful collection.</t>
         </is>
       </c>
     </row>
@@ -13632,9 +13602,9 @@
       <c r="AU59" s="5" t="inlineStr">
         <is>
           <t>Jamie,
-Zia's line — designed in Los Angeles, crafted by artisans around the globe — is a curated position rather than a made-to-order one, and the filters on the site reflect that.
-Which makes the customer's job harder in one specific way: zellige varies, and a swatch photo doesn't tell you what a whole wall of it looks like.
-We built the AI studio MEC Artworks runs. Someone describes their room and sees a treatment placed in a photo of it.
+Zia's line, designed in Los Angeles and crafted by artisans around the globe, is a curated position rather than a made to order one. The filters on the site reflect that and they work well.
+It makes the customer's job harder in one specific way though. Zellige varies, and a swatch photo does not tell you what a whole wall of it looks like. That uncertainty is where orders shrink.
+The AI studio MEC Artworks uses came from us. Someone describes their room and sees a treatment placed in a photo of it.
 Worth two minutes of a marketing director's time?</t>
         </is>
       </c>
@@ -13646,10 +13616,9 @@
       <c r="AW59" s="5" t="inlineStr">
         <is>
           <t>Jamie,
-To be clear, I'm not suggesting Zia move into custom — the curated position is the brand.
-This sits before the filters: someone who knows the room but not the collection sees a direction, then lands on the product that matches. Discovery, not a design service.
-ai.mecartworks.com — free, five previews.
-Two minutes and you'd know if it's on-brand.</t>
+To be clear, I am not suggesting Zia moves into custom. The curated position is the brand and it is working.
+This sits before the filters. Someone who knows their room but not the collection sees a direction first, then lands on the product that matches. It is a discovery tool, not a design service, and it feeds the catalogue you already have.
+ai.mecartworks.com, five previews, email code, no subscription.</t>
         </is>
       </c>
       <c r="AX59" s="4" t="inlineStr">
@@ -13660,10 +13629,10 @@
       <c r="AY59" s="5" t="inlineStr">
         <is>
           <t>Jamie,
-Last note.
-If site search and the collection filters already do this job, then I've misread it and I'd rather know.
-ai.mecartworks.com if discovery is ever the drop-off point.
-Either way, good luck with the season.</t>
+One last note.
+If site search and the collection filters already do this job, then I have misread it and I would rather know.
+ai.mecartworks.com if discovery is ever where people drop off.
+Best of luck with the season.</t>
         </is>
       </c>
     </row>
@@ -13889,24 +13858,23 @@
       <c r="AU60" s="5" t="inlineStr">
         <is>
           <t>Lindsay,
-The Gilded print technology in the Reflections Collection — fine gold accents, reflective detail — is the kind of thing that has to be seen rather than described.
-Which is the whole difficulty. Your process is deliberately collaborative, concept through production, and each round of that collaboration is your team's time before a job is confirmed.
-We built the AI studio MEC Artworks runs. A designer describes the piece and sees it in a photo of the actual space.
+The Gilded print technology in the Reflections Collection, with fine gold accents and reflective detail, is the kind of thing that has to be seen rather than described. A photo does not carry it.
+That is the whole difficulty. Your process is deliberately collaborative, concept through production, and every round of that collaboration is your team's time spent before a job is confirmed.
+We built MEC Artworks an AI studio for this. A designer describes the piece and sees it in a photo of the actual space.
 Worth 15 minutes?</t>
         </is>
       </c>
       <c r="AV60" s="4" t="inlineStr">
         <is>
-          <t>for a 15-person studio, rounds are margin</t>
+          <t>for a 15 person studio, rounds are margin</t>
         </is>
       </c>
       <c r="AW60" s="5" t="inlineStr">
         <is>
           <t>Lindsay,
-The commercial angle for a fifteen-person studio: rounds are your margin.
-If the designer and their client agree a direction from a rendered image before your team starts, you spend production time on confirmed work instead of exploration.
-ai.mecartworks.com — five free previews, email code only.
-Two minutes will tell you whether it does the Gilded finish justice. I suspect that's the real test.</t>
+What it is worth to a fifteen person studio. Rounds are your margin.
+If the designer and their client agree a direction from a rendered image before your team starts, you spend production time on confirmed work instead of exploring. That is the difference between a studio that grows and one that stays busy.
+It lives at ai.mecartworks.com. Five free previews, no password. Two minutes will tell you whether it does the Gilded finish justice, and I suspect that is the real test.</t>
         </is>
       </c>
       <c r="AX60" s="4" t="inlineStr">
@@ -13917,10 +13885,10 @@
       <c r="AY60" s="5" t="inlineStr">
         <is>
           <t>Lindsay,
-I'll leave it here.
-Founder-run and fifteen people means every tool has to earn its place, so no is a completely reasonable answer.
+Closing the loop and stopping.
+Founder run and fifteen people means every tool has to earn its place, so no is a completely reasonable answer.
 ai.mecartworks.com if the concept rounds ever get long.
-Either way, building a print operation alongside a design studio is a genuinely smart structure.</t>
+Building a print operation alongside a design studio is a genuinely smart structure.</t>
         </is>
       </c>
     </row>
@@ -14339,17 +14307,16 @@
       </c>
       <c r="AT62" s="4" t="inlineStr">
         <is>
-          <t>approving a wall they've never seen</t>
+          <t>approving a wall they have never seen</t>
         </is>
       </c>
       <c r="AU62" s="5" t="inlineStr">
         <is>
           <t>Heather,
-Area sells to the trade only, and your FAQ says if someone brings a piece or a photograph, you'll build the wallcovering around it.
-So the person who signs off — the designer's client — is approving from a sample and their imagination. That's where custom work shrinks: a smaller wall, a safer colourway, a "let's revisit next quarter."
-Show them the finished piece on their own wall and they stop hedging. Bigger yes, sooner.
-We built the AI studio MEC Artworks runs.
-Want me to run one of your collections through it and send you the result?</t>
+Area sells to the trade only, and your FAQ says if someone brings a piece or a photograph, you will build the wallcovering around it.
+So the person who signs off, the designer's client, is approving from a sample and their imagination. That is where custom work shrinks. A smaller wall, a safer colourway, a let us revisit next quarter.
+Show them the finished piece on their own wall and they stop hedging. Bigger yes, and sooner.
+We built the AI studio MEC Artworks put on their site. Want me to run one of your collections through it and send you the result?</t>
         </is>
       </c>
       <c r="AV62" s="4" t="inlineStr">
@@ -14360,10 +14327,9 @@
       <c r="AW62" s="5" t="inlineStr">
         <is>
           <t>Heather,
-One thing I'd guess at: how often does a custom project come back smaller than it started?
-Not lost — just trimmed. A feature wall becomes an accent panel. That trim is almost always uncertainty, not budget.
-The tool is at ai.mecartworks.com. Email code, five free previews, no subscription. Upload a room, describe the piece, see it in place.
-Ninety seconds will tell you whether it holds up next to your artists' work.</t>
+One thing I would guess at. How often does a custom project come back smaller than it started?
+Not lost, just trimmed. A feature wall becomes an accent panel. That trim is almost always uncertainty rather than budget, and it is worth counting, because it never shows up as a lost sale in any report.
+ai.mecartworks.com. ai.mecartworks.com. Five previews, free, nothing to subscribe to. Upload a room, describe the piece, see it in place.</t>
         </is>
       </c>
       <c r="AX62" s="4" t="inlineStr">
@@ -14374,10 +14340,10 @@
       <c r="AY62" s="5" t="inlineStr">
         <is>
           <t>Heather,
-I'll stop here.
-If your designers already have a way to show a client the finished wall before it's printed, you've solved the hard part — and I'd genuinely like to know how.
-If not: ai.mecartworks.com, five previews, free.
-Either way, paying artists a royalty on every piece sold in their name is a good thing to see in this industry.</t>
+That is everything from me.
+If your designers already have a way to show a client the finished wall before it is printed, you have solved the hard part and I would like to know how.
+If not, ai.mecartworks.com, five previews, free.
+Paying artists a royalty on every piece sold in their name is a good thing to see in this industry.</t>
         </is>
       </c>
     </row>
@@ -14973,16 +14939,16 @@
       </c>
       <c r="AT65" s="4" t="inlineStr">
         <is>
-          <t>Murals &amp; Graphics, before the first install</t>
+          <t>Murals and Graphics, before the first install</t>
         </is>
       </c>
       <c r="AU65" s="5" t="inlineStr">
         <is>
           <t>Susan,
-USV Murals &amp; Graphics is a different sell from hotel standards. Marriott and Hilton buy to spec — they know exactly what arrives. Art-led work gets bought on how it looks in the room.
-And a new line has no installed photography yet, so there's nothing to point at.
-We built the AI studio MEC Artworks runs. It fills that gap: upload a photo of the space, describe the mural, see it on the wall before it's printed.
-Would it help to see one of your new pieces mocked into a real hotel corridor? I'll send it over.</t>
+USV Murals and Graphics is a different sell from hotel standards. Marriott and Hilton buy to spec and know exactly what arrives. Art led work gets bought on how it looks in the room.
+And a new line has no installed photography yet, so there is nothing to point at. Every early sale has to be made on description alone.
+We built this already, for MEC Artworks. Upload a photo of the space, describe the mural, see it on the wall before it is printed.
+Would it help to see one of your new pieces put into a real hotel corridor? I will send it over.</t>
         </is>
       </c>
       <c r="AV65" s="4" t="inlineStr">
@@ -14993,10 +14959,9 @@
       <c r="AW65" s="5" t="inlineStr">
         <is>
           <t>Susan,
-Worth adding — it isn't a rendering job. Someone types "brushed gold, botanical, low contrast" and gets an original concept back, then drops it into a photo of the actual space.
-For a line without a back catalogue, that does the job reference images usually do.
-ai.mecartworks.com — email code, five previews, no subscription.
-If it's not up to your print standards you'll know in two minutes, and I'll take the hint.</t>
+Worth adding, it is not a rendering job. Someone types "brushed gold, botanical, low contrast" and gets an original concept, then drops it into a photo of the actual space.
+For a line with no back catalogue, that does the job reference images usually do. You get to sell the new direction with pictures instead of waiting a year for the first install to photograph.
+ai.mecartworks.com, five free previews, email code.</t>
         </is>
       </c>
       <c r="AX65" s="4" t="inlineStr">
@@ -15007,10 +14972,10 @@
       <c r="AY65" s="5" t="inlineStr">
         <is>
           <t>Susan,
-Closing this off.
-Forty years of combined print experience on your team means you've solved harder problems than showing a mural before it exists.
-If the Murals &amp; Graphics launch ever needs that, ai.mecartworks.com is the working example.
-Good luck with it either way.</t>
+I will let you get on.
+Forty years of combined print experience on your team means you have solved harder problems than showing a mural before it exists.
+If the Murals and Graphics launch ever needs it, ai.mecartworks.com is the working example.
+Best of luck with the launch.</t>
         </is>
       </c>
     </row>
@@ -15226,38 +15191,37 @@
       <c r="AU66" s="5" t="inlineStr">
         <is>
           <t>Bardia,
-Kimia's line about no two tiles being exactly alike — subtle variation in colour and texture — is the honest way to sell handmade tile.
-It's also the hardest thing to sell from a sample. One tile shows the variation; it doesn't show what a whole wall of it looks like, and the wall is what the client is actually buying.
-We built the AI studio MEC Artworks runs. Someone describes the space and sees the treatment across a photo of the real wall.
-Worth two minutes?</t>
+Kimia's line about no two tiles being exactly alike, with subtle variation in colour and texture, is the honest way to sell handmade tile.
+It is also the hardest thing to sell from a sample. One tile shows the variation. It does not show what a whole wall of it looks like, and the wall is what the client is actually buying.
+MEC Artworks has one. We built it for them. Someone describes the space and sees the treatment across a photo of the real wall.
+Would you take a look?</t>
         </is>
       </c>
       <c r="AV66" s="4" t="inlineStr">
         <is>
-          <t>character across a wall, inconsistency on a sample</t>
+          <t>character on a wall, inconsistency on a sample</t>
         </is>
       </c>
       <c r="AW66" s="5" t="inlineStr">
         <is>
           <t>Bardia,
-The specific gap for handmade: variation reads as character across a wall and as inconsistency on a single sample.
-Showing the whole surface before the order is placed removes the objection you probably answer most often.
-ai.mecartworks.com — free, five previews, email code.
-Two minutes and you'd know whether it renders the variation honestly.</t>
+The specific problem with handmade. Variation reads as character across a whole wall and as inconsistency on a single sample.
+Showing the full surface before the order is placed removes the objection you probably answer more often than any other. It also protects you after delivery, because the client already knew what they were getting.
+ai.mecartworks.com, free to try, five previews, email code.</t>
         </is>
       </c>
       <c r="AX66" s="4" t="inlineStr">
         <is>
-          <t>the sample-to-wall gap</t>
+          <t>the sample to wall gap</t>
         </is>
       </c>
       <c r="AY66" s="5" t="inlineStr">
         <is>
           <t>Bardia,
-Last note from me.
-Building a tile company in the UAE market means you're closer to how your clients decide than I could be from here.
-ai.mecartworks.com if the sample-to-wall gap is ever a problem.
-Good luck with the growth.</t>
+Last word from me.
+Building a tile company in the UAE market means you are closer to how your clients decide than I could be from here.
+ai.mecartworks.com if the sample to wall gap is ever a problem.
+Best of luck with the growth.</t>
         </is>
       </c>
     </row>
@@ -15783,17 +15747,16 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>approving a wall they've never seen</t>
+          <t>approving a wall they have never seen</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
           <t>Heather,
-Area sells to the trade only, and your FAQ says if someone brings a piece or a photograph, you'll build the wallcovering around it.
-So the person who signs off — the designer's client — is approving from a sample and their imagination. That's where custom work shrinks: a smaller wall, a safer colourway, a "let's revisit next quarter."
-Show them the finished piece on their own wall and they stop hedging. Bigger yes, sooner.
-We built the AI studio MEC Artworks runs.
-Want me to run one of your collections through it and send you the result?</t>
+Area sells to the trade only, and your FAQ says if someone brings a piece or a photograph, you will build the wallcovering around it.
+So the person who signs off, the designer's client, is approving from a sample and their imagination. That is where custom work shrinks. A smaller wall, a safer colourway, a let us revisit next quarter.
+Show them the finished piece on their own wall and they stop hedging. Bigger yes, and sooner.
+We built the AI studio MEC Artworks put on their site. Want me to run one of your collections through it and send you the result?</t>
         </is>
       </c>
       <c r="M2" s="4" t="inlineStr">
@@ -15804,10 +15767,9 @@
       <c r="N2" s="5" t="inlineStr">
         <is>
           <t>Heather,
-One thing I'd guess at: how often does a custom project come back smaller than it started?
-Not lost — just trimmed. A feature wall becomes an accent panel. That trim is almost always uncertainty, not budget.
-The tool is at ai.mecartworks.com. Email code, five free previews, no subscription. Upload a room, describe the piece, see it in place.
-Ninety seconds will tell you whether it holds up next to your artists' work.</t>
+One thing I would guess at. How often does a custom project come back smaller than it started?
+Not lost, just trimmed. A feature wall becomes an accent panel. That trim is almost always uncertainty rather than budget, and it is worth counting, because it never shows up as a lost sale in any report.
+ai.mecartworks.com. ai.mecartworks.com. Five previews, free, nothing to subscribe to. Upload a room, describe the piece, see it in place.</t>
         </is>
       </c>
       <c r="O2" s="4" t="inlineStr">
@@ -15818,10 +15780,10 @@
       <c r="P2" s="5" t="inlineStr">
         <is>
           <t>Heather,
-I'll stop here.
-If your designers already have a way to show a client the finished wall before it's printed, you've solved the hard part — and I'd genuinely like to know how.
-If not: ai.mecartworks.com, five previews, free.
-Either way, paying artists a royalty on every piece sold in their name is a good thing to see in this industry.</t>
+That is everything from me.
+If your designers already have a way to show a client the finished wall before it is printed, you have solved the hard part and I would like to know how.
+If not, ai.mecartworks.com, five previews, free.
+Paying artists a royalty on every piece sold in their name is a good thing to see in this industry.</t>
         </is>
       </c>
     </row>
@@ -15874,29 +15836,28 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>your artists, working step-by-step</t>
+          <t>your artists, working step by step</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
           <t>Sal,
-Blue Water's own copy says your ceramic artists work with the customer step-by-step to create the custom piece — logos, mascots, family crests.
-That's a person on every enquiry. The design software sits with your team, so the customer only sees a result after someone has already spent the hours.
-Being direct: we built the AI studio MEC Artworks runs — same industry as you. It puts a first version on screen from a description, on a photo of the actual pool.
-Happy to walk you through it. Worth 15 minutes?</t>
+Your own site says your ceramic artists work with the customer step by step to create the custom piece. Logos, mascots, family crests.
+That means a person on every request. The design software sits with your team, so the customer sees nothing until someone has already spent the hours. The ones who go quiet after that took those hours with them.
+Being direct: we built the AI studio that MEC Artworks runs, same industry as you. It puts a first version on screen from a description, on a photo of the actual pool.
+Happy to show you myself. Would fifteen minutes work?</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>software for your artists vs software for your customer</t>
+          <t>software for your artists, software for your customer</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr">
         <is>
           <t>Sal,
-The difference in one line: your software is a tool for your artists. This one is a tool for your customer.
-They type "navy, school mascot, six feet across", see a version on the pool photo, and arrive at your artists already knowing what they want.
-Same step-by-step outcome, minus the hours spent before the customer is serious.
+The difference in one line. Your software is a tool for your artists. This one is a tool for your customer.
+They type "navy, school mascot, six feet across", see a version on the pool photo, and arrive at your artists already knowing what they want. Same step by step service. The unpaid hours at the front of it go away.
 Screen share, 15 minutes, no deck. Want me to send times?</t>
         </is>
       </c>
@@ -15908,10 +15869,10 @@
       <c r="P3" s="5" t="inlineStr">
         <is>
           <t>Sal,
-I'll close this off.
-Twenty years in the pool industry means you've seen a lot of tools promise this. Fair to be sceptical.
-The walkthrough offer stands if it's ever worth an afternoon.
-Good luck with the season.</t>
+I will close this off.
+Twenty years in the pool business means you have watched a lot of tools promise this exact thing. Being sceptical is the right call.
+The walkthrough offer stands if it is ever worth an afternoon.
+Best of luck with the rest of the year.</t>
         </is>
       </c>
     </row>
@@ -15970,9 +15931,9 @@
       <c r="L4" s="5" t="inlineStr">
         <is>
           <t>Verena,
-Glamora offers a Bespoke Design Service to professionals — an architect brings a project, your studio designs to it.
-That process starts with a conversation and a lot of imagination. The client approving the budget usually can't picture the result, which is where bespoke work gets trimmed or delayed.
-We built the AI studio MEC Artworks runs. It puts a concept on screen in that first conversation — described in words, then placed on a photo of the actual space.
+Glamora offers a Bespoke Design Service to professionals. An architect brings a project, your studio designs to it.
+That process starts with a conversation and a lot of imagining. The person who signs off the budget usually cannot picture the result, and that is where bespoke work gets cut back or pushed to next quarter.
+We built the AI design tool MEC Artworks runs. It puts a concept on screen inside that first conversation. Described in words, then placed on a photo of the real space.
 Would it be useful to see it against one of your collections?</t>
         </is>
       </c>
@@ -15984,10 +15945,9 @@
       <c r="N4" s="5" t="inlineStr">
         <is>
           <t>Verena,
-The detail worth adding: no CAD and no drawing. Someone describes the piece — colour, mood, scale — and gets an original concept, then sees it in the room.
-For a bespoke service selling into hotels like SILENA and Bellerive, that turns the first meeting into a decision instead of a brief.
-ai.mecartworks.com — free, five previews, email verification only.
-Two minutes and you'll know if it holds up next to Glamora's work.</t>
+Worth adding, because "AI" says nothing useful on its own. There is no CAD and no drawing. Someone describes the piece by colour, mood and scale, gets an original concept, then sees it in the room.
+For a bespoke service selling into hotels like SILENA and Bellerive, the value is simple. The first meeting ends with a direction instead of a brief, so your studio spends its hours on work someone has already said yes to.
+ai.mecartworks.com. Five free previews after a one time code.</t>
         </is>
       </c>
       <c r="O4" s="4" t="inlineStr">
@@ -15998,10 +15958,10 @@
       <c r="P4" s="5" t="inlineStr">
         <is>
           <t>Verena,
-I'll leave this with you.
-If your studio already shows clients something visual in that first meeting, you've solved the part most bespoke suppliers haven't.
-If not, ai.mecartworks.com is the working example.
-Either way, the hospitality work on your diary page is a strong showcase.</t>
+This is the last one.
+If your studio already puts something visual in front of a client in that first meeting, you have solved the part most bespoke suppliers have not, and I would take that as the answer.
+If not, the working example is at ai.mecartworks.com.
+The hospitality work in your diary section is a strong showcase.</t>
         </is>
       </c>
     </row>
@@ -16060,9 +16020,9 @@
       <c r="L5" s="5" t="inlineStr">
         <is>
           <t>Anna,
-Heath built a set builder for dinnerware — start building, save 10%, see it come together.
-Tile doesn't have one. It has over a hundred glazes and an inquiry form, which means the customer choosing between them is doing it in their head while the dinnerware customer gets a tool.
-We built the AI studio MEC Artworks runs. Someone describes a room, sees a tile treatment placed in a photo of it, and chooses with their eyes.
+Heath built a set builder for dinnerware. Start building, save 10%, watch it come together.
+Tile does not have one. It has over a hundred glazes and a contact form, which means the customer choosing between them is doing it in their head, while the dinnerware customer gets a tool that does it for them.
+We built the AI studio running on MEC Artworks' site. Someone describes a room, sees a tile treatment placed in a photo of it, and chooses with their eyes.
 Worth seeing the parallel?</t>
         </is>
       </c>
@@ -16074,10 +16034,9 @@
       <c r="N5" s="5" t="inlineStr">
         <is>
           <t>Anna,
-Seeds of Summer is the case in point — moodier pinks and reds, launched in April, and the hard part is getting someone to imagine a whole wall of it.
-Described in words, rendered into their own room, decided in a minute.
-ai.mecartworks.com — free, five previews, email code only.
-Two minutes will tell you whether the glazes survive the translation.</t>
+Seeds of Summer is the case in point. Moodier pinks and reds, launched in April, and the hard part is getting someone to picture a whole wall of it from a swatch.
+Described in words, rendered into their own room, decided in a minute. A seasonal collection has a short window, and anything that shortens the decision inside that window is worth more than it looks.
+ai.mecartworks.com, free, five previews, email code only.</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -16088,10 +16047,10 @@
       <c r="P5" s="5" t="inlineStr">
         <is>
           <t>Anna,
-I'll leave this here.
-Heath's design standards are the reason to say no to a tool like this, and I'd take that answer seriously.
+I will drop it here.
+Heath's design standards are the best reason to say no to a tool like this, and I would take that answer seriously.
 ai.mecartworks.com if the tile side ever wants what the dinnerware side has.
-Either way, Seeds of Summer is a beautiful collection.</t>
+Seeds of Summer is a beautiful collection.</t>
         </is>
       </c>
     </row>
@@ -16156,24 +16115,23 @@
       <c r="L6" s="5" t="inlineStr">
         <is>
           <t>Lindsay,
-The Gilded print technology in the Reflections Collection — fine gold accents, reflective detail — is the kind of thing that has to be seen rather than described.
-Which is the whole difficulty. Your process is deliberately collaborative, concept through production, and each round of that collaboration is your team's time before a job is confirmed.
-We built the AI studio MEC Artworks runs. A designer describes the piece and sees it in a photo of the actual space.
+The Gilded print technology in the Reflections Collection, with fine gold accents and reflective detail, is the kind of thing that has to be seen rather than described. A photo does not carry it.
+That is the whole difficulty. Your process is deliberately collaborative, concept through production, and every round of that collaboration is your team's time spent before a job is confirmed.
+We built MEC Artworks an AI studio for this. A designer describes the piece and sees it in a photo of the actual space.
 Worth 15 minutes?</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>for a 15-person studio, rounds are margin</t>
+          <t>for a 15 person studio, rounds are margin</t>
         </is>
       </c>
       <c r="N6" s="5" t="inlineStr">
         <is>
           <t>Lindsay,
-The commercial angle for a fifteen-person studio: rounds are your margin.
-If the designer and their client agree a direction from a rendered image before your team starts, you spend production time on confirmed work instead of exploration.
-ai.mecartworks.com — five free previews, email code only.
-Two minutes will tell you whether it does the Gilded finish justice. I suspect that's the real test.</t>
+What it is worth to a fifteen person studio. Rounds are your margin.
+If the designer and their client agree a direction from a rendered image before your team starts, you spend production time on confirmed work instead of exploring. That is the difference between a studio that grows and one that stays busy.
+It lives at ai.mecartworks.com. Five free previews, no password. Two minutes will tell you whether it does the Gilded finish justice, and I suspect that is the real test.</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
@@ -16184,10 +16142,10 @@
       <c r="P6" s="5" t="inlineStr">
         <is>
           <t>Lindsay,
-I'll leave it here.
-Founder-run and fifteen people means every tool has to earn its place, so no is a completely reasonable answer.
+Closing the loop and stopping.
+Founder run and fifteen people means every tool has to earn its place, so no is a completely reasonable answer.
 ai.mecartworks.com if the concept rounds ever get long.
-Either way, building a print operation alongside a design studio is a genuinely smart structure.</t>
+Building a print operation alongside a design studio is a genuinely smart structure.</t>
         </is>
       </c>
     </row>
@@ -16246,10 +16204,10 @@
       <c r="L7" s="5" t="inlineStr">
         <is>
           <t>Stephenie,
-New Ravenna's bespoke route starts with photographs, fabric swatches, sometimes a magazine clipping — and your team turning that into a mosaic concept before anything is cut.
-You have a manager for that step, which tells me it carries real weight and real hours.
-Being upfront: we built the AI studio MEC Artworks runs, and they're in mosaics too. It produces a first-pass concept from a description and places it on a photo of the room.
-I'd rather show you than send a competitor's link. Worth 15 minutes?</t>
+New Ravenna's bespoke route starts with photographs, fabric swatches, sometimes a magazine clipping, and your team turning that into a mosaic concept before anything is cut.
+You have a manager dedicated to that step. That tells me it carries real weight and real hours, and that it happens before the client has committed.
+Being upfront: we built the AI studio that MEC Artworks runs, and they are in mosaics too. It makes a first pass concept from a description and places it on a photo of the room.
+I would rather show you than send a competitor's link. Free for fifteen minutes this week?</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
@@ -16260,10 +16218,9 @@
       <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Stephenie,
-The mechanic specifically: someone types "warm terracotta, geometric, Moorish influence" and gets an original concept back, then sees it on a photo of the actual wall.
-It doesn't replace a concept board. It gets the client to a direction before the board is worth making — which is where your team's hours go.
-Fifteen minutes on a screen share and you'd know.
-Want me to send a couple of times?</t>
+How it actually works. Someone types "warm terracotta, geometric, Moorish influence" and gets an original concept, then sees it on a photo of the real wall.
+It does not replace a concept board. It gets the client to a direction before the board is worth making, which is where your team's hours currently go. The boards you do make are then for clients who have already chosen.
+Fifteen minutes on a screen share and you would know. Want me to propose a time?</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -16274,9 +16231,9 @@
       <c r="P7" s="5" t="inlineStr">
         <is>
           <t>Stephenie,
-I'll leave this alone now.
-If your first pass is already fast enough at the volume you run, that's a good place to be and I'm glad I asked.
-If it's ever the bottleneck — usually when volume climbs, not when the work changes — the walkthrough offer stands.
+I will leave this alone now.
+If your first pass is already fast enough at the volume you run, that is a good place to be and I am glad I asked.
+If it ever becomes the slow part, and that usually happens when volume climbs rather than when the work changes, the offer to walk you through it stands.
 Thanks for reading this far.</t>
         </is>
       </c>
@@ -16330,16 +16287,16 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Murals &amp; Graphics, before the first install</t>
+          <t>Murals and Graphics, before the first install</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
           <t>Susan,
-USV Murals &amp; Graphics is a different sell from hotel standards. Marriott and Hilton buy to spec — they know exactly what arrives. Art-led work gets bought on how it looks in the room.
-And a new line has no installed photography yet, so there's nothing to point at.
-We built the AI studio MEC Artworks runs. It fills that gap: upload a photo of the space, describe the mural, see it on the wall before it's printed.
-Would it help to see one of your new pieces mocked into a real hotel corridor? I'll send it over.</t>
+USV Murals and Graphics is a different sell from hotel standards. Marriott and Hilton buy to spec and know exactly what arrives. Art led work gets bought on how it looks in the room.
+And a new line has no installed photography yet, so there is nothing to point at. Every early sale has to be made on description alone.
+We built this already, for MEC Artworks. Upload a photo of the space, describe the mural, see it on the wall before it is printed.
+Would it help to see one of your new pieces put into a real hotel corridor? I will send it over.</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
@@ -16350,10 +16307,9 @@
       <c r="N8" s="5" t="inlineStr">
         <is>
           <t>Susan,
-Worth adding — it isn't a rendering job. Someone types "brushed gold, botanical, low contrast" and gets an original concept back, then drops it into a photo of the actual space.
-For a line without a back catalogue, that does the job reference images usually do.
-ai.mecartworks.com — email code, five previews, no subscription.
-If it's not up to your print standards you'll know in two minutes, and I'll take the hint.</t>
+Worth adding, it is not a rendering job. Someone types "brushed gold, botanical, low contrast" and gets an original concept, then drops it into a photo of the actual space.
+For a line with no back catalogue, that does the job reference images usually do. You get to sell the new direction with pictures instead of waiting a year for the first install to photograph.
+ai.mecartworks.com, five free previews, email code.</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
@@ -16364,10 +16320,10 @@
       <c r="P8" s="5" t="inlineStr">
         <is>
           <t>Susan,
-Closing this off.
-Forty years of combined print experience on your team means you've solved harder problems than showing a mural before it exists.
-If the Murals &amp; Graphics launch ever needs that, ai.mecartworks.com is the working example.
-Good luck with it either way.</t>
+I will let you get on.
+Forty years of combined print experience on your team means you have solved harder problems than showing a mural before it exists.
+If the Murals and Graphics launch ever needs it, ai.mecartworks.com is the working example.
+Best of luck with the launch.</t>
         </is>
       </c>
     </row>
@@ -16426,10 +16382,10 @@
       <c r="L9" s="5" t="inlineStr">
         <is>
           <t>Michael,
-Your "Create a Mosaic" service is why I'm writing — a homeowner or builder describes what they want in the pool, and your team turns it into a design.
-Between that conversation and an approved drawing is where custom pool work slows down, and pool budgets move fast.
-Being upfront: we built the AI studio MEC Artworks runs, and they're in mosaics too. It takes a plain-words description and puts the design on a photo of the actual pool.
-Happy to walk you through it rather than send a link — worth 15 minutes?</t>
+Your Create a Mosaic service is why I am writing. A homeowner or a builder describes what they want in the pool, and your team turns it into a design.
+The gap between that conversation and an approved drawing is where custom pool work stalls. Pool budgets move fast, and a client who cannot picture the result often takes the plain tile instead.
+Straight with you: MEC Artworks runs an AI studio we built, and they work in mosaics too. It takes a plain description and puts the design on a photo of the actual pool.
+I would rather walk you through it than send you a competitor's link. Can I book fifteen minutes?</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
@@ -16440,10 +16396,9 @@
       <c r="N9" s="5" t="inlineStr">
         <is>
           <t>Michael,
-The specific mechanic: someone types "deep blue, geometric, Mediterranean" and gets an original mosaic concept back, then it's placed on a photo of the real pool.
-At a Ritz-Carlton level of spec, that's the difference between selling a drawing and selling a picture of the finished pool.
-I'd rather show you than have you register on a competitor's site — 15 minutes, screen share, no deck.
-Want me to send a couple of times?</t>
+How it works. Someone types "deep blue, geometric, Mediterranean" and gets an original mosaic concept, then it is placed on a photo of the real pool.
+The difference is what you are selling. A drawing asks the client to trust you. A picture of their own pool asks them to approve something they can already see. At a Ritz-Carlton level of spec that changes which option gets picked.
+Fifteen minutes on a screen share, no deck. Shall I send two or three times that suit you?</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -16454,10 +16409,10 @@
       <c r="P9" s="5" t="inlineStr">
         <is>
           <t>Michael,
-I'll stop here.
-If your team already gets clients to a yes quickly on custom pools, that's the whole game and you've got it.
-If concept-to-approval is ever the slow part, the offer to walk you through it stands.
-Either way, good luck with the season.</t>
+That is me done.
+If your team already gets clients to yes quickly on custom work, that is the whole game and you have it.
+If the stretch between concept and approval is ever the slow part, the offer to walk you through it stands.
+Good luck with the season.</t>
         </is>
       </c>
     </row>
@@ -16516,10 +16471,10 @@
       <c r="L10" s="5" t="inlineStr">
         <is>
           <t>Colleen,
-"Tailored To" is a proper bespoke programme — custom cutting and finishing, not just a size option.
-The client approving it is looking at slabs and gallery photos and imagining the result. At Artistic Tile's price point, imagination is doing a lot of expensive work.
-Being upfront: we built the AI studio MEC Artworks runs — they're in tile and mosaic too. It renders a described design onto a photo of the actual room.
-I'd rather walk you through it than send a competitor's link. Worth 15 minutes?</t>
+Tailored To is a real bespoke programme. Custom cutting and finishing, not a size option with a nicer name.
+The client approving it is looking at slabs and gallery photos and imagining the rest. At Artistic Tile's price point, that imagining is doing very expensive work, and it usually argues for the safer choice.
+Being upfront: we built the AI studio that MEC Artworks runs, and they are in tile and mosaic too. It renders a described design onto a photo of the actual room.
+I would rather walk you through it than send a competitor's link. Open to a short call?</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
@@ -16530,10 +16485,9 @@
       <c r="N10" s="5" t="inlineStr">
         <is>
           <t>Colleen,
-From a marketing angle: this is content as much as it is a tool.
-A visitor describes what they want, sees it on their own wall, and hands you their intent — which is a better lead than a sample request.
-Fifteen minutes on a screen share and you'd know if it's worth a conversation internally.
-Want me to send a couple of times?</t>
+From a marketing seat there is a second angle here. This is content as much as it is a tool.
+A visitor describes what they want, sees it on their own wall, and hands you their intent while doing it. That is a far better lead than a sample request, because you learn the room, the style and the scale before anyone calls them.
+Fifteen minutes on a screen share and you would know whether it is worth raising internally. Want me to send a couple of times?</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
@@ -16544,10 +16498,10 @@
       <c r="P10" s="5" t="inlineStr">
         <is>
           <t>Colleen,
-I'll stop here.
-If Tailored To is already converting the way you want, this is noise and I'd rather not add to your inbox.
+Last one, then I am out of your inbox.
+If Tailored To already converts the way you want, this is noise and I would rather not add to your inbox.
 The offer to walk through it stands.
-Either way, good luck with the season's launches.</t>
+Best of luck with the season's launches.</t>
         </is>
       </c>
     </row>
@@ -16610,9 +16564,9 @@
       <c r="L11" s="5" t="inlineStr">
         <is>
           <t>Mark,
-Making the New Orleans letter and number tiles for the city since 2003 is a hard credential to argue with.
-The rest of the range is where I'm curious — Victorian patterns with traditional and specialty glazing, ordered by people who've only seen a photo of somebody else's floor.
-We built the AI studio MEC Artworks runs. Someone describes what they want and sees it laid into a photo of their own room.
+Making the city's letter and number tiles since 2003 is a hard credential to argue with.
+The rest of the range is what I am curious about. Victorian patterns with traditional and specialty glazing, ordered by people who have only seen a photo of somebody else's floor. Some of them buy less than they wanted because they are not sure.
+We built an AI studio for MEC Artworks. Someone describes what they want and sees it laid into a photo of their own room.
 Worth two minutes of an owner's time?</t>
         </is>
       </c>
@@ -16624,10 +16578,10 @@
       <c r="N11" s="5" t="inlineStr">
         <is>
           <t>Mark,
-More useful detail: no drawing, no software to learn. A customer types "Victorian, deep green, geometric border" and sees it on their own floor.
-For a studio your size that's the difference between answering the same questions by email for a week and getting to a yes.
-ai.mecartworks.com — five free previews, email code.
-If it doesn't do your glazes justice, I'd want to know that too.</t>
+The useful detail. No drawing, no software to learn. A customer types "Victorian, deep green, geometric border" and sees it on their own floor.
+For a studio your size that is the difference between answering the same three questions by email all week and getting to a yes. Your time is the scarce thing here, not the tile.
+ai.mecartworks.com. Five free previews after a one time code.
+If it does not do your glazes justice, I would want to know that too.</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -16638,10 +16592,10 @@
       <c r="P11" s="5" t="inlineStr">
         <is>
           <t>Mark,
-I'll leave it here.
+Signing off on this one.
 Running a studio means the last thing you need is another tool to evaluate. Fair enough.
-ai.mecartworks.com if it's ever a slow week.
-Either way, twenty-plus years making the city's own tiles is a good thing to have built.</t>
+ai.mecartworks.com if it is ever a slow week.
+Twenty plus years making the city's own tiles is a good thing to have built.</t>
         </is>
       </c>
     </row>
@@ -16696,10 +16650,10 @@
       <c r="L12" s="5" t="inlineStr">
         <is>
           <t>Ivars,
-Fancy Walls already white-labels — private label, dropship, one to two day turnaround. You sell your capability onward, not just your product.
-Which makes the bottleneck clear: your partners' customers still have to decide what they want before any of that speed matters. Printing in two days doesn't help if choosing took three weeks.
-We built the AI studio MEC Artworks runs. It compresses the choosing — describe it, get an original design, see it on your own wall.
-Want me to show you where it would sit in a private-label flow?</t>
+Fancy Walls already sells its capability onward. Private label, dropship, one to two day turnaround. That is a harder business to build than a shop.
+Which makes the slow point easy to spot. Your partners' customers still have to decide what they want before any of that speed helps. Printing in two days does nothing if choosing took three weeks.
+We are the studio behind MEC Artworks' AI tool. It shortens the choosing. Describe it, get an original design, see it on your own wall.
+Want me to show you where it would sit inside a private label flow?</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
@@ -16710,24 +16664,23 @@
       <c r="N12" s="5" t="inlineStr">
         <is>
           <t>Ivars,
-More concretely: a shopper types what they want, gets an original design back, and sees it on a photo of their room — no drawing, no designer.
-For a dropship partner that's the difference between a browser and an order. Your two-day turnaround only starts once someone decides.
-ai.mecartworks.com — five free previews, email code.
-Happy to talk through the embed side if it looks relevant.</t>
+More concrete. A shopper types what they want, gets an original design back, and sees it on a photo of their room. No drawing, no designer, no brief.
+The angle I think is actually yours: you already white label. A design step your partners can put their own name on is another thing to sell them, not just a feature on your site. That is a revenue line, not a cost.
+ai.mecartworks.com, five free previews, email code.</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>is choosing actually your bottleneck?</t>
+          <t>is choosing really the slow part?</t>
         </is>
       </c>
       <c r="P12" s="5" t="inlineStr">
         <is>
           <t>Ivars,
-Last note.
-If your private-label partners already convert well without a design step, then this isn't your bottleneck and I'd rather know that.
-If it is, ai.mecartworks.com shows what it looks like.
-Either way — 3,400 designs and two-day print is a genuinely strong setup.</t>
+I will stop here.
+If your private label partners convert fine without a design step, then this is not your problem and I would rather know that than keep guessing.
+If it is, ai.mecartworks.com shows what it looks like in practice.
+3,400 designs with a two day print run is a strong setup whatever you decide.</t>
         </is>
       </c>
     </row>
@@ -16790,10 +16743,10 @@
       <c r="L13" s="5" t="inlineStr">
         <is>
           <t>Christina,
-Hakatai does custom designed glass tile installations — mosaic murals and uncut custom patterns, not just stock series.
-That work asks the client to picture a whole wall from a sample board and a photo of somebody else's project. Some of them shrink the scope rather than commit.
-Being straight: we built the AI studio MEC Artworks runs — same industry. It generates a concept from a description and places it on a photo of the actual space.
-Happy to walk you through it — worth 15 minutes?</t>
+Hakatai does custom designed glass tile installations. Mosaic murals and uncut custom patterns, not only stock series.
+That work asks a client to picture a whole wall from a sample board and a photo of someone else's project. Plenty of them shrink the job rather than commit to the version they cannot see.
+Being straight: we built the AI studio that MEC Artworks runs, same industry. It creates a concept from a description and places it on a photo of the actual space.
+Happy to walk you through it instead. Fifteen minutes on a call?</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
@@ -16804,10 +16757,9 @@
       <c r="N13" s="5" t="inlineStr">
         <is>
           <t>Christina,
-The commercial version of this: clients who can see the finished wall approve the bigger piece, and they approve it sooner.
-Someone types "sea glass blues, organic, twelve feet" and sees it on the real wall — before the layout work starts.
-I'd rather demo it than send you to a competitor's site. Fifteen minutes, screen share.
-Want a couple of times?</t>
+The money point, plainly. A client who can see the finished wall does not need to hedge. The ones who cannot see it protect themselves by ordering less.
+Someone types "sea glass blues, organic, twelve feet" and sees it on the real wall, before any layout work starts.
+I would rather demo it than send you to a competitor's site. Fifteen minutes, screen share. Want a couple of times?</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -16819,9 +16771,9 @@
         <is>
           <t>Christina,
 Closing this out.
-As CEO you'll have a clearer view than I do on whether custom enquiries convert well enough already. If they do, ignore me entirely.
-The offer to walk through it stands.
-Good luck with the year.</t>
+As CEO you have a clearer view than I do on whether custom requests already convert well enough. If they do, ignore me completely.
+The offer to show you stands.
+Thanks for the time.</t>
         </is>
       </c>
     </row>
@@ -16876,10 +16828,10 @@
       <c r="L14" s="5" t="inlineStr">
         <is>
           <t>Paolo,
-Inkiostro Bianco offers progetti su misura — and with a 3D lead in the room, you're already producing visuals to sell them.
-That's the expensive part. Every bespoke enquiry that needs a render costs studio time before anyone has committed to anything.
-We built the AI studio MEC Artworks runs. It produces the first-pass version in seconds: describe the piece, get an original concept, place it on a photo of the room.
-Not a replacement for your 3D work — a filter in front of it. Worth a look?</t>
+Inkiostro Bianco offers progetti su misura, and with a 3D lead in the room you are already making visuals to sell them.
+That is the expensive part. Every custom request that needs a render costs studio time before anyone has committed to anything, and some of those requests were never going to close.
+MEC Artworks runs an AI studio. We built it. It makes the first pass in seconds. Describe the piece, get an original concept, place it on a photo of the room.
+Not a replacement for your 3D work. A filter in front of it. Worth a look?</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
@@ -16890,10 +16842,10 @@
       <c r="N14" s="5" t="inlineStr">
         <is>
           <t>Paolo,
-The part I'd want your read on specifically: output quality.
+You would judge this faster than anyone I could send it to, so I will be direct about what I want.
 Someone types "warm ochre, botanical, large scale" and gets an original concept, then drops it into a photo of the space. No CAD.
-You'd know within a minute whether it's good enough to put in front of a client, or only good enough to narrow a direction internally. Both are useful — I'd like to know which.
-ai.mecartworks.com, five free previews.</t>
+Within a minute you would know whether it is good enough to put in front of a client, or only good enough to narrow a direction in house. Both answers are useful to me, and the second one is still worth money to you, because it saves the render.
+ai.mecartworks.com, free, five previews, email code.</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
@@ -16904,10 +16856,10 @@
       <c r="P14" s="5" t="inlineStr">
         <is>
           <t>Paolo,
-I'll stop here.
-If your 3D pipeline already turns bespoke enquiries around fast enough, this solves nothing for you and that's a good place to be.
-If it's ever a queue, ai.mecartworks.com is the example.
-Either way, the Hotel La Gemma work is a strong reference.</t>
+I will let this go.
+If your 3D pipeline already turns custom requests around fast enough, this solves nothing for you. That is a good position and I am glad to hear it.
+If it ever backs up, the example is at ai.mecartworks.com.
+The Hotel La Gemma work is a strong reference to have.</t>
         </is>
       </c>
     </row>
@@ -16971,9 +16923,9 @@
         <is>
           <t>Carli,
 Kibak offers custom tile and custom murals, and the site invites people to book a meeting to talk the project through.
-That meeting is doing a lot of work — the customer arrives with a vague idea and you turn it into something concrete, one conversation at a time.
-We built the AI studio MEC Artworks runs. Someone describes the mural in plain words, gets an original concept, and sees it on a photo of the actual wall.
-Would that be useful before the meeting rather than during it?</t>
+That meeting is doing a lot of work. The customer arrives with a vague idea and you turn it into something concrete, one conversation at a time. Some of those meetings were never going to become orders.
+We built the AI tool MEC Artworks runs for their clients. Someone describes the mural in plain words, gets an original concept, and sees it on a photo of the actual wall.
+Would that be more useful before the meeting than during it?</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -16984,10 +16936,9 @@
       <c r="N15" s="5" t="inlineStr">
         <is>
           <t>Carli,
-Concretely: the customer books the meeting already holding a picture of what they want, placed in their own space.
-You spend the call refining instead of interpreting — and the ones who were never serious don't book at all.
-ai.mecartworks.com — five free previews, email code.
-Two minutes and you'd know whether it fits how Kibak works.</t>
+Concretely. The customer books the meeting already holding a picture of what they want, placed in their own space.
+Two things change. You spend the call refining instead of interpreting, and the people who were never serious do not book at all. For a studio where the owner takes the calls, that second one is the real saving.
+ai.mecartworks.com, five previews, email code, no subscription.</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -16998,10 +16949,10 @@
       <c r="P15" s="5" t="inlineStr">
         <is>
           <t>Carli,
-I'll leave this with you.
-If your booked meetings already convert well, this is a solution looking for a problem and I'd rather admit that.
-ai.mecartworks.com if the vague-idea stage is ever the slow one.
-Good luck with the year.</t>
+I will leave this with you.
+If your booked meetings already convert well, this is a solution looking for a problem and I would rather admit that than push.
+ai.mecartworks.com if the vague idea stage is ever the slow one.
+Thanks for reading.</t>
         </is>
       </c>
     </row>
@@ -17060,24 +17011,23 @@
       <c r="L16" s="5" t="inlineStr">
         <is>
           <t>Randi,
-"Create Your Blend" lets a customer pick colours for diamond tiles — and you have a director of design consultants, which suggests plenty of custom work starts as a conversation rather than a selector.
-Those first conversations are where the hours go: translating "something warm, sort of organic" into an actual layout.
-We built the AI studio MEC Artworks runs. It turns that sentence into an original concept and puts it on a photo of the customer's room.
+Create Your Blend lets a customer pick colours for diamond tiles, and you have a director of design consultants. That combination tells me plenty of custom work still starts as a conversation rather than a selector.
+Those first conversations are where the hours go. Turning "something warm, sort of organic" into an actual layout is skilled work, and most of it happens before anyone has paid.
+We built MEC Artworks the AI studio they run today. It turns that sentence into an original concept and puts it on a photo of the customer's room.
 Would it help your consultants to see it?</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>refining instead of interpreting</t>
+          <t>refining instead of guessing</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr">
         <is>
           <t>Randi,
-Specifically for a consulting team: it changes what the first call starts from.
-Instead of describing options, your consultant opens with a concept already placed in the customer's room, and spends the call refining rather than interpreting.
-ai.mecartworks.com — free, five previews, email code only.
-Two minutes and you'd know whether it's useful to the team or just to the marketing page.</t>
+For a consulting team, the value is in what the first call starts from.
+Right now your consultant describes options and the customer tries to picture them. With this, the call opens with a concept already placed in the customer's room, and the whole conversation becomes refining instead of guessing. Shorter calls, and more of them ending in a decision.
+ai.mecartworks.com. Free, five previews, code by email.</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
@@ -17089,9 +17039,9 @@
         <is>
           <t>Randi,
 Last note.
-If your consultants already get customers to a clear direction quickly, then this solves something you don't have.
-If the first ten minutes are ever the slow part, ai.mecartworks.com is the example.
-Either way — the Whitney commission is a remarkable credit.</t>
+If your consultants already get customers to a clear direction quickly, this solves something you do not have.
+If those first ten minutes are ever the slow part, the example is at ai.mecartworks.com.
+The Whitney commission is a remarkable credit to have.</t>
         </is>
       </c>
     </row>
@@ -17150,9 +17100,9 @@
       <c r="L17" s="5" t="inlineStr">
         <is>
           <t>Neil,
-Nineteen design collections in the Molding &amp; Trim series is a lot of choice — and choice is exactly what stalls a tile decision.
-A customer looking at stunning patterns and rich glazes across nineteen options usually needs someone to narrow it for them. That someone is you.
-We built the AI studio MEC Artworks runs. They describe the room, see a combination placed on a photo of it, and arrive at you already decided.
+Nineteen design collections in the Molding and Trim series is a lot of choice, and choice is exactly what stalls a tile decision.
+Someone looking at rich glazes across nineteen options usually needs a person to narrow it down for them. That person is you, and it happens before they have bought anything.
+The AI studio on MEC Artworks' site is our build. They describe the room, see a combination placed on a photo of it, and arrive at you already decided.
 Worth a couple of minutes?</t>
         </is>
       </c>
@@ -17164,10 +17114,9 @@
       <c r="N17" s="5" t="inlineStr">
         <is>
           <t>Neil,
-The practical version: the customer does the narrowing themselves, on screen, before they contact you.
-They type what they're after, see it on their own wall, and the conversation you get is about ordering rather than choosing.
-ai.mecartworks.com — free, five previews, email code only.
-Two minutes will tell you whether it handles your glazes properly.</t>
+The practical version. The customer narrows it themselves, on screen, before they contact you.
+They type what they are after, see it on their own wall, and the conversation you get is about ordering rather than choosing. Same sale, minus the unpaid consulting in the middle.
+ai.mecartworks.com, no cost, five previews, code by email. Two minutes will tell you whether it handles your glazes properly.</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -17178,10 +17127,10 @@
       <c r="P17" s="5" t="inlineStr">
         <is>
           <t>Neil,
-Last one from me.
-Owner-run means your time is the scarce thing, so I won't keep asking for it.
+Ending it here.
+Owner run means your time is the scarce thing, so I will not keep asking for it.
 ai.mecartworks.com if the choosing stage ever eats a week.
-Good luck with the season.</t>
+Thanks for the time.</t>
         </is>
       </c>
     </row>
@@ -17244,9 +17193,9 @@
       <c r="L18" s="5" t="inlineStr">
         <is>
           <t>Chad,
-Mosaics Lab offers a free design consultation on custom work — a customer sends a photo or a painting, and your team turns it into a mosaic concept.
-That's real staff time on every enquiry, spent before anyone has committed to buying.
-Straight with you: we built the AI studio MEC Artworks runs, and they're in your industry. It does the first pass — a description or an uploaded image in, concept out, placed on a photo of the space.
+Mosaics Lab offers a free design consultation on custom work. A customer sends a photo or a painting, and your team turns it into a mosaic concept.
+That is real staff time on every request, spent before anyone has agreed to buy anything. It works, which is why you do it, but it does not scale past the hours your artists have.
+Straight with you: we built the AI studio that MEC Artworks runs, and they are in your industry. It does that first pass from a description or an uploaded image, and places it on a photo of the space.
 Rather than point you at a competitor's site, can I walk you through it?</t>
         </is>
       </c>
@@ -17258,9 +17207,9 @@
       <c r="N18" s="5" t="inlineStr">
         <is>
           <t>Chad,
-The number I'd be curious about: how many free consultations turn into paid mosaics?
-If it's high, ignore me. If it's the usual, the consultation is doing sales work a first-pass visual could do in seconds — leaving your artists for the customers who are serious.
-Fifteen minutes on a screen share and you'd know whether it fits.
+The number I would want if I ran your business: what share of free consultations become paid mosaics?
+If it is high, ignore me. If it is the usual, then the consultation is doing sales work that a first draft could do in seconds, and your artists are spending their best hours on people who were never going to buy.
+That is the case for it in one line. Fifteen minutes on a screen share and you would know if it holds up.
 Want a couple of times?</t>
         </is>
       </c>
@@ -17272,10 +17221,10 @@
       <c r="P18" s="5" t="inlineStr">
         <is>
           <t>Chad,
-Last one from me.
-Owner-run studios usually know exactly where their time leaks, so if the consultation isn't one of them, I'll take your word for it.
+No more from me after this.
+Owner run studios usually know exactly where their time leaks. If the consultation is not one of yours, I will take your word for it.
 The walkthrough offer stands if it ever is.
-Good luck with the year.</t>
+Thanks for the time.</t>
         </is>
       </c>
     </row>
@@ -17334,10 +17283,10 @@
       <c r="L19" s="5" t="inlineStr">
         <is>
           <t>Justin,
-Project Tile is a smart piece of work — customers planning a backsplash or fireplace with your patterns instead of guessing.
-It starts once they've chosen the pattern, though. The customer who knows the room but not the tile has nothing to plan with, and that's usually where an art director's time gets spent.
-We built the AI studio MEC Artworks runs. It generates an original design from a description and places it on a photo of the actual room.
-Worth seeing how it sits in front of Project Tile?</t>
+Project Tile is a smart piece of work. Customers planning a backsplash or a fireplace with your patterns instead of guessing at them.
+It starts once they have chosen the pattern though. The customer who knows their room but not the tile has nothing to plan with, and sorting that out is usually where an art director's time disappears.
+We are the team behind MEC Artworks' AI studio. It creates an original design from a description and places it on a photo of the actual room.
+Worth seeing how it might sit in front of Project Tile?</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -17348,10 +17297,10 @@
       <c r="N19" s="5" t="inlineStr">
         <is>
           <t>Justin,
-As an art director you'd judge this faster than anyone: does the generated output look like something you'd let out under your name?
-Someone types "arts and crafts, muted green, botanical" and gets an original concept, placed in the room. Two minutes will answer it.
-ai.mecartworks.com — five free previews, email code.
-Genuinely interested in your verdict either way.</t>
+As an art director you will spot the flaws faster than I could list them, so here is the honest ask.
+Someone types "arts and crafts, muted green, botanical" and gets an original concept, placed in the room. Two minutes will tell you whether the output is something you would let out under the Motawi name.
+Either answer is useful to me. A no from an art director is worth more than a maybe from anyone else.
+Find it at ai.mecartworks.com. One code by email unlocks five previews.</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -17362,10 +17311,10 @@
       <c r="P19" s="5" t="inlineStr">
         <is>
           <t>Justin,
-I'll leave this here.
-Motawi's patterns are distinctive enough that generated design may be exactly the wrong fit — that's a legitimate answer and I'd rather hear it than not.
-ai.mecartworks.com if you're curious.
-Either way, Project Tile is better than most of what this industry ships.</t>
+I will leave this here.
+Motawi's patterns are distinctive enough that generated design may be exactly the wrong fit. That is a fair answer and I would rather hear it than not.
+ai.mecartworks.com if you are curious.
+Project Tile is better than most of what this industry ships.</t>
         </is>
       </c>
     </row>
@@ -17429,9 +17378,9 @@
         <is>
           <t>Sean,
 Oceanside's Special Order Program and the Uniquely Oceanside collaboration both let a client customise before the tile ships.
-Both still ask them to commit to a combination they've only seen as separate samples. Your own site makes the point — liners, decos and trim combine for "unlimited possibilities", which is a lot to hold in your head.
-Being upfront: we built the AI studio MEC Artworks runs, same industry. It puts the combination on a photo of the real space.
-Worth 15 minutes to walk through?</t>
+Both still ask them to commit to a combination they have only seen as separate samples. Your own site makes the point: liners, decos and trim combine for unlimited possibilities. That is a lot to hold in your head while deciding how to spend money.
+Being upfront: we built the AI studio that MEC Artworks runs, same industry. It puts the combination on a photo of the real space.
+Can I walk you through it? Fifteen minutes.</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
@@ -17442,10 +17391,9 @@
       <c r="N20" s="5" t="inlineStr">
         <is>
           <t>Sean,
-Where it fits Oceanside specifically: unlimited combinations is a selling point right up until the client has to choose one.
-Someone describes what they're after, sees it rendered on the actual pool or wall, and the special order gets placed instead of postponed.
-I'd rather show you directly than send a competitor's link. Fifteen minutes on a screen share.
-Want me to send times?</t>
+Where it fits Oceanside. Unlimited combinations is a great selling line right up to the moment a client has to pick one, and then it becomes the reason they delay.
+Someone describes what they are after, sees it on the actual pool or wall, and the special order gets placed instead of postponed to next season.
+I would rather show you directly than send a competitor's link. A quick screen share is all it takes. Want me to send times?</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
@@ -17456,10 +17404,10 @@
       <c r="P20" s="5" t="inlineStr">
         <is>
           <t>Sean,
-Last one from me.
-Thirty-plus years and a recycled-glass process that predates everyone else doing it — you've built something durable, and you don't need a tool to prove it.
+Final note.
+Thirty plus years and a recycled glass process that predates everyone else doing it. You have built something durable and you do not need a tool to prove it.
 The walkthrough offer stands if the special order flow ever needs help.
-Good luck with it.</t>
+Thanks for reading.</t>
         </is>
       </c>
     </row>
@@ -17518,9 +17466,9 @@
       <c r="L21" s="5" t="inlineStr">
         <is>
           <t>Susanne,
-Your InLine Design Cards are a genuinely good idea — physical cards so someone can experiment and let serendipity do its work.
-They also require shipping, handling, and a customer patient enough to play. Plenty of people who'd have bought after experimenting never start.
-We built the AI studio MEC Artworks runs. Same experimentation, on screen: describe a direction, get an original concept, see it on a photo of the actual room.
+Your InLine Design Cards are a genuinely good idea. Physical cards so someone can experiment and let serendipity do its work.
+They also need shipping, handling, and a customer patient enough to play. Plenty of people who would have bought after experimenting never get as far as starting.
+We made the AI studio MEC Artworks runs on their site. Same experimenting, on screen. Describe a direction, get an original concept, see it on a photo of the real room.
 Worth showing you the parallel?</t>
         </is>
       </c>
@@ -17532,10 +17480,9 @@
       <c r="N21" s="5" t="inlineStr">
         <is>
           <t>Susanne,
-The commercial version: customers who experiment buy more confidently and specify bigger. Your cards prove you already believe that — this just removes the postage and the wait.
-Describe it, see it on the wall, adjust, decide.
-ai.mecartworks.com — five previews, free, email code only.
-Two minutes will tell you whether it belongs next to the cards or nowhere near them.</t>
+What it is worth to you. Customers who experiment buy with more confidence and specify larger areas. Your cards prove you already believe that, or you would not have made them.
+This removes the postage and the wait. Describe it, see it on the wall, adjust, decide, all in one sitting while they are still interested.
+Find it at ai.mecartworks.com. An email code gets you five previews. Two minutes will tell you whether it belongs next to the cards or nowhere near them.</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -17546,10 +17493,10 @@
       <c r="P21" s="5" t="inlineStr">
         <is>
           <t>Susanne,
-I'll stop here.
-If the cards are converting the way you hoped, that's a better result than most digital tools produce and I'd leave well alone.
-ai.mecartworks.com if the digital version is ever interesting.
-Either way, the Cedar &amp; Moss collaboration is lovely work.</t>
+I will stop chasing this.
+If the cards are converting the way you hoped, that is a better result than most digital tools manage and I would leave well alone.
+ai.mecartworks.com if a digital version is ever interesting.
+The Cedar and Moss collaboration is lovely work.</t>
         </is>
       </c>
     </row>
@@ -17608,24 +17555,23 @@
       <c r="L22" s="5" t="inlineStr">
         <is>
           <t>Andrea,
-Sicis runs a design service for architects — soluzioni su misura across mosaic, glass and interiors.
-An architect specifying that has to sell it onward to their own client, usually from a sample and a portfolio of someone else's project. Work like Paradis Latin or the Benetti yacht is hard to translate into a different room.
-We built the AI studio MEC Artworks runs — same industry. It renders a described design onto a photo of the actual space.
+Sicis runs a design service for architects, soluzioni su misura across mosaic, glass and interiors.
+An architect specifying that has to sell it onward to their own client, usually from a sample and a portfolio of a different project. Work like Paradis Latin or the Benetti yacht is beautiful and almost impossible to translate into someone else's room.
+We built the AI studio that MEC Artworks runs, same industry. It renders a described design onto a photo of the actual space.
 Worth walking you through?</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>an image that works as a proposal and as content</t>
+          <t>one image that works as a proposal and as content</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
           <t>Andrea,
-For your side of the business specifically: this makes shareable content as easily as it makes proposals.
-Someone describes a space, sees a Sicis-style treatment placed in it, and that image is both a sales asset and a social one.
-Fifteen minutes on a screen share and you'd see whether the output is up to the brand.
-Want me to send a couple of times?</t>
+For your side of the business specifically. The output is shareable, not just usable.
+Someone describes a space, sees a Sicis style treatment placed in it, and that single image is a sales asset and a social asset at the same time. You currently need a finished project to get an image like that, which means waiting months to post about work you sold last year.
+Fifteen minutes on a screen share and you would see whether the quality is up to the brand.</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
@@ -17636,10 +17582,10 @@
       <c r="P22" s="5" t="inlineStr">
         <is>
           <t>Andrea,
-I'll leave it here.
-Sicis has a stronger visual archive than almost anyone in this category, so you may simply not need generated imagery.
-If it's ever useful, the walkthrough offer stands.
-Either way, the Flora Springs project is a great piece of work.</t>
+I will leave it there.
+Sicis has a stronger visual archive than nearly anyone in this category, so you may simply not need generated images. That is a reasonable answer.
+If it is ever useful, the walkthrough offer stands.
+The Flora Springs project is a great piece of work.</t>
         </is>
       </c>
     </row>
@@ -17699,38 +17645,37 @@
       <c r="L23" s="5" t="inlineStr">
         <is>
           <t>Bardia,
-Kimia's line about no two tiles being exactly alike — subtle variation in colour and texture — is the honest way to sell handmade tile.
-It's also the hardest thing to sell from a sample. One tile shows the variation; it doesn't show what a whole wall of it looks like, and the wall is what the client is actually buying.
-We built the AI studio MEC Artworks runs. Someone describes the space and sees the treatment across a photo of the real wall.
-Worth two minutes?</t>
+Kimia's line about no two tiles being exactly alike, with subtle variation in colour and texture, is the honest way to sell handmade tile.
+It is also the hardest thing to sell from a sample. One tile shows the variation. It does not show what a whole wall of it looks like, and the wall is what the client is actually buying.
+MEC Artworks has one. We built it for them. Someone describes the space and sees the treatment across a photo of the real wall.
+Would you take a look?</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>character across a wall, inconsistency on a sample</t>
+          <t>character on a wall, inconsistency on a sample</t>
         </is>
       </c>
       <c r="N23" s="5" t="inlineStr">
         <is>
           <t>Bardia,
-The specific gap for handmade: variation reads as character across a wall and as inconsistency on a single sample.
-Showing the whole surface before the order is placed removes the objection you probably answer most often.
-ai.mecartworks.com — free, five previews, email code.
-Two minutes and you'd know whether it renders the variation honestly.</t>
+The specific problem with handmade. Variation reads as character across a whole wall and as inconsistency on a single sample.
+Showing the full surface before the order is placed removes the objection you probably answer more often than any other. It also protects you after delivery, because the client already knew what they were getting.
+ai.mecartworks.com, free to try, five previews, email code.</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>the sample-to-wall gap</t>
+          <t>the sample to wall gap</t>
         </is>
       </c>
       <c r="P23" s="5" t="inlineStr">
         <is>
           <t>Bardia,
-Last note from me.
-Building a tile company in the UAE market means you're closer to how your clients decide than I could be from here.
-ai.mecartworks.com if the sample-to-wall gap is ever a problem.
-Good luck with the growth.</t>
+Last word from me.
+Building a tile company in the UAE market means you are closer to how your clients decide than I could be from here.
+ai.mecartworks.com if the sample to wall gap is ever a problem.
+Best of luck with the growth.</t>
         </is>
       </c>
     </row>
@@ -17789,9 +17734,9 @@
       <c r="L24" s="5" t="inlineStr">
         <is>
           <t>Paolo,
-Bisazza already runs a space configurator and a free Design Studio consultation for custom mosaic work — further along than most of this industry.
-The consultation is the interesting part. It's staffed, it's free, and it exists because the app configures existing products rather than generating new ones.
-We built the AI studio MEC Artworks runs. It takes a plain-words brief and returns an original design, placed on a photo of the real space.
+Bisazza already runs a space configurator and a free Design Studio consultation for custom mosaic work. That is further along than most of this industry.
+The consultation is the interesting bit. It is staffed, it is free, and it exists because the app configures existing products rather than creating new ones. Every custom idea still lands on a person.
+We put together the AI studio MEC Artworks runs. It takes a plain description and returns an original design, placed on a photo of the real space.
 Worth a look as a front end to the Design Studio?</t>
         </is>
       </c>
@@ -17803,24 +17748,23 @@
       <c r="N24" s="5" t="inlineStr">
         <is>
           <t>Paolo,
-Framing it for your side: the app handles configuration, the studio handles creation, and the gap between them is human hours.
-Someone types "Novembre-scale geometry, warm metallics" and gets an original concept placed in the room. The consultation then starts from something instead of nothing.
-I'd rather show you than send a link — 15 minutes on a screen share.
-Want a couple of times?</t>
+Framing it for your side. The app handles configuration. The studio handles creation. The gap between them is paid human time, and it scales linearly with demand.
+Someone types "Novembre scale geometry, warm metallics" and gets an original concept placed in the room. The consultation then starts from something instead of from nothing, which shortens it.
+I would rather show you than send a link. Fifteen minutes on a screen share. Want a couple of times?</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>have you looked at generative tooling already?</t>
+          <t>have you looked at generated design already?</t>
         </is>
       </c>
       <c r="P24" s="5" t="inlineStr">
         <is>
           <t>Paolo,
 Closing this off.
-At Bisazza's scale you'll have looked at generative tooling already, and possibly built some. If so, I'd genuinely like to know what you concluded.
-The walkthrough offer stands either way.
-Good luck with the season.</t>
+At Bisazza's scale you have almost certainly looked at this kind of tooling already, and possibly built some. If so, I would rather hear what you concluded than pitch you.
+The walkthrough offer stands.
+Thanks for the time.</t>
         </is>
       </c>
     </row>
@@ -17879,24 +17823,23 @@
       <c r="L25" s="5" t="inlineStr">
         <is>
           <t>Samantha,
-Fireclay's Mosaic Visualizer is one of the few real ones in this industry — most tile brands still ship a photo gallery and call it a tool.
-It visualises patterns you've already designed, though. The customer who wants something that isn't in the system still ends up in a custom enquiry queue.
-We built the AI studio MEC Artworks runs: describe a design in plain words, get an original back, see it on a photo of the actual room.
+Fireclay's Mosaic Visualizer is one of the few real ones in this industry. Most tile brands still ship a photo gallery and call it a tool.
+It visualises patterns you have already designed though. The customer who wants something that is not in the system still ends up in a custom request queue, waiting on a person.
+The AI studio MEC Artworks runs is ours. Describe a design in plain words, get an original back, see it on a photo of the actual room.
 Would it be useful to see how it sits in front of the Visualizer?</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>the Foundry launch and the 'like that, but…' requests</t>
+          <t>the Foundry launch and the like that but requests</t>
         </is>
       </c>
       <c r="N25" s="5" t="inlineStr">
         <is>
           <t>Samantha,
-The Foundry Collection is a good example of the gap. A launch creates demand for a look, and the requests that follow are always "like that, but…".
-This handles the "but" — original concept from a description, placed in the customer's own space, before it reaches your custom team.
-ai.mecartworks.com, five free previews, email code.
-Two minutes will tell you whether the output clears Fireclay's bar.</t>
+The Foundry Collection is a good example of the gap. A launch creates demand for a look, and the requests that follow are always "like that, but".
+This handles the "but". Original concept from a description, placed in the customer's own space, before it reaches your custom team. The requests that do reach them are then real ones.
+It is at ai.mecartworks.com. Five previews, no cost, code by email. You would know inside two minutes whether the output clears Fireclay's bar.</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
@@ -17907,10 +17850,10 @@
       <c r="P25" s="5" t="inlineStr">
         <is>
           <t>Samantha,
-I'll stop here.
-You've already built visualisation tooling in-house, so you know the cost and the payoff better than I can argue it.
-If the generative step is ever on the roadmap, ai.mecartworks.com is a working reference.
-Either way, the Foundry launch looks great.</t>
+This is my last email on it.
+You have already built visualisation tooling in house, so you know the cost and the payoff better than I can argue it.
+If the design generation step ever lands on the roadmap, ai.mecartworks.com is a working reference.
+The Foundry launch looks great.</t>
         </is>
       </c>
     </row>
@@ -17969,9 +17912,9 @@
       <c r="L26" s="5" t="inlineStr">
         <is>
           <t>Giulia,
-Real Wall and Live Room put Instabilelab ahead of most of this industry — most wallcovering brands still ship a static gallery.
-Both configurators start from your existing collections, though. The visitor who wants something that isn't in them has no path, and a laboratorio di sperimentazione is exactly the brand that customer came looking for.
-We built the AI studio MEC Artworks runs. It generates the design first, described in words, then places it in the room.
+Real Wall and Live Room put Instabilelab ahead of most of this industry. Plenty of wallcovering brands still ship a static gallery and call it a tool.
+Both start from your existing collections though. A visitor who wants something that is not in them has nowhere to go, and a laboratorio di sperimentazione is exactly the brand that customer came looking for.
+We built the AI mosaic studio MEC Artworks uses. It creates the design first, from words, then places it in the room.
 Would it be useful to see how it sits in front of Real Wall?</t>
         </is>
       </c>
@@ -17983,24 +17926,23 @@
       <c r="N26" s="5" t="inlineStr">
         <is>
           <t>Giulia,
-To be concrete: someone types "ochre, oversized botanical, matte" and gets an original design, then sees it on their wall. Your configurators handle everything after that.
-For Instabilelab it's a first step, not a replacement — it feeds Real Wall the customers who currently leave.
-ai.mecartworks.com — five previews, email code, no subscription.
-Two minutes will tell you whether the output is up to your standard.</t>
+To be concrete. Someone types "ochre, oversized botanical, matte" and gets an original design, then sees it on their wall. Your configurators handle everything after that.
+The value for you is not a new tool. It is more traffic reaching the tools you already paid to build. Right now the customer without a collection in mind never gets as far as Real Wall.
+You will find it at ai.mecartworks.com. Five previews, no cost.</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>you've built configurators — what did you learn?</t>
+          <t>you built configurators. what did you learn?</t>
         </is>
       </c>
       <c r="P26" s="5" t="inlineStr">
         <is>
           <t>Giulia,
-I'll leave it here.
-You've already invested in configurators, so you know what they cost and what they return better than I do. If the gap I'm describing isn't real for you, that's genuinely useful to hear.
+Final email from me.
+You have already invested in configurators, so you know better than I do what they cost and what they return. If the gap I am describing is not real for you, that is genuinely worth hearing.
 ai.mecartworks.com if it ever is.
-Either way, the Hotel Feldhof project is a good showcase.</t>
+The Hotel Feldhof project is a good showcase.</t>
         </is>
       </c>
     </row>
@@ -18063,10 +18005,10 @@
       <c r="L27" s="5" t="inlineStr">
         <is>
           <t>Connie,
-Seneca brought back the Handmold Mini Panels by popular demand — which tells me your specifiers respond to seeing the real thing in front of them.
-That's the whole difficulty with tile: panels and samples travel slowly, and the architect's client is usually the one who needs convincing.
-We built the AI studio MEC Artworks runs. It puts a described design onto a photo of the actual space, in seconds.
-I couldn't tell from your site how much custom work Seneca takes on — worth a short conversation?</t>
+Seneca brought the Handmold Mini Panels back by popular demand. That tells me your specifiers respond to seeing the real thing in front of them, which is worth knowing about your own market.
+It is also the difficulty with tile. Panels and samples travel slowly, and the architect's client is usually the person who needs convincing, sitting one step further away from the sample.
+MEC Artworks uses an AI studio we built for them. It puts a described design onto a photo of the actual space in seconds.
+I could not tell from your site how much custom work Seneca takes on. Open to a short call?</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
@@ -18077,10 +18019,10 @@
       <c r="N27" s="5" t="inlineStr">
         <is>
           <t>Connie,
-Being honest about why I'm asking: your site is clear on collections but not on how far you'll go on a custom request.
-If the answer is "quite far", this is relevant — it shortens the distance between an enquiry and an approved design.
-If the answer is "we're a manufacturer, not a design studio", tell me and I'll stop.
-Either way, ai.mecartworks.com shows what I mean in two minutes.</t>
+Being honest about why I am asking. Your site is clear on collections and quiet on how far you will go on a custom request.
+If the answer is "quite far", this is relevant, because it shortens the distance between a request and an approved design.
+If the answer is "we are a manufacturer, not a design studio", tell me and I will stop. That is useful to me and costs you one line.
+ai.mecartworks.com shows what I mean in two minutes.</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
@@ -18091,9 +18033,9 @@
       <c r="P27" s="5" t="inlineStr">
         <is>
           <t>Connie,
-Last note from me.
-A general manager's time is the wrong thing to spend on a cold email, so I'll leave it.
-If Seneca does take custom design work and it ever slows things down, ai.mecartworks.com is the example.
+One more and then I am done.
+A general manager's time is the wrong thing to spend on a cold email, so I will leave it.
+If Seneca does take on custom design work and it ever slows things down, the example is at ai.mecartworks.com.
 Good luck with the Mini Panels run.</t>
         </is>
       </c>
@@ -18153,9 +18095,9 @@
       <c r="L28" s="5" t="inlineStr">
         <is>
           <t>Jamie,
-Zia's line — designed in Los Angeles, crafted by artisans around the globe — is a curated position rather than a made-to-order one, and the filters on the site reflect that.
-Which makes the customer's job harder in one specific way: zellige varies, and a swatch photo doesn't tell you what a whole wall of it looks like.
-We built the AI studio MEC Artworks runs. Someone describes their room and sees a treatment placed in a photo of it.
+Zia's line, designed in Los Angeles and crafted by artisans around the globe, is a curated position rather than a made to order one. The filters on the site reflect that and they work well.
+It makes the customer's job harder in one specific way though. Zellige varies, and a swatch photo does not tell you what a whole wall of it looks like. That uncertainty is where orders shrink.
+The AI studio MEC Artworks uses came from us. Someone describes their room and sees a treatment placed in a photo of it.
 Worth two minutes of a marketing director's time?</t>
         </is>
       </c>
@@ -18167,10 +18109,9 @@
       <c r="N28" s="5" t="inlineStr">
         <is>
           <t>Jamie,
-To be clear, I'm not suggesting Zia move into custom — the curated position is the brand.
-This sits before the filters: someone who knows the room but not the collection sees a direction, then lands on the product that matches. Discovery, not a design service.
-ai.mecartworks.com — free, five previews.
-Two minutes and you'd know if it's on-brand.</t>
+To be clear, I am not suggesting Zia moves into custom. The curated position is the brand and it is working.
+This sits before the filters. Someone who knows their room but not the collection sees a direction first, then lands on the product that matches. It is a discovery tool, not a design service, and it feeds the catalogue you already have.
+ai.mecartworks.com, five previews, email code, no subscription.</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
@@ -18181,10 +18122,10 @@
       <c r="P28" s="5" t="inlineStr">
         <is>
           <t>Jamie,
-Last note.
-If site search and the collection filters already do this job, then I've misread it and I'd rather know.
-ai.mecartworks.com if discovery is ever the drop-off point.
-Either way, good luck with the season.</t>
+One last note.
+If site search and the collection filters already do this job, then I have misread it and I would rather know.
+ai.mecartworks.com if discovery is ever where people drop off.
+Best of luck with the season.</t>
         </is>
       </c>
     </row>
@@ -18241,30 +18182,30 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>the commission your artists can't preview</t>
+          <t>the commission your artists cannot preview</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
           <t>James,
-FinerWorks is built around artists who already have the file — drag it in, live preview, COA on the way out. That's a clean pipeline.
-The gap is the commission. When a buyer asks an artist for "something like this, but for my dining room," there's nothing to drag in, and that conversation runs over email for weeks.
-We built the AI studio MEC Artworks runs, for exactly that stage: describe it, get an original concept, place it on a photo of the buyer's room.
+FinerWorks is built for the artist who already has the file. Drag it in, live preview, COA on the way out. That is a clean pipeline and it shows.
+The gap is the commission. When a buyer asks an artist for "something like this, but for my dining room", there is no file to drag in. That conversation then runs over email for weeks, and plenty of it dies there.
+We built the AI studio that MEC Artworks runs for exactly that stage. Describe it, get an original concept, place it on a photo of the buyer's room.
 Worth showing you?</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>a COA for a piece that doesn't exist yet</t>
+          <t>a COA for a piece that does not exist yet</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr">
         <is>
           <t>James,
-Concretely: the buyer types what they're after, gets an original concept, then sees it on their own wall before the artist starts.
-For FinerWorks that could sit ahead of the upload — the artist closes the commission faster, and the file that eventually gets dragged in is one the buyer already approved.
-ai.mecartworks.com — five previews, email code, no subscription.
-Curious what you'd make of the output quality.</t>
+The practical version. The buyer types what they want, gets an original concept, then sees it on their own wall before the artist starts painting.
+The part I think is useful for FinerWorks: it sits ahead of your upload, not against it. The artist closes the commission faster, and the file that eventually gets dragged in is one the buyer has already approved. Fewer reprints, fewer refunds.
+ai.mecartworks.com. One time code, five previews, free.
+I would value your read on the output quality.</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
@@ -18275,10 +18216,10 @@
       <c r="P29" s="5" t="inlineStr">
         <is>
           <t>James,
-Last one from me.
-You've clearly thought about the artist's workflow more than most print platforms have — the COA tool alone says that.
-If the commission stage ever comes up as something to solve, ai.mecartworks.com is the working example.
-Either way, good luck with it.</t>
+I will leave it here.
+You have thought about the artist's workflow more than most print platforms bother to. The COA tool on its own says that.
+If the commission stage ever becomes something you want to solve, the example is at ai.mecartworks.com.
+Thanks for reading this far.</t>
         </is>
       </c>
     </row>
@@ -18337,38 +18278,37 @@
       <c r="L30" s="5" t="inlineStr">
         <is>
           <t>Stacy,
-Your "GO CUSTOM!" flow is one of the better ones I've seen — upload, crop, resize, live pricing, done.
-It only helps the customer who already has the image. The ones who know they want "something botanical, muted, for a north-facing room" have nothing to drop in the box, so they leave.
-We built the AI studio MEC Artworks runs. That customer describes it in words, gets an original design back, then sees it on a photo of their own wall.
-Want me to send you a walkthrough?</t>
+Your GO CUSTOM flow is better than most. Upload, crop, resize, live pricing, done.
+It only works for someone who already has the image. A customer who knows they want something botanical and muted for a north facing room has nothing to put in the box, so they close the tab. That visitor had money and intent. You just had no way to serve them.
+We built the AI studio that MEC Artworks runs. That same customer types what they want, gets an original design back, then sees it on a photo of their own wall.
+Want me to send you a short walkthrough?</t>
         </is>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>when there's nothing in the box</t>
+          <t>when there is nothing to put in the box</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
           <t>Stacy,
-The specific bit: someone types "brushed sage, large-scale botanical, low contrast" and gets an original mural concept — not a stock search result. Then they upload the room and see it hung.
-For Limitless that's the top of the funnel your crop tool can't reach: the visitor with an idea and no file.
-It's live at ai.mecartworks.com — email code, five previews, no subscription.
-Two minutes tells you if it fits.</t>
+Here is the part that matters for you. Someone types "brushed sage, large botanical, low contrast" and gets an original design. Not a stock search result. Then they upload their room and see it hanging there.
+One thing you can check today without me: pull your search log for the last month and count the queries that returned nothing. That number is the size of this gap, and it costs you nothing to find out.
+The tool is at ai.mecartworks.com. ai.mecartworks.com, five previews free, email verification only.</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>how do you convert the no-image visitor?</t>
+          <t>how do you convert the no image visitor?</t>
         </is>
       </c>
       <c r="P30" s="5" t="inlineStr">
         <is>
           <t>Stacy,
-Last note from me.
-If you're already converting the no-image visitor some other way, I'd genuinely like to hear how — that's the hard half of custom.
-If not, ai.mecartworks.com is the working example.
-Either way, your custom flow is better than most of what's out there.</t>
+I will stop emailing after this one.
+If you already have a way to convert the visitor who arrives without an image, I would honestly like to hear it. That is the hard half of selling custom, and most people in your category have not solved it.
+If you do not, the example is at ai.mecartworks.com.
+Your custom flow is still one of the better ones I have looked at this month.</t>
         </is>
       </c>
     </row>
@@ -18425,15 +18365,15 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>the step before the 48-inch panels</t>
+          <t>the step before the 48 inch panels</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
           <t>Tim,
-MegaPrint prints removable custom wallpaper on 48-inch panels, two to three week turnaround, and the customer supplies the artwork.
-That last part is the filter. A business that knows it wants a branded wall but has no file and no designer never reaches your order form.
-We built the AI studio MEC Artworks runs. It closes that gap: describe the design in plain words, get an original concept, see it on a photo of the actual space.
+MegaPrint prints removable custom wallpaper on 48 inch panels, two to three weeks, and the customer supplies the artwork.
+That last part quietly filters your market. A business that wants a branded wall but has no file and no designer never reaches your order form. They are not price shopping. They are stuck one step earlier.
+We built MEC Artworks' AI studio. It closes that step. Describe the design in plain words, get an original concept back, then see it on a photo of the real space.
 Want me to run your own lobby through it and send you the result?</t>
         </is>
       </c>
@@ -18445,10 +18385,10 @@
       <c r="N31" s="5" t="inlineStr">
         <is>
           <t>Tim,
-The specific: it isn't stock search. Someone types "industrial, muted teal, hop vines" and gets an original design, then drops it into a photo of their space.
-For MegaPrint that's the customer who currently never arrives — the one with an idea and no artwork.
-ai.mecartworks.com, five free previews, email code only.
-If the output isn't print-grade for your panels, you'll know fast.</t>
+To be clear about what it does, since "AI design" means very little on its own.
+It is not stock search. Someone types "industrial, muted teal, hop vines" and gets an original design, then drops it into a photo of their space.
+Worth knowing either way: the businesses that ask you for design help are usually your best margin jobs, because they are buying a result and not comparing print prices. Right now you have to turn them away or hand them to a designer.
+ai.mecartworks.com. Email code, five previews, nothing to cancel.</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
@@ -18459,10 +18399,10 @@
       <c r="P31" s="5" t="inlineStr">
         <is>
           <t>Tim,
-I'll leave it here.
-If most orders arrive with artwork already sorted, this solves a problem you don't have — and that's a good position to be in.
-If you ever want the other half of that market, ai.mecartworks.com is the example.
-Good luck either way.</t>
+Last one from me.
+If most of your orders already arrive with artwork sorted, this fixes something you do not have. That is a good place to be and I would rather you tell me than keep reading.
+If you ever want the other half of that market, the working example is at ai.mecartworks.com.
+Thanks for the time.</t>
         </is>
       </c>
     </row>
@@ -18515,16 +18455,16 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>your simulator, for designs that don't exist yet</t>
+          <t>your simulator, for designs that do not exist yet</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
           <t>Jennifer,
-Photowall's "Try Before You Buy" simulator already does the hard half — the customer sees the design on their own wall before buying.
-What it can't do is invent the design. If someone wants "muted botanical, wide format, north-facing room" and nothing in the catalogue matches, the simulator has nothing to show them.
-We built the AI studio MEC Artworks runs. It generates the design from that sentence, then places it in the room.
-Want to see how the two stages fit together?</t>
+Photowall's Try Before You Buy simulator already does the hard half. The customer sees the design on their own wall before they buy.
+What it cannot do is invent the design. If someone wants "muted botanical, wide format, north facing room" and nothing in the catalogue is close, the simulator has nothing to show them and they leave.
+My team built the AI studio MEC Artworks uses. It creates the design from that sentence, then places it in the room.
+Want to see how the two steps fit together?</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
@@ -18535,24 +18475,23 @@
       <c r="N32" s="5" t="inlineStr">
         <is>
           <t>Jennifer,
-The specific: someone describes the design in ordinary words, gets an original back, then previews it in their own room — same last step as yours, different first step.
-For Photowall that's the visitor who searches, finds nothing close, and leaves. Right now the simulator never gets a chance with them.
-ai.mecartworks.com — free, five previews, email code.
-Worth two minutes of a marketing afternoon.</t>
+The mechanic in one line. Someone describes the design in ordinary words, gets an original back, then previews it in their own room. Same last step as yours. Different first step.
+Something you can test without talking to me: check your on site search for queries with no results, or with results nobody clicked. Those are customers who wanted to buy and could not find it. In most catalogues that number is much larger than people expect.
+ai.mecartworks.com, email code, five previews, no card.</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>does 'no close match' show in your search data?</t>
+          <t>does no close match show in your search data?</t>
         </is>
       </c>
       <c r="P32" s="5" t="inlineStr">
         <is>
           <t>Jennifer,
-I'll stop here.
-If catalogue depth already covers most searches, this is a smaller problem than I think, and that's fair.
-If "no close match" ever shows up in your search data, ai.mecartworks.com is the example to look at.
-Thanks for reading.</t>
+Last note from me.
+If your catalogue depth already covers most searches, then this is a smaller problem than I think it is, and that is fair.
+If "no close match" does show up in your data, the example is at ai.mecartworks.com.
+Thanks for the time.</t>
         </is>
       </c>
     </row>

--- a/gtm/mec/MEC_Outreach_Ready.xlsx
+++ b/gtm/mec/MEC_Outreach_Ready.xlsx
@@ -10,11 +10,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outreach" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Send List" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Held &amp; Excluded" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contact Gaps" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Outreach'!$A$1:$AY$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Send List'!$A$1:$P$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Outreach'!$A$1:$BA$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Send List'!$A$1:$R$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Held &amp; Excluded'!$A$1:$J$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Contact Gaps'!$A$1:$L$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,11 +495,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:BA68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -516,7 +518,7 @@
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
     <col width="18" customWidth="1" min="22" max="22"/>
     <col width="18" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
@@ -524,11 +526,11 @@
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
     <col width="18" customWidth="1" min="28" max="28"/>
-    <col width="18" customWidth="1" min="29" max="29"/>
+    <col width="24" customWidth="1" min="29" max="29"/>
     <col width="24" customWidth="1" min="30" max="30"/>
     <col width="18" customWidth="1" min="31" max="31"/>
     <col width="18" customWidth="1" min="32" max="32"/>
-    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="34" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="20" customWidth="1" min="35" max="35"/>
     <col width="18" customWidth="1" min="36" max="36"/>
@@ -539,14 +541,16 @@
     <col width="18" customWidth="1" min="41" max="41"/>
     <col width="18" customWidth="1" min="42" max="42"/>
     <col width="18" customWidth="1" min="43" max="43"/>
-    <col width="15" customWidth="1" min="44" max="44"/>
-    <col width="44" customWidth="1" min="45" max="45"/>
-    <col width="30" customWidth="1" min="46" max="46"/>
-    <col width="68" customWidth="1" min="47" max="47"/>
+    <col width="16" customWidth="1" min="44" max="44"/>
+    <col width="46" customWidth="1" min="45" max="45"/>
+    <col width="15" customWidth="1" min="46" max="46"/>
+    <col width="44" customWidth="1" min="47" max="47"/>
     <col width="30" customWidth="1" min="48" max="48"/>
     <col width="68" customWidth="1" min="49" max="49"/>
     <col width="30" customWidth="1" min="50" max="50"/>
     <col width="68" customWidth="1" min="51" max="51"/>
+    <col width="30" customWidth="1" min="52" max="52"/>
+    <col width="68" customWidth="1" min="53" max="53"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -767,40 +771,50 @@
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
+          <t>contact_status</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>contact_note</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
           <t>send_status</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>send_note</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>email_1_subject</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>email_1_body</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>email_2_subject</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>email_2_body</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>email_3_subject</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>email_3_body</t>
         </is>
@@ -994,22 +1008,32 @@
           <t>CLIENT_PROOF: Not found — testimonials/business pages list industries not named brands — /testimonials</t>
         </is>
       </c>
-      <c r="AR2" s="3" t="inlineStr">
+      <c r="AR2" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="AS2" s="2" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+      <c r="AT2" s="3" t="inlineStr">
         <is>
           <t>NO EMAIL</t>
         </is>
       </c>
-      <c r="AS2" s="4" t="inlineStr">
+      <c r="AU2" s="4" t="inlineStr">
         <is>
           <t>No work email on this row — LinkedIn or enrichment needed</t>
         </is>
       </c>
-      <c r="AT2" s="4" t="inlineStr"/>
-      <c r="AU2" s="5" t="inlineStr"/>
       <c r="AV2" s="4" t="inlineStr"/>
       <c r="AW2" s="5" t="inlineStr"/>
       <c r="AX2" s="4" t="inlineStr"/>
       <c r="AY2" s="5" t="inlineStr"/>
+      <c r="AZ2" s="4" t="inlineStr"/>
+      <c r="BA2" s="5" t="inlineStr"/>
     </row>
     <row r="3" ht="92" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -1199,22 +1223,32 @@
           <t>CLIENT_PROOF: Not found — only individual customer testimonials, no named brand/venue — /pages (customer photos)</t>
         </is>
       </c>
-      <c r="AR3" s="6" t="inlineStr">
+      <c r="AR3" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS3" s="2" t="inlineStr">
+        <is>
+          <t>found on SMB fallback</t>
+        </is>
+      </c>
+      <c r="AT3" s="6" t="inlineStr">
         <is>
           <t>HOLD - REVENUE</t>
         </is>
       </c>
-      <c r="AS3" s="4" t="inlineStr">
+      <c r="AU3" s="4" t="inlineStr">
         <is>
           <t>Revenue 500K-1M is below the $1M gate (S7.4) — verify before sending</t>
         </is>
       </c>
-      <c r="AT3" s="4" t="inlineStr">
+      <c r="AV3" s="4" t="inlineStr">
         <is>
           <t>Watercolor Forest, and the mural nobody made</t>
         </is>
       </c>
-      <c r="AU3" s="5" t="inlineStr">
+      <c r="AW3" s="5" t="inlineStr">
         <is>
           <t>Geoffrey,
 Eazywallz has the upload path solved. Crop tool, live strip preview, pricing as you go. Most of this industry still cannot do that.
@@ -1223,12 +1257,12 @@
 Want me to send you a walkthrough?</t>
         </is>
       </c>
-      <c r="AV3" s="4" t="inlineStr">
+      <c r="AX3" s="4" t="inlineStr">
         <is>
           <t>like that, but warmer</t>
         </is>
       </c>
-      <c r="AW3" s="5" t="inlineStr">
+      <c r="AY3" s="5" t="inlineStr">
         <is>
           <t>Geoffrey,
 The specific. Someone types "watercolour forest, warmer, less contrast, twelve feet wide" and gets an original design back, then previews it in their room.
@@ -1236,12 +1270,12 @@
 It is at ai.mecartworks.com. Five previews, free, email code only.</t>
         </is>
       </c>
-      <c r="AX3" s="4" t="inlineStr">
+      <c r="AZ3" s="4" t="inlineStr">
         <is>
           <t>you already built the hard half</t>
         </is>
       </c>
-      <c r="AY3" s="5" t="inlineStr">
+      <c r="BA3" s="5" t="inlineStr">
         <is>
           <t>Geoffrey,
 I will step back here.
@@ -1415,22 +1449,32 @@
           <t>CLIENT_PROOF: Avon Park Baseball Museum, Route 66 Museum, Rocha Art and Design — /inspiration/wall-mural-business-case-studies</t>
         </is>
       </c>
-      <c r="AR4" s="3" t="inlineStr">
+      <c r="AR4" s="2" t="inlineStr">
+        <is>
+          <t>NO CONTACT</t>
+        </is>
+      </c>
+      <c r="AS4" s="2" t="inlineStr">
+        <is>
+          <t>both people searches failed. Needs manual sourcing or LinkedIn</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
         <is>
           <t>NO EMAIL</t>
         </is>
       </c>
-      <c r="AS4" s="4" t="inlineStr">
+      <c r="AU4" s="4" t="inlineStr">
         <is>
           <t>No work email on this row — LinkedIn or enrichment needed</t>
         </is>
       </c>
-      <c r="AT4" s="4" t="inlineStr"/>
-      <c r="AU4" s="5" t="inlineStr"/>
       <c r="AV4" s="4" t="inlineStr"/>
       <c r="AW4" s="5" t="inlineStr"/>
       <c r="AX4" s="4" t="inlineStr"/>
       <c r="AY4" s="5" t="inlineStr"/>
+      <c r="AZ4" s="4" t="inlineStr"/>
+      <c r="BA4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -1588,22 +1632,32 @@
           <t>CLIENT_PROOF: Not found</t>
         </is>
       </c>
-      <c r="AR5" s="3" t="inlineStr">
+      <c r="AR5" s="2" t="inlineStr">
+        <is>
+          <t>NO CONTACT</t>
+        </is>
+      </c>
+      <c r="AS5" s="2" t="inlineStr">
+        <is>
+          <t>both people searches failed. Needs manual sourcing or LinkedIn</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
         <is>
           <t>NO EMAIL</t>
         </is>
       </c>
-      <c r="AS5" s="4" t="inlineStr">
+      <c r="AU5" s="4" t="inlineStr">
         <is>
           <t>No work email on this row — LinkedIn or enrichment needed</t>
         </is>
       </c>
-      <c r="AT5" s="4" t="inlineStr"/>
-      <c r="AU5" s="5" t="inlineStr"/>
       <c r="AV5" s="4" t="inlineStr"/>
       <c r="AW5" s="5" t="inlineStr"/>
       <c r="AX5" s="4" t="inlineStr"/>
       <c r="AY5" s="5" t="inlineStr"/>
+      <c r="AZ5" s="4" t="inlineStr"/>
+      <c r="BA5" s="5" t="inlineStr"/>
     </row>
     <row r="6" ht="92" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -1804,22 +1858,32 @@
           <t>CLIENT_PROOF: "RHG Architecture + Design" (NJ-based interior design studio) partnered for hotel lobby mural — /us/commercial-work/hotels</t>
         </is>
       </c>
-      <c r="AR6" s="6" t="inlineStr">
+      <c r="AR6" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS6" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT6" s="6" t="inlineStr">
         <is>
           <t>HOLD - REVENUE</t>
         </is>
       </c>
-      <c r="AS6" s="4" t="inlineStr">
+      <c r="AU6" s="4" t="inlineStr">
         <is>
           <t>Revenue 0-500K is below the $1M gate (S7.4) — verify before sending</t>
         </is>
       </c>
-      <c r="AT6" s="4" t="inlineStr">
+      <c r="AV6" s="4" t="inlineStr">
         <is>
           <t>Try Before You Buy, without the email round trip</t>
         </is>
       </c>
-      <c r="AU6" s="5" t="inlineStr">
+      <c r="AW6" s="5" t="inlineStr">
         <is>
           <t>Tony,
 Wallsauce offers a free wall preview. The customer emails a product code and a photo, and someone sends back a visual.
@@ -1828,12 +1892,12 @@
 Want me to show you where it would fit?</t>
         </is>
       </c>
-      <c r="AV6" s="4" t="inlineStr">
+      <c r="AX6" s="4" t="inlineStr">
         <is>
           <t>the same service, without the person</t>
         </is>
       </c>
-      <c r="AW6" s="5" t="inlineStr">
+      <c r="AY6" s="5" t="inlineStr">
         <is>
           <t>Tony,
 The difference, plainly. Your preview service needs a product code, so the customer has already chosen. This starts one step earlier. They describe what they want, get an original design, then see it on their wall.
@@ -1841,12 +1905,12 @@
 ai.mecartworks.com gives you five previews for an email code.</t>
         </is>
       </c>
-      <c r="AX6" s="4" t="inlineStr">
+      <c r="AZ6" s="4" t="inlineStr">
         <is>
           <t>you clearly already believe in previews</t>
         </is>
       </c>
-      <c r="AY6" s="5" t="inlineStr">
+      <c r="BA6" s="5" t="inlineStr">
         <is>
           <t>Tony,
 Final message on this.
@@ -2056,22 +2120,32 @@
           <t>CLIENT_PROOF: Not found — no named third-party brands/projects on /pages/designers-and-trade</t>
         </is>
       </c>
-      <c r="AR7" s="7" t="inlineStr">
+      <c r="AR7" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS7" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT7" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS7" s="4" t="inlineStr">
+      <c r="AU7" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT7" s="4" t="inlineStr">
+      <c r="AV7" s="4" t="inlineStr">
         <is>
           <t>the customer who has nothing to upload</t>
         </is>
       </c>
-      <c r="AU7" s="5" t="inlineStr">
+      <c r="AW7" s="5" t="inlineStr">
         <is>
           <t>Stacy,
 Your GO CUSTOM flow is better than most. Upload, crop, resize, live pricing, done.
@@ -2080,25 +2154,25 @@
 Want me to send you a short walkthrough?</t>
         </is>
       </c>
-      <c r="AV7" s="4" t="inlineStr">
+      <c r="AX7" s="4" t="inlineStr">
         <is>
           <t>when there is nothing to put in the box</t>
         </is>
       </c>
-      <c r="AW7" s="5" t="inlineStr">
+      <c r="AY7" s="5" t="inlineStr">
         <is>
           <t>Stacy,
 Here is the part that matters for you. Someone types "brushed sage, large botanical, low contrast" and gets an original design. Not a stock search result. Then they upload their room and see it hanging there.
 One thing you can check today without me: pull your search log for the last month and count the queries that returned nothing. That number is the size of this gap, and it costs you nothing to find out.
-The tool is at ai.mecartworks.com. ai.mecartworks.com, five previews free, email verification only.</t>
-        </is>
-      </c>
-      <c r="AX7" s="4" t="inlineStr">
+The tool is at ai.mecartworks.com. Five previews free, email verification only.</t>
+        </is>
+      </c>
+      <c r="AZ7" s="4" t="inlineStr">
         <is>
           <t>how do you convert the no image visitor?</t>
         </is>
       </c>
-      <c r="AY7" s="5" t="inlineStr">
+      <c r="BA7" s="5" t="inlineStr">
         <is>
           <t>Stacy,
 I will stop emailing after this one.
@@ -2297,22 +2371,32 @@
           <t>CLIENT_PROOF: Barth-Haas Group and Portable Air Group named in testimonials — /removable_wallpaper.php</t>
         </is>
       </c>
-      <c r="AR8" s="7" t="inlineStr">
+      <c r="AR8" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS8" s="2" t="inlineStr">
+        <is>
+          <t>found on SMB fallback</t>
+        </is>
+      </c>
+      <c r="AT8" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS8" s="4" t="inlineStr">
+      <c r="AU8" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT8" s="4" t="inlineStr">
+      <c r="AV8" s="4" t="inlineStr">
         <is>
           <t>the step before the 48 inch panels</t>
         </is>
       </c>
-      <c r="AU8" s="5" t="inlineStr">
+      <c r="AW8" s="5" t="inlineStr">
         <is>
           <t>Tim,
 MegaPrint prints removable custom wallpaper on 48 inch panels, two to three weeks, and the customer supplies the artwork.
@@ -2321,12 +2405,12 @@
 Want me to run your own lobby through it and send you the result?</t>
         </is>
       </c>
-      <c r="AV8" s="4" t="inlineStr">
+      <c r="AX8" s="4" t="inlineStr">
         <is>
           <t>before the artwork file exists</t>
         </is>
       </c>
-      <c r="AW8" s="5" t="inlineStr">
+      <c r="AY8" s="5" t="inlineStr">
         <is>
           <t>Tim,
 To be clear about what it does, since "AI design" means very little on its own.
@@ -2335,12 +2419,12 @@
 ai.mecartworks.com. Email code, five previews, nothing to cancel.</t>
         </is>
       </c>
-      <c r="AX8" s="4" t="inlineStr">
+      <c r="AZ8" s="4" t="inlineStr">
         <is>
           <t>parking this with you</t>
         </is>
       </c>
-      <c r="AY8" s="5" t="inlineStr">
+      <c r="BA8" s="5" t="inlineStr">
         <is>
           <t>Tim,
 Last one from me.
@@ -2541,22 +2625,32 @@
           <t>CLIENT_PROOF: Not found — no named third-party brand/venue/project identified on site</t>
         </is>
       </c>
-      <c r="AR9" s="7" t="inlineStr">
+      <c r="AR9" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS9" s="2" t="inlineStr">
+        <is>
+          <t>found on SMB fallback</t>
+        </is>
+      </c>
+      <c r="AT9" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS9" s="4" t="inlineStr">
+      <c r="AU9" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT9" s="4" t="inlineStr">
+      <c r="AV9" s="4" t="inlineStr">
         <is>
           <t>the commission your artists cannot preview</t>
         </is>
       </c>
-      <c r="AU9" s="5" t="inlineStr">
+      <c r="AW9" s="5" t="inlineStr">
         <is>
           <t>James,
 FinerWorks is built for the artist who already has the file. Drag it in, live preview, COA on the way out. That is a clean pipeline and it shows.
@@ -2565,12 +2659,12 @@
 Worth showing you?</t>
         </is>
       </c>
-      <c r="AV9" s="4" t="inlineStr">
+      <c r="AX9" s="4" t="inlineStr">
         <is>
           <t>a COA for a piece that does not exist yet</t>
         </is>
       </c>
-      <c r="AW9" s="5" t="inlineStr">
+      <c r="AY9" s="5" t="inlineStr">
         <is>
           <t>James,
 The practical version. The buyer types what they want, gets an original concept, then sees it on their own wall before the artist starts painting.
@@ -2579,12 +2673,12 @@
 I would value your read on the output quality.</t>
         </is>
       </c>
-      <c r="AX9" s="4" t="inlineStr">
+      <c r="AZ9" s="4" t="inlineStr">
         <is>
           <t>one for the roadmap</t>
         </is>
       </c>
-      <c r="AY9" s="5" t="inlineStr">
+      <c r="BA9" s="5" t="inlineStr">
         <is>
           <t>James,
 I will leave it here.
@@ -2795,22 +2889,32 @@
           <t>CLIENT_PROOF: Not found — "Photowall for Business" page mentions offices/restaurants/hotels generically, no named brand — /us/customer-service/wallpaper-for-companies</t>
         </is>
       </c>
-      <c r="AR10" s="7" t="inlineStr">
+      <c r="AR10" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS10" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT10" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS10" s="4" t="inlineStr">
+      <c r="AU10" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT10" s="4" t="inlineStr">
+      <c r="AV10" s="4" t="inlineStr">
         <is>
           <t>your simulator, for designs that do not exist yet</t>
         </is>
       </c>
-      <c r="AU10" s="5" t="inlineStr">
+      <c r="AW10" s="5" t="inlineStr">
         <is>
           <t>Jennifer,
 Photowall's Try Before You Buy simulator already does the hard half. The customer sees the design on their own wall before they buy.
@@ -2819,12 +2923,12 @@
 Want to see how the two steps fit together?</t>
         </is>
       </c>
-      <c r="AV10" s="4" t="inlineStr">
+      <c r="AX10" s="4" t="inlineStr">
         <is>
           <t>thousands of designs, still no match</t>
         </is>
       </c>
-      <c r="AW10" s="5" t="inlineStr">
+      <c r="AY10" s="5" t="inlineStr">
         <is>
           <t>Jennifer,
 The mechanic in one line. Someone describes the design in ordinary words, gets an original back, then previews it in their own room. Same last step as yours. Different first step.
@@ -2832,12 +2936,12 @@
 ai.mecartworks.com, email code, five previews, no card.</t>
         </is>
       </c>
-      <c r="AX10" s="4" t="inlineStr">
+      <c r="AZ10" s="4" t="inlineStr">
         <is>
           <t>does no close match show in your search data?</t>
         </is>
       </c>
-      <c r="AY10" s="5" t="inlineStr">
+      <c r="BA10" s="5" t="inlineStr">
         <is>
           <t>Jennifer,
 Last note from me.
@@ -3026,22 +3130,32 @@
           <t>CLIENT_PROOF: Not found</t>
         </is>
       </c>
-      <c r="AR11" s="3" t="inlineStr">
+      <c r="AR11" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="AS11" s="2" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
         <is>
           <t>NO EMAIL</t>
         </is>
       </c>
-      <c r="AS11" s="4" t="inlineStr">
+      <c r="AU11" s="4" t="inlineStr">
         <is>
           <t>No work email on this row — LinkedIn or enrichment needed</t>
         </is>
       </c>
-      <c r="AT11" s="4" t="inlineStr"/>
-      <c r="AU11" s="5" t="inlineStr"/>
       <c r="AV11" s="4" t="inlineStr"/>
       <c r="AW11" s="5" t="inlineStr"/>
       <c r="AX11" s="4" t="inlineStr"/>
       <c r="AY11" s="5" t="inlineStr"/>
+      <c r="AZ11" s="4" t="inlineStr"/>
+      <c r="BA11" s="5" t="inlineStr"/>
     </row>
     <row r="12" ht="92" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -3236,22 +3350,32 @@
           <t>CLIENT_PROOF: Not found</t>
         </is>
       </c>
-      <c r="AR12" s="7" t="inlineStr">
+      <c r="AR12" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS12" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT12" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS12" s="4" t="inlineStr">
+      <c r="AU12" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT12" s="4" t="inlineStr">
+      <c r="AV12" s="4" t="inlineStr">
         <is>
           <t>your private label partners, and their customers</t>
         </is>
       </c>
-      <c r="AU12" s="5" t="inlineStr">
+      <c r="AW12" s="5" t="inlineStr">
         <is>
           <t>Ivars,
 Fancy Walls already sells its capability onward. Private label, dropship, one to two day turnaround. That is a harder business to build than a shop.
@@ -3260,12 +3384,12 @@
 Want me to show you where it would sit inside a private label flow?</t>
         </is>
       </c>
-      <c r="AV12" s="4" t="inlineStr">
+      <c r="AX12" s="4" t="inlineStr">
         <is>
           <t>two days to print, three weeks to decide</t>
         </is>
       </c>
-      <c r="AW12" s="5" t="inlineStr">
+      <c r="AY12" s="5" t="inlineStr">
         <is>
           <t>Ivars,
 More concrete. A shopper types what they want, gets an original design back, and sees it on a photo of their room. No drawing, no designer, no brief.
@@ -3273,12 +3397,12 @@
 ai.mecartworks.com, five free previews, email code.</t>
         </is>
       </c>
-      <c r="AX12" s="4" t="inlineStr">
+      <c r="AZ12" s="4" t="inlineStr">
         <is>
           <t>is choosing really the slow part?</t>
         </is>
       </c>
-      <c r="AY12" s="5" t="inlineStr">
+      <c r="BA12" s="5" t="inlineStr">
         <is>
           <t>Ivars,
 I will stop here.
@@ -3447,48 +3571,62 @@
         </is>
       </c>
       <c r="AK13" s="2" t="inlineStr"/>
-      <c r="AL13" s="2" t="inlineStr"/>
+      <c r="AL13" s="2" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
       <c r="AM13" s="2" t="inlineStr">
         <is>
-          <t>SITE_MATCH: Match — contemporary wallpaper customization specialist</t>
+          <t>SITE_MATCH: Match — brand, wallcoverings/wallpaper products align with company</t>
         </is>
       </c>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>CUSTOM_OFFERING: Yes — "customizing colors and sizes to crafting entirely new patterns" — /en-us/bespoke/</t>
+          <t>CUSTOM_OFFERING: Yes — bespoke custom patterns, colors, sizes offered (/en-us/bespoke)</t>
         </is>
       </c>
       <c r="AO13" s="2" t="inlineStr">
         <is>
-          <t>VISUAL_TOOL: Basic — "Search by RAL® color" colour picker interface — /en-us/</t>
+          <t>VISUAL_TOOL: Basic — search-by-word and search-by-color/RAL tools, no live configurator (/en-us/bespoke)</t>
         </is>
       </c>
       <c r="AP13" s="2" t="inlineStr">
         <is>
-          <t>HOOK: "tailor-made contemporary wallcoverings"; Wallpaper Design Competition launched spring 2026 — /en-us/news/projects/</t>
+          <t>"Bespoke: the project is tailor-made" — over 1500 graphic designs customizable in size and color, from sketch to wall (/en-us/bespoke)</t>
         </is>
       </c>
       <c r="AQ13" s="2" t="inlineStr">
         <is>
-          <t>CLIENT_PROOF: Villa Adele Dubai, SOUL Beachclub &amp; Restaurant, Grand Madrid Casino Torrequebrada — /en-us/news/projects/</t>
-        </is>
-      </c>
-      <c r="AR13" s="3" t="inlineStr">
+          <t>CLIENT_PROOF: "Wall&amp;decò for EATALY" bespoke project example (/en-us/bespoke)</t>
+        </is>
+      </c>
+      <c r="AR13" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="AS13" s="2" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
         <is>
           <t>NO EMAIL</t>
         </is>
       </c>
-      <c r="AS13" s="4" t="inlineStr">
+      <c r="AU13" s="4" t="inlineStr">
         <is>
           <t>No work email on this row — LinkedIn or enrichment needed</t>
         </is>
       </c>
-      <c r="AT13" s="4" t="inlineStr"/>
-      <c r="AU13" s="5" t="inlineStr"/>
       <c r="AV13" s="4" t="inlineStr"/>
       <c r="AW13" s="5" t="inlineStr"/>
       <c r="AX13" s="4" t="inlineStr"/>
       <c r="AY13" s="5" t="inlineStr"/>
+      <c r="AZ13" s="4" t="inlineStr"/>
+      <c r="BA13" s="5" t="inlineStr"/>
     </row>
     <row r="14" ht="92" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -3686,22 +3824,32 @@
           <t>CLIENT_PROOF: SILENA hotel, Bellerive hotel, named Milan/Roman/Bologna residences — /diary</t>
         </is>
       </c>
-      <c r="AR14" s="7" t="inlineStr">
+      <c r="AR14" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS14" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT14" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS14" s="4" t="inlineStr">
+      <c r="AU14" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT14" s="4" t="inlineStr">
+      <c r="AV14" s="4" t="inlineStr">
         <is>
           <t>your Bespoke Design Service, before the first sketch</t>
         </is>
       </c>
-      <c r="AU14" s="5" t="inlineStr">
+      <c r="AW14" s="5" t="inlineStr">
         <is>
           <t>Verena,
 Glamora offers a Bespoke Design Service to professionals. An architect brings a project, your studio designs to it.
@@ -3710,12 +3858,12 @@
 Would it be useful to see it against one of your collections?</t>
         </is>
       </c>
-      <c r="AV14" s="4" t="inlineStr">
+      <c r="AX14" s="4" t="inlineStr">
         <is>
           <t>turning the first meeting into a decision</t>
         </is>
       </c>
-      <c r="AW14" s="5" t="inlineStr">
+      <c r="AY14" s="5" t="inlineStr">
         <is>
           <t>Verena,
 Worth adding, because "AI" says nothing useful on its own. There is no CAD and no drawing. Someone describes the piece by colour, mood and scale, gets an original concept, then sees it in the room.
@@ -3723,12 +3871,12 @@
 ai.mecartworks.com. Five free previews after a one time code.</t>
         </is>
       </c>
-      <c r="AX14" s="4" t="inlineStr">
+      <c r="AZ14" s="4" t="inlineStr">
         <is>
           <t>do you show them anything in meeting one?</t>
         </is>
       </c>
-      <c r="AY14" s="5" t="inlineStr">
+      <c r="BA14" s="5" t="inlineStr">
         <is>
           <t>Verena,
 This is the last one.
@@ -3926,22 +4074,32 @@
           <t>CLIENT_PROOF: Hotel La Gemma (Florence), Löwengrube (Bavaria) — /progetti/</t>
         </is>
       </c>
-      <c r="AR15" s="7" t="inlineStr">
+      <c r="AR15" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS15" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT15" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS15" s="4" t="inlineStr">
+      <c r="AU15" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT15" s="4" t="inlineStr">
+      <c r="AV15" s="4" t="inlineStr">
         <is>
           <t>progetti su misura, before the render</t>
         </is>
       </c>
-      <c r="AU15" s="5" t="inlineStr">
+      <c r="AW15" s="5" t="inlineStr">
         <is>
           <t>Paolo,
 Inkiostro Bianco offers progetti su misura, and with a 3D lead in the room you are already making visuals to sell them.
@@ -3950,12 +4108,12 @@
 Not a replacement for your 3D work. A filter in front of it. Worth a look?</t>
         </is>
       </c>
-      <c r="AV15" s="4" t="inlineStr">
+      <c r="AX15" s="4" t="inlineStr">
         <is>
           <t>a 3D lead's read on the output</t>
         </is>
       </c>
-      <c r="AW15" s="5" t="inlineStr">
+      <c r="AY15" s="5" t="inlineStr">
         <is>
           <t>Paolo,
 You would judge this faster than anyone I could send it to, so I will be direct about what I want.
@@ -3964,12 +4122,12 @@
 ai.mecartworks.com, free, five previews, email code.</t>
         </is>
       </c>
-      <c r="AX15" s="4" t="inlineStr">
+      <c r="AZ15" s="4" t="inlineStr">
         <is>
           <t>if the 3D queue is never a queue</t>
         </is>
       </c>
-      <c r="AY15" s="5" t="inlineStr">
+      <c r="BA15" s="5" t="inlineStr">
         <is>
           <t>Paolo,
 I will let this go.
@@ -4171,22 +4329,32 @@
           <t>CLIENT_PROOF: Hotel Feldhof (Merano), Cascina Morelli 1862 (Avigliana), Tomiko-San (Wilmington) — /it/progetti-interior-design-carta-da-parati/</t>
         </is>
       </c>
-      <c r="AR16" s="7" t="inlineStr">
+      <c r="AR16" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS16" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT16" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS16" s="4" t="inlineStr">
+      <c r="AU16" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT16" s="4" t="inlineStr">
+      <c r="AV16" s="4" t="inlineStr">
         <is>
           <t>Real Wall and Live Room, one step earlier</t>
         </is>
       </c>
-      <c r="AU16" s="5" t="inlineStr">
+      <c r="AW16" s="5" t="inlineStr">
         <is>
           <t>Giulia,
 Real Wall and Live Room put Instabilelab ahead of most of this industry. Plenty of wallcovering brands still ship a static gallery and call it a tool.
@@ -4195,12 +4363,12 @@
 Would it be useful to see how it sits in front of Real Wall?</t>
         </is>
       </c>
-      <c r="AV16" s="4" t="inlineStr">
+      <c r="AX16" s="4" t="inlineStr">
         <is>
           <t>the visitor your configurators never meet</t>
         </is>
       </c>
-      <c r="AW16" s="5" t="inlineStr">
+      <c r="AY16" s="5" t="inlineStr">
         <is>
           <t>Giulia,
 To be concrete. Someone types "ochre, oversized botanical, matte" and gets an original design, then sees it on their wall. Your configurators handle everything after that.
@@ -4208,12 +4376,12 @@
 You will find it at ai.mecartworks.com. Five previews, no cost.</t>
         </is>
       </c>
-      <c r="AX16" s="4" t="inlineStr">
+      <c r="AZ16" s="4" t="inlineStr">
         <is>
           <t>you built configurators. what did you learn?</t>
         </is>
       </c>
-      <c r="AY16" s="5" t="inlineStr">
+      <c r="BA16" s="5" t="inlineStr">
         <is>
           <t>Giulia,
 Final email from me.
@@ -4424,22 +4592,32 @@
           <t>CLIENT_PROOF: "As seen in" logos incl. Ritz-Carlton, Luxe Pools — footer</t>
         </is>
       </c>
-      <c r="AR17" s="7" t="inlineStr">
+      <c r="AR17" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS17" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT17" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS17" s="4" t="inlineStr">
+      <c r="AU17" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT17" s="4" t="inlineStr">
+      <c r="AV17" s="4" t="inlineStr">
         <is>
           <t>Create a Mosaic, before the drawing</t>
         </is>
       </c>
-      <c r="AU17" s="5" t="inlineStr">
+      <c r="AW17" s="5" t="inlineStr">
         <is>
           <t>Michael,
 Your Create a Mosaic service is why I am writing. A homeowner or a builder describes what they want in the pool, and your team turns it into a design.
@@ -4448,12 +4626,12 @@
 I would rather walk you through it than send you a competitor's link. Can I book fifteen minutes?</t>
         </is>
       </c>
-      <c r="AV17" s="4" t="inlineStr">
+      <c r="AX17" s="4" t="inlineStr">
         <is>
           <t>selling the finished pool, not the drawing</t>
         </is>
       </c>
-      <c r="AW17" s="5" t="inlineStr">
+      <c r="AY17" s="5" t="inlineStr">
         <is>
           <t>Michael,
 How it works. Someone types "deep blue, geometric, Mediterranean" and gets an original mosaic concept, then it is placed on a photo of the real pool.
@@ -4461,12 +4639,12 @@
 Fifteen minutes on a screen share, no deck. Shall I send two or three times that suit you?</t>
         </is>
       </c>
-      <c r="AX17" s="4" t="inlineStr">
+      <c r="AZ17" s="4" t="inlineStr">
         <is>
           <t>if custom pools already close fast</t>
         </is>
       </c>
-      <c r="AY17" s="5" t="inlineStr">
+      <c r="BA17" s="5" t="inlineStr">
         <is>
           <t>Michael,
 That is me done.
@@ -4653,22 +4831,32 @@
           <t>CLIENT_PROOF: Not found</t>
         </is>
       </c>
-      <c r="AR18" s="7" t="inlineStr">
+      <c r="AR18" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS18" s="2" t="inlineStr">
+        <is>
+          <t>found on SMB fallback</t>
+        </is>
+      </c>
+      <c r="AT18" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS18" s="4" t="inlineStr">
+      <c r="AU18" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT18" s="4" t="inlineStr">
+      <c r="AV18" s="4" t="inlineStr">
         <is>
           <t>the free design consultation</t>
         </is>
       </c>
-      <c r="AU18" s="5" t="inlineStr">
+      <c r="AW18" s="5" t="inlineStr">
         <is>
           <t>Chad,
 Mosaics Lab offers a free design consultation on custom work. A customer sends a photo or a painting, and your team turns it into a mosaic concept.
@@ -4677,12 +4865,12 @@
 Rather than point you at a competitor's site, can I walk you through it?</t>
         </is>
       </c>
-      <c r="AV18" s="4" t="inlineStr">
+      <c r="AX18" s="4" t="inlineStr">
         <is>
           <t>how many consultations turn into orders?</t>
         </is>
       </c>
-      <c r="AW18" s="5" t="inlineStr">
+      <c r="AY18" s="5" t="inlineStr">
         <is>
           <t>Chad,
 The number I would want if I ran your business: what share of free consultations become paid mosaics?
@@ -4691,12 +4879,12 @@
 Want a couple of times?</t>
         </is>
       </c>
-      <c r="AX18" s="4" t="inlineStr">
+      <c r="AZ18" s="4" t="inlineStr">
         <is>
           <t>owners know where the time leaks</t>
         </is>
       </c>
-      <c r="AY18" s="5" t="inlineStr">
+      <c r="BA18" s="5" t="inlineStr">
         <is>
           <t>Chad,
 No more from me after this.
@@ -4850,22 +5038,32 @@
           <t>CLIENT_PROOF: Not found</t>
         </is>
       </c>
-      <c r="AR19" s="7" t="inlineStr">
+      <c r="AR19" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS19" s="2" t="inlineStr">
+        <is>
+          <t>found on SMB fallback</t>
+        </is>
+      </c>
+      <c r="AT19" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS19" s="4" t="inlineStr">
+      <c r="AU19" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT19" s="4" t="inlineStr">
+      <c r="AV19" s="4" t="inlineStr">
         <is>
           <t>your artists, working step by step</t>
         </is>
       </c>
-      <c r="AU19" s="5" t="inlineStr">
+      <c r="AW19" s="5" t="inlineStr">
         <is>
           <t>Sal,
 Your own site says your ceramic artists work with the customer step by step to create the custom piece. Logos, mascots, family crests.
@@ -4874,12 +5072,12 @@
 Happy to show you myself. Would fifteen minutes work?</t>
         </is>
       </c>
-      <c r="AV19" s="4" t="inlineStr">
+      <c r="AX19" s="4" t="inlineStr">
         <is>
           <t>software for your artists, software for your customer</t>
         </is>
       </c>
-      <c r="AW19" s="5" t="inlineStr">
+      <c r="AY19" s="5" t="inlineStr">
         <is>
           <t>Sal,
 The difference in one line. Your software is a tool for your artists. This one is a tool for your customer.
@@ -4887,12 +5085,12 @@
 Screen share, 15 minutes, no deck. Want me to send times?</t>
         </is>
       </c>
-      <c r="AX19" s="4" t="inlineStr">
+      <c r="AZ19" s="4" t="inlineStr">
         <is>
           <t>wrapping this up</t>
         </is>
       </c>
-      <c r="AY19" s="5" t="inlineStr">
+      <c r="BA19" s="5" t="inlineStr">
         <is>
           <t>Sal,
 I will close this off.
@@ -5070,48 +5268,62 @@
           <t>swilkins@newravenna.com</t>
         </is>
       </c>
-      <c r="AL20" s="2" t="inlineStr"/>
+      <c r="AL20" s="2" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
       <c r="AM20" s="2" t="inlineStr">
         <is>
-          <t>SITE_MATCH: Match — custom stone and glass mosaics match company</t>
+          <t>SITE_MATCH: Match — brand and mosaic/tile products align with New Ravenna</t>
         </is>
       </c>
       <c r="AN20" s="2" t="inlineStr">
         <is>
-          <t>CUSTOM_OFFERING: Yes — bespoke projects from photographs, swatches, clippings; made to measure — /made-to-meaure/</t>
+          <t>CUSTOM_OFFERING: Yes — "turn almost any inspiration into a mosaic" via customization process — /product (Customizable Mosaics)</t>
         </is>
       </c>
       <c r="AO20" s="2" t="inlineStr">
         <is>
-          <t>VISUAL_TOOL: None — /design-resources/ not reachable; no configurator found — unverified</t>
+          <t>VISUAL_TOOL: Basic — Mosaic Templates &amp; Design Portfolio galleries, no interactive configurator — /design-resources/mosaic-templates</t>
         </is>
       </c>
       <c r="AP20" s="2" t="inlineStr">
         <is>
-          <t>HOOK: "Made To Measure" — patterns custom cut to exact project dimensions — /made-to-meaure/</t>
+          <t>"Made to Measure" custom-cut mosaics fit exact project dimensions — /made-to-meaure</t>
         </is>
       </c>
       <c r="AQ20" s="2" t="inlineStr">
         <is>
-          <t>CLIENT_PROOF: Not found</t>
-        </is>
-      </c>
-      <c r="AR20" s="7" t="inlineStr">
+          <t>CLIENT_PROOF: Designer collaboration "J. Banks Design" collection named; no branded venue found — /product?_sfm_nr_collection=j-banks-design</t>
+        </is>
+      </c>
+      <c r="AR20" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS20" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT20" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS20" s="4" t="inlineStr">
+      <c r="AU20" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT20" s="4" t="inlineStr">
+      <c r="AV20" s="4" t="inlineStr">
         <is>
           <t>your concept board team</t>
         </is>
       </c>
-      <c r="AU20" s="5" t="inlineStr">
+      <c r="AW20" s="5" t="inlineStr">
         <is>
           <t>Stephenie,
 New Ravenna's bespoke route starts with photographs, fabric swatches, sometimes a magazine clipping, and your team turning that into a mosaic concept before anything is cut.
@@ -5120,12 +5332,12 @@
 I would rather show you than send a competitor's link. Free for fifteen minutes this week?</t>
         </is>
       </c>
-      <c r="AV20" s="4" t="inlineStr">
+      <c r="AX20" s="4" t="inlineStr">
         <is>
           <t>photographs, swatches, clippings</t>
         </is>
       </c>
-      <c r="AW20" s="5" t="inlineStr">
+      <c r="AY20" s="5" t="inlineStr">
         <is>
           <t>Stephenie,
 How it actually works. Someone types "warm terracotta, geometric, Moorish influence" and gets an original concept, then sees it on a photo of the real wall.
@@ -5133,12 +5345,12 @@
 Fifteen minutes on a screen share and you would know. Want me to propose a time?</t>
         </is>
       </c>
-      <c r="AX20" s="4" t="inlineStr">
+      <c r="AZ20" s="4" t="inlineStr">
         <is>
           <t>how does the first pass work now?</t>
         </is>
       </c>
-      <c r="AY20" s="5" t="inlineStr">
+      <c r="BA20" s="5" t="inlineStr">
         <is>
           <t>Stephenie,
 I will leave this alone now.
@@ -5331,22 +5543,32 @@
           <t>CLIENT_PROOF: Not found</t>
         </is>
       </c>
-      <c r="AR21" s="7" t="inlineStr">
+      <c r="AR21" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS21" s="2" t="inlineStr">
+        <is>
+          <t>found on SMB fallback</t>
+        </is>
+      </c>
+      <c r="AT21" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS21" s="4" t="inlineStr">
+      <c r="AU21" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT21" s="4" t="inlineStr">
+      <c r="AV21" s="4" t="inlineStr">
         <is>
           <t>custom mosaic murals, before the layout</t>
         </is>
       </c>
-      <c r="AU21" s="5" t="inlineStr">
+      <c r="AW21" s="5" t="inlineStr">
         <is>
           <t>Christina,
 Hakatai does custom designed glass tile installations. Mosaic murals and uncut custom patterns, not only stock series.
@@ -5355,12 +5577,12 @@
 Happy to walk you through it instead. Fifteen minutes on a call?</t>
         </is>
       </c>
-      <c r="AV21" s="4" t="inlineStr">
+      <c r="AX21" s="4" t="inlineStr">
         <is>
           <t>clients who can see it approve the bigger piece</t>
         </is>
       </c>
-      <c r="AW21" s="5" t="inlineStr">
+      <c r="AY21" s="5" t="inlineStr">
         <is>
           <t>Christina,
 The money point, plainly. A client who can see the finished wall does not need to hedge. The ones who cannot see it protect themselves by ordering less.
@@ -5368,12 +5590,12 @@
 I would rather demo it than send you to a competitor's site. Fifteen minutes, screen share. Want a couple of times?</t>
         </is>
       </c>
-      <c r="AX21" s="4" t="inlineStr">
+      <c r="AZ21" s="4" t="inlineStr">
         <is>
           <t>one last note</t>
         </is>
       </c>
-      <c r="AY21" s="5" t="inlineStr">
+      <c r="BA21" s="5" t="inlineStr">
         <is>
           <t>Christina,
 Closing this out.
@@ -5513,48 +5735,62 @@
           <t>sgildea@oceansideglasstile.com</t>
         </is>
       </c>
-      <c r="AL22" s="2" t="inlineStr"/>
+      <c r="AL22" s="2" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
       <c r="AM22" s="2" t="inlineStr">
         <is>
-          <t>SITE_MATCH: Match — recycled glass tile manufacturer matches company</t>
+          <t>SITE_MATCH: Match — brand redirects to glasstile.com, glass tile products align with company</t>
         </is>
       </c>
       <c r="AN22" s="2" t="inlineStr">
         <is>
-          <t>CUSTOM_OFFERING: Yes — Special Order Program customizable mosaic; "Uniquely Oceanside" pool tile customization — glasstile.com</t>
+          <t>CUSTOM_OFFERING: Yes — "Make It Your Own" custom blends, gradients, color selection — /collections/make-it-your-own</t>
         </is>
       </c>
       <c r="AO22" s="2" t="inlineStr">
         <is>
-          <t>VISUAL_TOOL: None — no configurator or preview found — sitewide</t>
+          <t>VISUAL_TOOL: Advanced — interactive Blend Builder lets users pick colors, patterns, grout, live preview — tools.glasstile.com/BlendBuilder.aspx</t>
         </is>
       </c>
       <c r="AP22" s="2" t="inlineStr">
         <is>
-          <t>HOOK: "luxury glass tile using recycled bottle glass" — up to 85% recycled — glasstile.com</t>
+          <t>HOOK: "Make It Your Own" custom collection with Custom Blend &amp; Gradient tools — /collections/make-it-your-own</t>
         </is>
       </c>
       <c r="AQ22" s="2" t="inlineStr">
         <is>
-          <t>CLIENT_PROOF: Not found</t>
-        </is>
-      </c>
-      <c r="AR22" s="7" t="inlineStr">
+          <t>CLIENT_PROOF: Not found — only individual customer testimonials (e.g., Phil Thomison, Jack Cross pool projects), no named brand/venue — glasstile.com homepage</t>
+        </is>
+      </c>
+      <c r="AR22" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS22" s="2" t="inlineStr">
+        <is>
+          <t>found on SMB fallback</t>
+        </is>
+      </c>
+      <c r="AT22" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS22" s="4" t="inlineStr">
+      <c r="AU22" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT22" s="4" t="inlineStr">
+      <c r="AV22" s="4" t="inlineStr">
         <is>
           <t>the Special Order Program</t>
         </is>
       </c>
-      <c r="AU22" s="5" t="inlineStr">
+      <c r="AW22" s="5" t="inlineStr">
         <is>
           <t>Sean,
 Oceanside's Special Order Program and the Uniquely Oceanside collaboration both let a client customise before the tile ships.
@@ -5563,12 +5799,12 @@
 Can I walk you through it? Fifteen minutes.</t>
         </is>
       </c>
-      <c r="AV22" s="4" t="inlineStr">
+      <c r="AX22" s="4" t="inlineStr">
         <is>
           <t>unlimited possibilities, one decision</t>
         </is>
       </c>
-      <c r="AW22" s="5" t="inlineStr">
+      <c r="AY22" s="5" t="inlineStr">
         <is>
           <t>Sean,
 Where it fits Oceanside. Unlimited combinations is a great selling line right up to the moment a client has to pick one, and then it becomes the reason they delay.
@@ -5576,12 +5812,12 @@
 I would rather show you directly than send a competitor's link. A quick screen share is all it takes. Want me to send times?</t>
         </is>
       </c>
-      <c r="AX22" s="4" t="inlineStr">
+      <c r="AZ22" s="4" t="inlineStr">
         <is>
           <t>thirty years of recycled glass</t>
         </is>
       </c>
-      <c r="AY22" s="5" t="inlineStr">
+      <c r="BA22" s="5" t="inlineStr">
         <is>
           <t>Sean,
 Final note.
@@ -5786,22 +6022,32 @@
           <t>CLIENT_PROOF: Not found</t>
         </is>
       </c>
-      <c r="AR23" s="7" t="inlineStr">
+      <c r="AR23" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS23" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT23" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS23" s="4" t="inlineStr">
+      <c r="AU23" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT23" s="4" t="inlineStr">
+      <c r="AV23" s="4" t="inlineStr">
         <is>
           <t>what Tailored To asks of a client</t>
         </is>
       </c>
-      <c r="AU23" s="5" t="inlineStr">
+      <c r="AW23" s="5" t="inlineStr">
         <is>
           <t>Colleen,
 Tailored To is a real bespoke programme. Custom cutting and finishing, not a size option with a nicer name.
@@ -5810,12 +6056,12 @@
 I would rather walk you through it than send a competitor's link. Open to a short call?</t>
         </is>
       </c>
-      <c r="AV23" s="4" t="inlineStr">
+      <c r="AX23" s="4" t="inlineStr">
         <is>
           <t>a better lead than a sample request</t>
         </is>
       </c>
-      <c r="AW23" s="5" t="inlineStr">
+      <c r="AY23" s="5" t="inlineStr">
         <is>
           <t>Colleen,
 From a marketing seat there is a second angle here. This is content as much as it is a tool.
@@ -5823,12 +6069,12 @@
 Fifteen minutes on a screen share and you would know whether it is worth raising internally. Want me to send a couple of times?</t>
         </is>
       </c>
-      <c r="AX23" s="4" t="inlineStr">
+      <c r="AZ23" s="4" t="inlineStr">
         <is>
           <t>not adding to your inbox</t>
         </is>
       </c>
-      <c r="AY23" s="5" t="inlineStr">
+      <c r="BA23" s="5" t="inlineStr">
         <is>
           <t>Colleen,
 Last one, then I am out of your inbox.
@@ -6026,22 +6272,32 @@
           <t>CLIENT_PROOF: Not found</t>
         </is>
       </c>
-      <c r="AR24" s="3" t="inlineStr">
+      <c r="AR24" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="AS24" s="2" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
         <is>
           <t>NO EMAIL</t>
         </is>
       </c>
-      <c r="AS24" s="4" t="inlineStr">
+      <c r="AU24" s="4" t="inlineStr">
         <is>
           <t>No work email on this row — LinkedIn or enrichment needed</t>
         </is>
       </c>
-      <c r="AT24" s="4" t="inlineStr"/>
-      <c r="AU24" s="5" t="inlineStr"/>
       <c r="AV24" s="4" t="inlineStr"/>
       <c r="AW24" s="5" t="inlineStr"/>
       <c r="AX24" s="4" t="inlineStr"/>
       <c r="AY24" s="5" t="inlineStr"/>
+      <c r="AZ24" s="4" t="inlineStr"/>
+      <c r="BA24" s="5" t="inlineStr"/>
     </row>
     <row r="25" ht="92" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -6239,22 +6495,32 @@
           <t>CLIENT_PROOF: Flora Springs Winery (Napa Valley), Paradis Latin (Paris), Happy Me Yacht (Benetti) — /it/progetti</t>
         </is>
       </c>
-      <c r="AR25" s="7" t="inlineStr">
+      <c r="AR25" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS25" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT25" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS25" s="4" t="inlineStr">
+      <c r="AU25" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT25" s="4" t="inlineStr">
+      <c r="AV25" s="4" t="inlineStr">
         <is>
           <t>your design service for architects</t>
         </is>
       </c>
-      <c r="AU25" s="5" t="inlineStr">
+      <c r="AW25" s="5" t="inlineStr">
         <is>
           <t>Andrea,
 Sicis runs a design service for architects, soluzioni su misura across mosaic, glass and interiors.
@@ -6263,12 +6529,12 @@
 Worth walking you through?</t>
         </is>
       </c>
-      <c r="AV25" s="4" t="inlineStr">
+      <c r="AX25" s="4" t="inlineStr">
         <is>
           <t>one image that works as a proposal and as content</t>
         </is>
       </c>
-      <c r="AW25" s="5" t="inlineStr">
+      <c r="AY25" s="5" t="inlineStr">
         <is>
           <t>Andrea,
 For your side of the business specifically. The output is shareable, not just usable.
@@ -6276,12 +6542,12 @@
 Fifteen minutes on a screen share and you would see whether the quality is up to the brand.</t>
         </is>
       </c>
-      <c r="AX25" s="4" t="inlineStr">
+      <c r="AZ25" s="4" t="inlineStr">
         <is>
           <t>Sicis may not need generated imagery</t>
         </is>
       </c>
-      <c r="AY25" s="5" t="inlineStr">
+      <c r="BA25" s="5" t="inlineStr">
         <is>
           <t>Andrea,
 I will leave it there.
@@ -6457,48 +6723,62 @@
           <t>paolo.rinaldi@bisazza.com</t>
         </is>
       </c>
-      <c r="AL26" s="2" t="inlineStr"/>
+      <c r="AL26" s="2" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
       <c r="AM26" s="2" t="inlineStr">
         <is>
-          <t>SITE_MATCH: Match — luxury decor/furnishings with design customization services</t>
+          <t>SITE_MATCH: Match — glass mosaic brand and products align with Bisazza</t>
         </is>
       </c>
       <c r="AN26" s="2" t="inlineStr">
         <is>
-          <t>CUSTOM_OFFERING: Yes — "Configure your space" app + free Design Studio consultation for custom mosaic reproduction — /en-global/Products/Mosaico/</t>
+          <t>CUSTOM_OFFERING: Yes — Bisazza Design Studio offers custom drawing/photo reproduction in mosaic — /usa/Products</t>
         </is>
       </c>
       <c r="AO26" s="2" t="inlineStr">
         <is>
-          <t>VISUAL_TOOL: Advanced — "Bisazza App" interactive space configurator — app.bisazza.com</t>
+          <t>VISUAL_TOOL: Advanced — online configurator "Configure your space" to design/customize spaces — app.bisazza.com</t>
         </is>
       </c>
       <c r="AP26" s="2" t="inlineStr">
         <is>
-          <t>HOOK: "Bisazza Design Studio is available for a free consultation" — custom mosaics with hand-cut tiles — /en-global/</t>
+          <t>"70th anniversary project with AMDL CIRCLE unveiled at Milan Design Week 2026" — /usa/Designers</t>
         </is>
       </c>
       <c r="AQ26" s="2" t="inlineStr">
         <is>
-          <t>CLIENT_PROOF: Designer collaborations (Fabio Novembre, Jaime Hayon, AMDL CIRCLE, Andree Putman); no third-party venue — /en-global/Designers/</t>
-        </is>
-      </c>
-      <c r="AR26" s="7" t="inlineStr">
+          <t>Hotel Bulgari (Roma, Tokyo, London) and Mandarin Oriental Barcelona with Patricia Urquiola design — /usa/projects-detail?type[0]=hotel</t>
+        </is>
+      </c>
+      <c r="AR26" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS26" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT26" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS26" s="4" t="inlineStr">
+      <c r="AU26" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT26" s="4" t="inlineStr">
+      <c r="AV26" s="4" t="inlineStr">
         <is>
           <t>the Bisazza App, and the consultation behind it</t>
         </is>
       </c>
-      <c r="AU26" s="5" t="inlineStr">
+      <c r="AW26" s="5" t="inlineStr">
         <is>
           <t>Paolo,
 Bisazza already runs a space configurator and a free Design Studio consultation for custom mosaic work. That is further along than most of this industry.
@@ -6507,12 +6787,12 @@
 Worth a look as a front end to the Design Studio?</t>
         </is>
       </c>
-      <c r="AV26" s="4" t="inlineStr">
+      <c r="AX26" s="4" t="inlineStr">
         <is>
           <t>where the Design Studio hours go</t>
         </is>
       </c>
-      <c r="AW26" s="5" t="inlineStr">
+      <c r="AY26" s="5" t="inlineStr">
         <is>
           <t>Paolo,
 Framing it for your side. The app handles configuration. The studio handles creation. The gap between them is paid human time, and it scales linearly with demand.
@@ -6520,12 +6800,12 @@
 I would rather show you than send a link. Fifteen minutes on a screen share. Want a couple of times?</t>
         </is>
       </c>
-      <c r="AX26" s="4" t="inlineStr">
+      <c r="AZ26" s="4" t="inlineStr">
         <is>
           <t>have you looked at generated design already?</t>
         </is>
       </c>
-      <c r="AY26" s="5" t="inlineStr">
+      <c r="BA26" s="5" t="inlineStr">
         <is>
           <t>Paolo,
 Closing this off.
@@ -6734,22 +7014,32 @@
           <t>CLIENT_PROOF: Not found</t>
         </is>
       </c>
-      <c r="AR27" s="7" t="inlineStr">
+      <c r="AR27" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS27" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT27" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS27" s="4" t="inlineStr">
+      <c r="AU27" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT27" s="4" t="inlineStr">
+      <c r="AV27" s="4" t="inlineStr">
         <is>
           <t>your Mosaic Visualizer, one step earlier</t>
         </is>
       </c>
-      <c r="AU27" s="5" t="inlineStr">
+      <c r="AW27" s="5" t="inlineStr">
         <is>
           <t>Samantha,
 Fireclay's Mosaic Visualizer is one of the few real ones in this industry. Most tile brands still ship a photo gallery and call it a tool.
@@ -6758,12 +7048,12 @@
 Would it be useful to see how it sits in front of the Visualizer?</t>
         </is>
       </c>
-      <c r="AV27" s="4" t="inlineStr">
+      <c r="AX27" s="4" t="inlineStr">
         <is>
           <t>the Foundry launch and the like that but requests</t>
         </is>
       </c>
-      <c r="AW27" s="5" t="inlineStr">
+      <c r="AY27" s="5" t="inlineStr">
         <is>
           <t>Samantha,
 The Foundry Collection is a good example of the gap. A launch creates demand for a look, and the requests that follow are always "like that, but".
@@ -6771,12 +7061,12 @@
 It is at ai.mecartworks.com. Five previews, no cost, code by email. You would know inside two minutes whether the output clears Fireclay's bar.</t>
         </is>
       </c>
-      <c r="AX27" s="4" t="inlineStr">
+      <c r="AZ27" s="4" t="inlineStr">
         <is>
           <t>one for the roadmap file</t>
         </is>
       </c>
-      <c r="AY27" s="5" t="inlineStr">
+      <c r="BA27" s="5" t="inlineStr">
         <is>
           <t>Samantha,
 This is my last email on it.
@@ -6945,48 +7235,62 @@
         </is>
       </c>
       <c r="AK28" s="2" t="inlineStr"/>
-      <c r="AL28" s="2" t="inlineStr"/>
+      <c r="AL28" s="2" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
       <c r="AM28" s="2" t="inlineStr">
         <is>
-          <t>SITE_MATCH: Match — artisan tile retailer with design collaborations</t>
+          <t>SITE_MATCH: Match — clé tile brand and artisan tile products align with company</t>
         </is>
       </c>
       <c r="AN28" s="2" t="inlineStr">
         <is>
-          <t>CUSTOM_OFFERING: Yes — shop by colors/shapes/areas; modular collections allow customization — /collections/all</t>
+          <t>CUSTOM_OFFERING: Yes — "modular formats for custom design compositions" mentioned on product/blog pages</t>
         </is>
       </c>
       <c r="AO28" s="2" t="inlineStr">
         <is>
-          <t>VISUAL_TOOL: Basic — colour swatches and shape galleries, static filter interface — /collections/shop-all-zellige</t>
+          <t>VISUAL_TOOL: None — no configurator or visualizer tool found sitewide</t>
         </is>
       </c>
       <c r="AP28" s="2" t="inlineStr">
         <is>
-          <t>HOOK: "cle classics are anything but basic...affordable staples" — heritage/maison tiers — /collections/cle-classics</t>
+          <t>"Maison clé" designer collaboration collections (e.g., Cristina Celestino, Ruan Hoffmann, Deborah Osburn) — /collections/shop-all-collaborations</t>
         </is>
       </c>
       <c r="AQ28" s="2" t="inlineStr">
         <is>
-          <t>CLIENT_PROOF: Not found</t>
-        </is>
-      </c>
-      <c r="AR28" s="3" t="inlineStr">
+          <t>Not found — no named third-party brand/venue project found; only designer collaborators listed (/collections/shop-all-collaborations)</t>
+        </is>
+      </c>
+      <c r="AR28" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="AS28" s="2" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
         <is>
           <t>NO EMAIL</t>
         </is>
       </c>
-      <c r="AS28" s="4" t="inlineStr">
+      <c r="AU28" s="4" t="inlineStr">
         <is>
           <t>No work email on this row — LinkedIn or enrichment needed</t>
         </is>
       </c>
-      <c r="AT28" s="4" t="inlineStr"/>
-      <c r="AU28" s="5" t="inlineStr"/>
       <c r="AV28" s="4" t="inlineStr"/>
       <c r="AW28" s="5" t="inlineStr"/>
       <c r="AX28" s="4" t="inlineStr"/>
       <c r="AY28" s="5" t="inlineStr"/>
+      <c r="AZ28" s="4" t="inlineStr"/>
+      <c r="BA28" s="5" t="inlineStr"/>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
@@ -7161,22 +7465,32 @@
           <t>CLIENT_PROOF: Not found</t>
         </is>
       </c>
-      <c r="AR29" s="3" t="inlineStr">
+      <c r="AR29" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="AS29" s="2" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
         <is>
           <t>NO EMAIL</t>
         </is>
       </c>
-      <c r="AS29" s="4" t="inlineStr">
+      <c r="AU29" s="4" t="inlineStr">
         <is>
           <t>No work email on this row — LinkedIn or enrichment needed</t>
         </is>
       </c>
-      <c r="AT29" s="4" t="inlineStr"/>
-      <c r="AU29" s="5" t="inlineStr"/>
       <c r="AV29" s="4" t="inlineStr"/>
       <c r="AW29" s="5" t="inlineStr"/>
       <c r="AX29" s="4" t="inlineStr"/>
       <c r="AY29" s="5" t="inlineStr"/>
+      <c r="AZ29" s="4" t="inlineStr"/>
+      <c r="BA29" s="5" t="inlineStr"/>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -7336,22 +7650,32 @@
           <t>CLIENT_PROOF: Scotiabank Canada, Sheikh Abdullah Al Salem Cultural Centre Kuwait, Condado Vanderbilt Hotel, The Mark Hotel New York — /projects/</t>
         </is>
       </c>
-      <c r="AR30" s="3" t="inlineStr">
+      <c r="AR30" s="2" t="inlineStr">
+        <is>
+          <t>NO CONTACT</t>
+        </is>
+      </c>
+      <c r="AS30" s="2" t="inlineStr">
+        <is>
+          <t>both people searches failed. Needs manual sourcing or LinkedIn</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
         <is>
           <t>NO EMAIL</t>
         </is>
       </c>
-      <c r="AS30" s="4" t="inlineStr">
+      <c r="AU30" s="4" t="inlineStr">
         <is>
           <t>No work email on this row — LinkedIn or enrichment needed</t>
         </is>
       </c>
-      <c r="AT30" s="4" t="inlineStr"/>
-      <c r="AU30" s="5" t="inlineStr"/>
       <c r="AV30" s="4" t="inlineStr"/>
       <c r="AW30" s="5" t="inlineStr"/>
       <c r="AX30" s="4" t="inlineStr"/>
       <c r="AY30" s="5" t="inlineStr"/>
+      <c r="AZ30" s="4" t="inlineStr"/>
+      <c r="BA30" s="5" t="inlineStr"/>
     </row>
     <row r="31" ht="92" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
@@ -7548,22 +7872,32 @@
           <t>CLIENT_PROOF: Whitney Museum commissioned "Nourish" by Dyani White Hawk; MSP Airport mosaic mural — /pages/the-whitney</t>
         </is>
       </c>
-      <c r="AR31" s="7" t="inlineStr">
+      <c r="AR31" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS31" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT31" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS31" s="4" t="inlineStr">
+      <c r="AU31" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT31" s="4" t="inlineStr">
+      <c r="AV31" s="4" t="inlineStr">
         <is>
           <t>your consultants, and the first ten minutes</t>
         </is>
       </c>
-      <c r="AU31" s="5" t="inlineStr">
+      <c r="AW31" s="5" t="inlineStr">
         <is>
           <t>Randi,
 Create Your Blend lets a customer pick colours for diamond tiles, and you have a director of design consultants. That combination tells me plenty of custom work still starts as a conversation rather than a selector.
@@ -7572,12 +7906,12 @@
 Would it help your consultants to see it?</t>
         </is>
       </c>
-      <c r="AV31" s="4" t="inlineStr">
+      <c r="AX31" s="4" t="inlineStr">
         <is>
           <t>refining instead of guessing</t>
         </is>
       </c>
-      <c r="AW31" s="5" t="inlineStr">
+      <c r="AY31" s="5" t="inlineStr">
         <is>
           <t>Randi,
 For a consulting team, the value is in what the first call starts from.
@@ -7585,12 +7919,12 @@
 ai.mecartworks.com. Free, five previews, code by email.</t>
         </is>
       </c>
-      <c r="AX31" s="4" t="inlineStr">
+      <c r="AZ31" s="4" t="inlineStr">
         <is>
           <t>closing the loop</t>
         </is>
       </c>
-      <c r="AY31" s="5" t="inlineStr">
+      <c r="BA31" s="5" t="inlineStr">
         <is>
           <t>Randi,
 Last note.
@@ -7795,22 +8129,32 @@
           <t>CLIENT_PROOF: Not found</t>
         </is>
       </c>
-      <c r="AR32" s="7" t="inlineStr">
+      <c r="AR32" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS32" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT32" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS32" s="4" t="inlineStr">
+      <c r="AU32" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT32" s="4" t="inlineStr">
+      <c r="AV32" s="4" t="inlineStr">
         <is>
           <t>Project Tile, and what comes before it</t>
         </is>
       </c>
-      <c r="AU32" s="5" t="inlineStr">
+      <c r="AW32" s="5" t="inlineStr">
         <is>
           <t>Justin,
 Project Tile is a smart piece of work. Customers planning a backsplash or a fireplace with your patterns instead of guessing at them.
@@ -7819,12 +8163,12 @@
 Worth seeing how it might sit in front of Project Tile?</t>
         </is>
       </c>
-      <c r="AV32" s="4" t="inlineStr">
+      <c r="AX32" s="4" t="inlineStr">
         <is>
           <t>an art director's verdict in two minutes</t>
         </is>
       </c>
-      <c r="AW32" s="5" t="inlineStr">
+      <c r="AY32" s="5" t="inlineStr">
         <is>
           <t>Justin,
 As an art director you will spot the flaws faster than I could list them, so here is the honest ask.
@@ -7833,12 +8177,12 @@
 Find it at ai.mecartworks.com. One code by email unlocks five previews.</t>
         </is>
       </c>
-      <c r="AX32" s="4" t="inlineStr">
+      <c r="AZ32" s="4" t="inlineStr">
         <is>
           <t>generated design might be exactly wrong for Motawi</t>
         </is>
       </c>
-      <c r="AY32" s="5" t="inlineStr">
+      <c r="BA32" s="5" t="inlineStr">
         <is>
           <t>Justin,
 I will leave this here.
@@ -8014,48 +8358,62 @@
           <t>susanne@prattandlarson.com</t>
         </is>
       </c>
-      <c r="AL33" s="2" t="inlineStr"/>
+      <c r="AL33" s="2" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
       <c r="AM33" s="2" t="inlineStr">
         <is>
-          <t>SITE_MATCH: Match — handmade ceramic tile manufacturer with design customization offerings</t>
+          <t>SITE_MATCH: Match — Pratt + Larson handmade ceramic tile brand and products confirmed</t>
         </is>
       </c>
       <c r="AN33" s="2" t="inlineStr">
         <is>
-          <t>CUSTOM_OFFERING: Yes — "Custom Work" product category + made-to-order tile — /product-category/custom-work/</t>
+          <t>CUSTOM_OFFERING: Yes — dedicated "Custom Work" category for custom artwork, shapes, glazes (/product-category/custom-work)</t>
         </is>
       </c>
       <c r="AO33" s="2" t="inlineStr">
         <is>
-          <t>VISUAL_TOOL: Basic — InLine Design Cards for pattern experimentation; no configurator — /product/inline-cards/</t>
+          <t>VISUAL_TOOL: Basic — "Design Tools" section with InLine Cards/Spellbinder physical samples, no interactive configurator (/product-category/curated-sample-sets/design_tools)</t>
         </is>
       </c>
       <c r="AP33" s="2" t="inlineStr">
         <is>
-          <t>HOOK: "InLine Design cards unlock a world where serendipity works its magic-experiment, explore, and embrace its delightful surprises" — /product/inline-cards/</t>
+          <t>HOOK: "Where Custom Comes Standard" — custom artwork, curved moldings, special shapes/sizes/glazes (/product-category/custom-work)</t>
         </is>
       </c>
       <c r="AQ33" s="2" t="inlineStr">
         <is>
-          <t>CLIENT_PROOF: Cedar &amp; Moss collaboration; Emily Henderson farmhouse renovation — /inspiration/cedar-moss-x-pratt-larson/</t>
-        </is>
-      </c>
-      <c r="AR33" s="7" t="inlineStr">
+          <t>CLIENT_PROOF: Bumble corporate headquarters — "immersive, branded experience across four different rooms" (/resources/commercial-resources); also Portland International Airport (PDX) mosaic installation per third-party source</t>
+        </is>
+      </c>
+      <c r="AR33" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS33" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT33" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS33" s="4" t="inlineStr">
+      <c r="AU33" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT33" s="4" t="inlineStr">
+      <c r="AV33" s="4" t="inlineStr">
         <is>
           <t>serendipity, minus the shipping time</t>
         </is>
       </c>
-      <c r="AU33" s="5" t="inlineStr">
+      <c r="AW33" s="5" t="inlineStr">
         <is>
           <t>Susanne,
 Your InLine Design Cards are a genuinely good idea. Physical cards so someone can experiment and let serendipity do its work.
@@ -8064,12 +8422,12 @@
 Worth showing you the parallel?</t>
         </is>
       </c>
-      <c r="AV33" s="4" t="inlineStr">
+      <c r="AX33" s="4" t="inlineStr">
         <is>
           <t>customers who experiment specify bigger</t>
         </is>
       </c>
-      <c r="AW33" s="5" t="inlineStr">
+      <c r="AY33" s="5" t="inlineStr">
         <is>
           <t>Susanne,
 What it is worth to you. Customers who experiment buy with more confidence and specify larger areas. Your cards prove you already believe that, or you would not have made them.
@@ -8077,12 +8435,12 @@
 Find it at ai.mecartworks.com. An email code gets you five previews. Two minutes will tell you whether it belongs next to the cards or nowhere near them.</t>
         </is>
       </c>
-      <c r="AX33" s="4" t="inlineStr">
+      <c r="AZ33" s="4" t="inlineStr">
         <is>
           <t>if the cards are working, ignore me</t>
         </is>
       </c>
-      <c r="AY33" s="5" t="inlineStr">
+      <c r="BA33" s="5" t="inlineStr">
         <is>
           <t>Susanne,
 I will stop chasing this.
@@ -8238,48 +8596,62 @@
         </is>
       </c>
       <c r="AK34" s="2" t="inlineStr"/>
-      <c r="AL34" s="2" t="inlineStr"/>
+      <c r="AL34" s="2" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
       <c r="AM34" s="2" t="inlineStr">
         <is>
-          <t>SITE_MATCH: Match — handmade art tile studio matches company</t>
+          <t>Match — North Prairie Tileworks handmade tile brand confirmed on handmadetile.com</t>
         </is>
       </c>
       <c r="AN34" s="2" t="inlineStr">
         <is>
-          <t>CUSTOM_OFFERING: Yes — 150+ custom glaze colors, custom relief tiles, made-to-order designs — /glaze.html</t>
+          <t>Yes — custom sizes, colors, and relief patterns made to client specifications — /ourtiles.html, /custom.html</t>
         </is>
       </c>
       <c r="AO34" s="2" t="inlineStr">
         <is>
-          <t>VISUAL_TOOL: None — static PHP/HTML pages, glaze palette is an image — /glaze.html</t>
+          <t>None — no configurator or interactive design tool found; only static galleries — /custom.html</t>
         </is>
       </c>
       <c r="AP34" s="2" t="inlineStr">
         <is>
-          <t>HOOK: "replicated tile for the Minnesota and Kansas State Capitals, Harvard University" — /restore.html</t>
+          <t>"Custom field tile sizes at NO extra charge" and NJ DOT Highlands-Seabright bridge replication project — /custom.html, /restore.html</t>
         </is>
       </c>
       <c r="AQ34" s="2" t="inlineStr">
         <is>
-          <t>CLIENT_PROOF: Minnesota and Kansas State Capitols, Harvard University, Hoover Dam visitor center — /restore.html</t>
-        </is>
-      </c>
-      <c r="AR34" s="3" t="inlineStr">
+          <t>Minnesota State Capitol, Hoover Dam (Lake Mead entry station), NJ DOT Highlands-Seabright bridge replication — /restore.html</t>
+        </is>
+      </c>
+      <c r="AR34" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="AS34" s="2" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
         <is>
           <t>NO EMAIL</t>
         </is>
       </c>
-      <c r="AS34" s="4" t="inlineStr">
+      <c r="AU34" s="4" t="inlineStr">
         <is>
           <t>No work email on this row — LinkedIn or enrichment needed</t>
         </is>
       </c>
-      <c r="AT34" s="4" t="inlineStr"/>
-      <c r="AU34" s="5" t="inlineStr"/>
       <c r="AV34" s="4" t="inlineStr"/>
       <c r="AW34" s="5" t="inlineStr"/>
       <c r="AX34" s="4" t="inlineStr"/>
       <c r="AY34" s="5" t="inlineStr"/>
+      <c r="AZ34" s="4" t="inlineStr"/>
+      <c r="BA34" s="5" t="inlineStr"/>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
@@ -8453,22 +8825,32 @@
           <t>CLIENT_PROOF: Not found</t>
         </is>
       </c>
-      <c r="AR35" s="3" t="inlineStr">
+      <c r="AR35" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="AS35" s="2" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
         <is>
           <t>NO EMAIL</t>
         </is>
       </c>
-      <c r="AS35" s="4" t="inlineStr">
+      <c r="AU35" s="4" t="inlineStr">
         <is>
           <t>No work email on this row — LinkedIn or enrichment needed</t>
         </is>
       </c>
-      <c r="AT35" s="4" t="inlineStr"/>
-      <c r="AU35" s="5" t="inlineStr"/>
       <c r="AV35" s="4" t="inlineStr"/>
       <c r="AW35" s="5" t="inlineStr"/>
       <c r="AX35" s="4" t="inlineStr"/>
       <c r="AY35" s="5" t="inlineStr"/>
+      <c r="AZ35" s="4" t="inlineStr"/>
+      <c r="BA35" s="5" t="inlineStr"/>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -8638,22 +9020,32 @@
           <t>CLIENT_PROOF: Calistoga Residence by Geremia Design — /tempest-tileworks</t>
         </is>
       </c>
-      <c r="AR36" s="3" t="inlineStr">
+      <c r="AR36" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="AS36" s="2" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
         <is>
           <t>NO EMAIL</t>
         </is>
       </c>
-      <c r="AS36" s="4" t="inlineStr">
+      <c r="AU36" s="4" t="inlineStr">
         <is>
           <t>No work email on this row — LinkedIn or enrichment needed</t>
         </is>
       </c>
-      <c r="AT36" s="4" t="inlineStr"/>
-      <c r="AU36" s="5" t="inlineStr"/>
       <c r="AV36" s="4" t="inlineStr"/>
       <c r="AW36" s="5" t="inlineStr"/>
       <c r="AX36" s="4" t="inlineStr"/>
       <c r="AY36" s="5" t="inlineStr"/>
+      <c r="AZ36" s="4" t="inlineStr"/>
+      <c r="BA36" s="5" t="inlineStr"/>
     </row>
     <row r="37" ht="92" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
@@ -8835,22 +9227,32 @@
           <t>CLIENT_PROOF: Not found</t>
         </is>
       </c>
-      <c r="AR37" s="7" t="inlineStr">
+      <c r="AR37" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS37" s="2" t="inlineStr">
+        <is>
+          <t>found on SMB fallback</t>
+        </is>
+      </c>
+      <c r="AT37" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS37" s="4" t="inlineStr">
+      <c r="AU37" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT37" s="4" t="inlineStr">
+      <c r="AV37" s="4" t="inlineStr">
         <is>
           <t>the Handmold Mini Panels</t>
         </is>
       </c>
-      <c r="AU37" s="5" t="inlineStr">
+      <c r="AW37" s="5" t="inlineStr">
         <is>
           <t>Connie,
 Seneca brought the Handmold Mini Panels back by popular demand. That tells me your specifiers respond to seeing the real thing in front of them, which is worth knowing about your own market.
@@ -8859,12 +9261,12 @@
 I could not tell from your site how much custom work Seneca takes on. Open to a short call?</t>
         </is>
       </c>
-      <c r="AV37" s="4" t="inlineStr">
+      <c r="AX37" s="4" t="inlineStr">
         <is>
           <t>a straight question about how Seneca sells</t>
         </is>
       </c>
-      <c r="AW37" s="5" t="inlineStr">
+      <c r="AY37" s="5" t="inlineStr">
         <is>
           <t>Connie,
 Being honest about why I am asking. Your site is clear on collections and quiet on how far you will go on a custom request.
@@ -8873,12 +9275,12 @@
 ai.mecartworks.com shows what I mean in two minutes.</t>
         </is>
       </c>
-      <c r="AX37" s="4" t="inlineStr">
+      <c r="AZ37" s="4" t="inlineStr">
         <is>
           <t>the Mini Panels run</t>
         </is>
       </c>
-      <c r="AY37" s="5" t="inlineStr">
+      <c r="BA37" s="5" t="inlineStr">
         <is>
           <t>Connie,
 One more and then I am done.
@@ -9052,22 +9454,32 @@
           <t>CLIENT_PROOF: "Mark Derby has been making these for the City of New Orleans since 2003" — ?page=nola-street-tiles</t>
         </is>
       </c>
-      <c r="AR38" s="7" t="inlineStr">
+      <c r="AR38" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS38" s="2" t="inlineStr">
+        <is>
+          <t>found on SMB fallback</t>
+        </is>
+      </c>
+      <c r="AT38" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS38" s="4" t="inlineStr">
+      <c r="AU38" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT38" s="4" t="inlineStr">
+      <c r="AV38" s="4" t="inlineStr">
         <is>
           <t>the New Orleans street tiles</t>
         </is>
       </c>
-      <c r="AU38" s="5" t="inlineStr">
+      <c r="AW38" s="5" t="inlineStr">
         <is>
           <t>Mark,
 Making the city's letter and number tiles since 2003 is a hard credential to argue with.
@@ -9076,12 +9488,12 @@
 Worth two minutes of an owner's time?</t>
         </is>
       </c>
-      <c r="AV38" s="4" t="inlineStr">
+      <c r="AX38" s="4" t="inlineStr">
         <is>
           <t>specialty glazing, undecided customers</t>
         </is>
       </c>
-      <c r="AW38" s="5" t="inlineStr">
+      <c r="AY38" s="5" t="inlineStr">
         <is>
           <t>Mark,
 The useful detail. No drawing, no software to learn. A customer types "Victorian, deep green, geometric border" and sees it on their own floor.
@@ -9090,12 +9502,12 @@
 If it does not do your glazes justice, I would want to know that too.</t>
         </is>
       </c>
-      <c r="AX38" s="4" t="inlineStr">
+      <c r="AZ38" s="4" t="inlineStr">
         <is>
           <t>one more tool to evaluate</t>
         </is>
       </c>
-      <c r="AY38" s="5" t="inlineStr">
+      <c r="BA38" s="5" t="inlineStr">
         <is>
           <t>Mark,
 Signing off on this one.
@@ -9265,22 +9677,32 @@
           <t>CLIENT_PROOF: Not found</t>
         </is>
       </c>
-      <c r="AR39" s="3" t="inlineStr">
+      <c r="AR39" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="AS39" s="2" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
         <is>
           <t>NO EMAIL</t>
         </is>
       </c>
-      <c r="AS39" s="4" t="inlineStr">
+      <c r="AU39" s="4" t="inlineStr">
         <is>
           <t>No work email on this row — LinkedIn or enrichment needed</t>
         </is>
       </c>
-      <c r="AT39" s="4" t="inlineStr"/>
-      <c r="AU39" s="5" t="inlineStr"/>
       <c r="AV39" s="4" t="inlineStr"/>
       <c r="AW39" s="5" t="inlineStr"/>
       <c r="AX39" s="4" t="inlineStr"/>
       <c r="AY39" s="5" t="inlineStr"/>
+      <c r="AZ39" s="4" t="inlineStr"/>
+      <c r="BA39" s="5" t="inlineStr"/>
     </row>
     <row r="40" ht="92" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -9428,48 +9850,62 @@
           <t>josh@claysquared.com</t>
         </is>
       </c>
-      <c r="AL40" s="2" t="inlineStr"/>
+      <c r="AL40" s="2" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
       <c r="AM40" s="2" t="inlineStr">
         <is>
-          <t>SITE_MATCH: Match — handmade tile manufacturer with custom design capabilities</t>
+          <t>SITE_MATCH: Match — handmade tile maker brand and products align with company</t>
         </is>
       </c>
       <c r="AN40" s="2" t="inlineStr">
         <is>
-          <t>CUSTOM_OFFERING: Yes — "Custom Projects" offering; custom tile creation for artwork — /tile/projects/custom/</t>
+          <t>CUSTOM_OFFERING: Yes — "Custom Projects" section with bespoke tile murals/designs — /tile/projects/custom</t>
         </is>
       </c>
       <c r="AO40" s="2" t="inlineStr">
         <is>
-          <t>VISUAL_TOOL: Basic — color/size/shape/pattern selectors, static galleries, no configurator — /tile/handmade-tile/</t>
+          <t>VISUAL_TOOL: None — no configurator or interactive design tool found — sitewide</t>
         </is>
       </c>
       <c r="AP40" s="2" t="inlineStr">
         <is>
-          <t>HOOK: "Cosmic Collection"; "Medieval Floral Tile"; "1920s-1950s Mid Century Tile" reproduction line — /tile-accents/cosmic-clouds/</t>
+          <t>"Minnesota State Capitol Historic Tile Reproduction" custom project — /tile/projects/custom</t>
         </is>
       </c>
       <c r="AQ40" s="2" t="inlineStr">
         <is>
-          <t>CLIENT_PROOF: David Heide Design Studio named client — testimonials section</t>
-        </is>
-      </c>
-      <c r="AR40" s="6" t="inlineStr">
+          <t>CLIENT_PROOF: "Minnesota State Capitol Historic Tile Reproduction" project — /tile/projects/custom</t>
+        </is>
+      </c>
+      <c r="AR40" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS40" s="2" t="inlineStr">
+        <is>
+          <t>found on SMB fallback</t>
+        </is>
+      </c>
+      <c r="AT40" s="6" t="inlineStr">
         <is>
           <t>HOLD - REVENUE</t>
         </is>
       </c>
-      <c r="AS40" s="4" t="inlineStr">
+      <c r="AU40" s="4" t="inlineStr">
         <is>
           <t>Revenue 500K-1M is below the $1M gate (S7.4) — verify before sending</t>
         </is>
       </c>
-      <c r="AT40" s="4" t="inlineStr">
+      <c r="AV40" s="4" t="inlineStr">
         <is>
           <t>the Cosmic Collection, on someone's actual wall</t>
         </is>
       </c>
-      <c r="AU40" s="5" t="inlineStr">
+      <c r="AW40" s="5" t="inlineStr">
         <is>
           <t>Josh,
 Clay Squared runs three quite different directions at once. The Cosmic Collection, Medieval Floral, and the 1920s to 50s mid century reproductions. That is a lot of range for one studio.
@@ -9478,12 +9914,12 @@
 Worth a couple of minutes of an owner's time?</t>
         </is>
       </c>
-      <c r="AV40" s="4" t="inlineStr">
+      <c r="AX40" s="4" t="inlineStr">
         <is>
           <t>an artist's afternoon, back</t>
         </is>
       </c>
-      <c r="AW40" s="5" t="inlineStr">
+      <c r="AY40" s="5" t="inlineStr">
         <is>
           <t>Josh,
 The practical version. They type "mid century, warm rust, geometric" and see it on their own wall before they ever email you.
@@ -9492,12 +9928,12 @@
 If it does not do your glazes justice, that is worth knowing too.</t>
         </is>
       </c>
-      <c r="AX40" s="4" t="inlineStr">
+      <c r="AZ40" s="4" t="inlineStr">
         <is>
           <t>three collections, one decision</t>
         </is>
       </c>
-      <c r="AY40" s="5" t="inlineStr">
+      <c r="BA40" s="5" t="inlineStr">
         <is>
           <t>Josh,
 I will leave you to it.
@@ -9663,22 +10099,32 @@
           <t>CLIENT_PROOF: "Oak Glen triptych three tile set based on the woodblock print by Yoshiko Yamamoto and used with permission" — /</t>
         </is>
       </c>
-      <c r="AR41" s="3" t="inlineStr">
+      <c r="AR41" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="AS41" s="2" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
         <is>
           <t>NO EMAIL</t>
         </is>
       </c>
-      <c r="AS41" s="4" t="inlineStr">
+      <c r="AU41" s="4" t="inlineStr">
         <is>
           <t>No work email on this row — LinkedIn or enrichment needed</t>
         </is>
       </c>
-      <c r="AT41" s="4" t="inlineStr"/>
-      <c r="AU41" s="5" t="inlineStr"/>
       <c r="AV41" s="4" t="inlineStr"/>
       <c r="AW41" s="5" t="inlineStr"/>
       <c r="AX41" s="4" t="inlineStr"/>
       <c r="AY41" s="5" t="inlineStr"/>
+      <c r="AZ41" s="4" t="inlineStr"/>
+      <c r="BA41" s="5" t="inlineStr"/>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -9840,22 +10286,32 @@
           <t>CLIENT_PROOF: Not found</t>
         </is>
       </c>
-      <c r="AR42" s="3" t="inlineStr">
+      <c r="AR42" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="AS42" s="2" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
         <is>
           <t>NO EMAIL</t>
         </is>
       </c>
-      <c r="AS42" s="4" t="inlineStr">
+      <c r="AU42" s="4" t="inlineStr">
         <is>
           <t>No work email on this row — LinkedIn or enrichment needed</t>
         </is>
       </c>
-      <c r="AT42" s="4" t="inlineStr"/>
-      <c r="AU42" s="5" t="inlineStr"/>
       <c r="AV42" s="4" t="inlineStr"/>
       <c r="AW42" s="5" t="inlineStr"/>
       <c r="AX42" s="4" t="inlineStr"/>
       <c r="AY42" s="5" t="inlineStr"/>
+      <c r="AZ42" s="4" t="inlineStr"/>
+      <c r="BA42" s="5" t="inlineStr"/>
     </row>
     <row r="43" ht="92" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
@@ -10001,22 +10457,32 @@
           <t>CLIENT_PROOF: Not found</t>
         </is>
       </c>
-      <c r="AR43" s="7" t="inlineStr">
+      <c r="AR43" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS43" s="2" t="inlineStr">
+        <is>
+          <t>found on SMB fallback</t>
+        </is>
+      </c>
+      <c r="AT43" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS43" s="4" t="inlineStr">
+      <c r="AU43" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT43" s="4" t="inlineStr">
+      <c r="AV43" s="4" t="inlineStr">
         <is>
           <t>19 collections, one decision</t>
         </is>
       </c>
-      <c r="AU43" s="5" t="inlineStr">
+      <c r="AW43" s="5" t="inlineStr">
         <is>
           <t>Neil,
 Nineteen design collections in the Molding and Trim series is a lot of choice, and choice is exactly what stalls a tile decision.
@@ -10025,12 +10491,12 @@
 Worth a couple of minutes?</t>
         </is>
       </c>
-      <c r="AV43" s="4" t="inlineStr">
+      <c r="AX43" s="4" t="inlineStr">
         <is>
           <t>let the customer do the narrowing</t>
         </is>
       </c>
-      <c r="AW43" s="5" t="inlineStr">
+      <c r="AY43" s="5" t="inlineStr">
         <is>
           <t>Neil,
 The practical version. The customer narrows it themselves, on screen, before they contact you.
@@ -10038,12 +10504,12 @@
 ai.mecartworks.com, no cost, five previews, code by email. Two minutes will tell you whether it handles your glazes properly.</t>
         </is>
       </c>
-      <c r="AX43" s="4" t="inlineStr">
+      <c r="AZ43" s="4" t="inlineStr">
         <is>
           <t>when choosing eats a week</t>
         </is>
       </c>
-      <c r="AY43" s="5" t="inlineStr">
+      <c r="BA43" s="5" t="inlineStr">
         <is>
           <t>Neil,
 Ending it here.
@@ -10213,48 +10679,62 @@
         </is>
       </c>
       <c r="AK44" s="2" t="inlineStr"/>
-      <c r="AL44" s="2" t="inlineStr"/>
+      <c r="AL44" s="2" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
       <c r="AM44" s="2" t="inlineStr">
         <is>
-          <t>SITE_MATCH: Match — artisan tile retailer with customization potential</t>
+          <t>SITE_MATCH: Match — brand and handmade tile products align with company</t>
         </is>
       </c>
       <c r="AN44" s="2" t="inlineStr">
         <is>
-          <t>CUSTOM_OFFERING: Yes — handmade tiles with "limited run philosophy" + color/pattern range selections — /collections/all</t>
+          <t>CUSTOM_OFFERING: Unclear — "Make it Mine"/"Make them Mine" CTAs present but no explicit tool described — sitewide</t>
         </is>
       </c>
       <c r="AO44" s="2" t="inlineStr">
         <is>
-          <t>VISUAL_TOOL: Basic — static tile galleries and color/format filters, no configurator — /collections/moroccan-zellige-all</t>
+          <t>VISUAL_TOOL: Basic — filter/browse by color, shape, finish; no interactive configurator — /collections/moroccan-zellige-all</t>
         </is>
       </c>
       <c r="AP44" s="2" t="inlineStr">
         <is>
-          <t>HOOK: "We celebrate wabi-sabi, the beauty of imperfection...because authenticity is the new luxury." — /pages/tilesofezra-standard</t>
+          <t>HOOK: "East Meets West in Brooklyn" project featured in Architectural Digest Italy, designed by Bespoke Only — /blogs/profiled/profiled-east-meets-west-in-brooklyn</t>
         </is>
       </c>
       <c r="AQ44" s="2" t="inlineStr">
         <is>
-          <t>CLIENT_PROOF: "Colorado Mountain House by Joanna Gaines" featuring Amano tiles — /blogs/profiled/profiled-colorado-mountain-house</t>
-        </is>
-      </c>
-      <c r="AR44" s="3" t="inlineStr">
+          <t>CLIENT_PROOF: "Colorado Mountain House by Joanna Gaines" and "East Meets West in Brooklyn" (Architectural Digest Italy feature) — /blogs/profiled</t>
+        </is>
+      </c>
+      <c r="AR44" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="AS44" s="2" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
         <is>
           <t>NO EMAIL</t>
         </is>
       </c>
-      <c r="AS44" s="4" t="inlineStr">
+      <c r="AU44" s="4" t="inlineStr">
         <is>
           <t>No work email on this row — LinkedIn or enrichment needed</t>
         </is>
       </c>
-      <c r="AT44" s="4" t="inlineStr"/>
-      <c r="AU44" s="5" t="inlineStr"/>
       <c r="AV44" s="4" t="inlineStr"/>
       <c r="AW44" s="5" t="inlineStr"/>
       <c r="AX44" s="4" t="inlineStr"/>
       <c r="AY44" s="5" t="inlineStr"/>
+      <c r="AZ44" s="4" t="inlineStr"/>
+      <c r="BA44" s="5" t="inlineStr"/>
     </row>
     <row r="45" ht="92" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
@@ -10416,22 +10896,32 @@
           <t>CLIENT_PROOF: Not found</t>
         </is>
       </c>
-      <c r="AR45" s="6" t="inlineStr">
+      <c r="AR45" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS45" s="2" t="inlineStr">
+        <is>
+          <t>found on SMB fallback</t>
+        </is>
+      </c>
+      <c r="AT45" s="6" t="inlineStr">
         <is>
           <t>HOLD - REVENUE</t>
         </is>
       </c>
-      <c r="AS45" s="4" t="inlineStr">
+      <c r="AU45" s="4" t="inlineStr">
         <is>
           <t>Revenue 0-500K is below the $1M gate (S7.4) — verify before sending</t>
         </is>
       </c>
-      <c r="AT45" s="4" t="inlineStr">
+      <c r="AV45" s="4" t="inlineStr">
         <is>
           <t>your simulators, and the pattern that is not in them</t>
         </is>
       </c>
-      <c r="AU45" s="5" t="inlineStr">
+      <c r="AW45" s="5" t="inlineStr">
         <is>
           <t>Caitlin,
 Popham runs two live simulators, concrete and zellige, which puts you further ahead than almost anyone in tile. BACKGAMMON, BRASILIA, KELLY Relief. A customer can play with all of them.
@@ -10440,12 +10930,12 @@
 Worth seeing how it might sit in front of the simulators?</t>
         </is>
       </c>
-      <c r="AV45" s="4" t="inlineStr">
+      <c r="AX45" s="4" t="inlineStr">
         <is>
           <t>creating the pattern, not just colouring it</t>
         </is>
       </c>
-      <c r="AW45" s="5" t="inlineStr">
+      <c r="AY45" s="5" t="inlineStr">
         <is>
           <t>Caitlin,
 The distinction that matters. Your simulators handle colour and layout on patterns that exist. This creates the pattern itself from a sentence, then puts it in the room.
@@ -10453,12 +10943,12 @@
 The link is ai.mecartworks.com. Five previews, no subscription.</t>
         </is>
       </c>
-      <c r="AX45" s="4" t="inlineStr">
+      <c r="AZ45" s="4" t="inlineStr">
         <is>
           <t>what did building the simulators teach you?</t>
         </is>
       </c>
-      <c r="AY45" s="5" t="inlineStr">
+      <c r="BA45" s="5" t="inlineStr">
         <is>
           <t>Caitlin,
 Done chasing after this one.
@@ -10639,22 +11129,32 @@
           <t>CLIENT_PROOF: Not found</t>
         </is>
       </c>
-      <c r="AR46" s="7" t="inlineStr">
+      <c r="AR46" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS46" s="2" t="inlineStr">
+        <is>
+          <t>found on SMB fallback</t>
+        </is>
+      </c>
+      <c r="AT46" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS46" s="4" t="inlineStr">
+      <c r="AU46" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT46" s="4" t="inlineStr">
+      <c r="AV46" s="4" t="inlineStr">
         <is>
           <t>before the meeting gets booked</t>
         </is>
       </c>
-      <c r="AU46" s="5" t="inlineStr">
+      <c r="AW46" s="5" t="inlineStr">
         <is>
           <t>Carli,
 Kibak offers custom tile and custom murals, and the site invites people to book a meeting to talk the project through.
@@ -10663,12 +11163,12 @@
 Would that be more useful before the meeting than during it?</t>
         </is>
       </c>
-      <c r="AV46" s="4" t="inlineStr">
+      <c r="AX46" s="4" t="inlineStr">
         <is>
           <t>refining, not interpreting</t>
         </is>
       </c>
-      <c r="AW46" s="5" t="inlineStr">
+      <c r="AY46" s="5" t="inlineStr">
         <is>
           <t>Carli,
 Concretely. The customer books the meeting already holding a picture of what they want, placed in their own space.
@@ -10676,12 +11176,12 @@
 ai.mecartworks.com, five previews, email code, no subscription.</t>
         </is>
       </c>
-      <c r="AX46" s="4" t="inlineStr">
+      <c r="AZ46" s="4" t="inlineStr">
         <is>
           <t>a solution looking for a problem?</t>
         </is>
       </c>
-      <c r="AY46" s="5" t="inlineStr">
+      <c r="BA46" s="5" t="inlineStr">
         <is>
           <t>Carli,
 I will leave this with you.
@@ -10857,48 +11357,62 @@
           <t>emma.geiszler@therugcompany.com</t>
         </is>
       </c>
-      <c r="AL47" s="2" t="inlineStr"/>
+      <c r="AL47" s="2" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
       <c r="AM47" s="2" t="inlineStr">
         <is>
-          <t>SITE_MATCH: Match — luxury handmade rugs match company</t>
+          <t>SITE_MATCH: Match — brand and rug/design products align with company</t>
         </is>
       </c>
       <c r="AN47" s="2" t="inlineStr">
         <is>
-          <t>CUSTOM_OFFERING: Yes — bespoke service, upload images and references, in-house studio — /custom-bespoke/</t>
+          <t>CUSTOM_OFFERING: Yes — "Custom Rugs" (resize/recolor existing design) and "Bespoke Rugs" (new design) — /custom-bespoke</t>
         </is>
       </c>
       <c r="AO47" s="2" t="inlineStr">
         <is>
-          <t>VISUAL_TOOL: Advanced — "Custom Rug Designer" portal, 100+ rugs, color and size — us.therugcompany.com/build-your-own/</t>
+          <t>VISUAL_TOOL: Basic — guided questionnaire ("Personal Curation") with AI chat stylist, no live preview/render — /personal-curation</t>
         </is>
       </c>
       <c r="AP47" s="2" t="inlineStr">
         <is>
-          <t>HOOK: "Climbing Leopard by Diane von Furstenberg"; Alexander McQueen "Monarch" pattern — /designers/</t>
+          <t>"Custom &amp; Bespoke (22+ weeks)" lead-time service, plus AI Stylist chat for personalized rug discovery — /custom-bespoke, /personal-curation</t>
         </is>
       </c>
       <c r="AQ47" s="2" t="inlineStr">
         <is>
-          <t>CLIENT_PROOF: Diane von Furstenberg, Alexander McQueen, Kelly Wearstler collaborations — /designers/</t>
-        </is>
-      </c>
-      <c r="AR47" s="6" t="inlineStr">
+          <t>CLIENT_PROOF: Designer collaborations named (Vivienne Westwood, Paul Smith, Kelly Wearstler, Christopher Kane) — /designers</t>
+        </is>
+      </c>
+      <c r="AR47" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS47" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT47" s="6" t="inlineStr">
         <is>
           <t>HOLD - PARKED</t>
         </is>
       </c>
-      <c r="AS47" s="4" t="inlineStr">
+      <c r="AU47" s="4" t="inlineStr">
         <is>
           <t>Parked niche (rugs / stained glass) — needs Abdullah on rendering fit before send</t>
         </is>
       </c>
-      <c r="AT47" s="4" t="inlineStr">
+      <c r="AV47" s="4" t="inlineStr">
         <is>
           <t>your Custom Rug Designer, and the bespoke queue</t>
         </is>
       </c>
-      <c r="AU47" s="5" t="inlineStr">
+      <c r="AW47" s="5" t="inlineStr">
         <is>
           <t>Emma,
 The Custom Rug Designer put you ahead of the category. A hundred designs, colour and size, all self serve.
@@ -10907,12 +11421,12 @@
 Worth seeing as a front end to the bespoke route?</t>
         </is>
       </c>
-      <c r="AV47" s="4" t="inlineStr">
+      <c r="AX47" s="4" t="inlineStr">
         <is>
           <t>the portal configures, the studio creates</t>
         </is>
       </c>
-      <c r="AW47" s="5" t="inlineStr">
+      <c r="AY47" s="5" t="inlineStr">
         <is>
           <t>Emma,
 Where it fits, plainly. Your portal configures. Your studio creates. The gap between them is people, and it grows with demand rather than shrinking.
@@ -10920,12 +11434,12 @@
 Glad to show you how it works. Twenty minutes, screen share.</t>
         </is>
       </c>
-      <c r="AX47" s="4" t="inlineStr">
+      <c r="AZ47" s="4" t="inlineStr">
         <is>
           <t>is the bespoke gap worth closing?</t>
         </is>
       </c>
-      <c r="AY47" s="5" t="inlineStr">
+      <c r="BA47" s="5" t="inlineStr">
         <is>
           <t>Emma,
 Wrapping this up.
@@ -11133,22 +11647,32 @@
           <t>CLIENT_PROOF: Not found</t>
         </is>
       </c>
-      <c r="AR48" s="6" t="inlineStr">
+      <c r="AR48" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS48" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT48" s="6" t="inlineStr">
         <is>
           <t>HOLD - PARKED</t>
         </is>
       </c>
-      <c r="AS48" s="4" t="inlineStr">
+      <c r="AU48" s="4" t="inlineStr">
         <is>
           <t>Parked niche (rugs / stained glass) — needs Abdullah on rendering fit before send</t>
         </is>
       </c>
-      <c r="AT48" s="4" t="inlineStr">
+      <c r="AV48" s="4" t="inlineStr">
         <is>
           <t>any size, any shape, any colour</t>
         </is>
       </c>
-      <c r="AU48" s="5" t="inlineStr">
+      <c r="AW48" s="5" t="inlineStr">
         <is>
           <t>Kayla,
 "Any size, any shape, any colour, we will bring your vision to life" is a strong promise, and your pickers cover size, material and weave well.
@@ -11157,12 +11681,12 @@
 Can I send it over?</t>
         </is>
       </c>
-      <c r="AV48" s="4" t="inlineStr">
+      <c r="AX48" s="4" t="inlineStr">
         <is>
           <t>fewer rounds before production</t>
         </is>
       </c>
-      <c r="AW48" s="5" t="inlineStr">
+      <c r="AY48" s="5" t="inlineStr">
         <is>
           <t>Kayla,
 From a production seat the value is simple: fewer rounds.
@@ -11170,12 +11694,12 @@
 ai.mecartworks.com, free, five previews, email code only.</t>
         </is>
       </c>
-      <c r="AX48" s="4" t="inlineStr">
+      <c r="AZ48" s="4" t="inlineStr">
         <is>
           <t>do custom briefs arrive clear?</t>
         </is>
       </c>
-      <c r="AY48" s="5" t="inlineStr">
+      <c r="BA48" s="5" t="inlineStr">
         <is>
           <t>Kayla,
 That is the last of it from me.
@@ -11348,48 +11872,62 @@
           <t>kruthika@rugartisan.com</t>
         </is>
       </c>
-      <c r="AL49" s="2" t="inlineStr"/>
+      <c r="AL49" s="2" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
       <c r="AM49" s="2" t="inlineStr">
         <is>
-          <t>SITE_MATCH: Match — custom handmade area rugs match company</t>
+          <t>SITE_MATCH: Match — brand, custom/bespoke rug products align with company</t>
         </is>
       </c>
       <c r="AN49" s="2" t="inlineStr">
         <is>
-          <t>CUSTOM_OFFERING: Yes — bespoke designs sent to customer for approval; any size, shape — /bespoke</t>
+          <t>CUSTOM_OFFERING: Yes — "custom color, material, shape, and sizes" bespoke rugs — /bespoke</t>
         </is>
       </c>
       <c r="AO49" s="2" t="inlineStr">
         <is>
-          <t>VISUAL_TOOL: Advanced — "customization software", custom color library, texture and shape selection — /personalise.html</t>
+          <t>VISUAL_TOOL: Advanced — step-by-step design tool with room-setting visualization — /personalise.html</t>
         </is>
       </c>
       <c r="AP49" s="2" t="inlineStr">
         <is>
-          <t>HOOK: "around 300 pre-set color combinations to choose from for each custom rug design" — /personalise.html</t>
+          <t>"Design your own rug and see it in your room" - interactive 6-step personalization tool — /personalise.html</t>
         </is>
       </c>
       <c r="AQ49" s="2" t="inlineStr">
         <is>
-          <t>CLIENT_PROOF: Not found</t>
-        </is>
-      </c>
-      <c r="AR49" s="6" t="inlineStr">
+          <t>Not found — projects page had no content; press page lists media outlets only, no named client venues — /press, /projects</t>
+        </is>
+      </c>
+      <c r="AR49" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS49" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT49" s="6" t="inlineStr">
         <is>
           <t>HOLD - PARKED</t>
         </is>
       </c>
-      <c r="AS49" s="4" t="inlineStr">
+      <c r="AU49" s="4" t="inlineStr">
         <is>
           <t>Parked niche (rugs / stained glass) — needs Abdullah on rendering fit before send</t>
         </is>
       </c>
-      <c r="AT49" s="4" t="inlineStr">
+      <c r="AV49" s="4" t="inlineStr">
         <is>
           <t>300 colourways, and the design nobody drew</t>
         </is>
       </c>
-      <c r="AU49" s="5" t="inlineStr">
+      <c r="AW49" s="5" t="inlineStr">
         <is>
           <t>Kruthika,
 Rug Artisan's customisation software with 300 preset colourways per design is further than most of this industry has got.
@@ -11398,12 +11936,12 @@
 Worth seeing where it sits before your designers pick it up?</t>
         </is>
       </c>
-      <c r="AV49" s="4" t="inlineStr">
+      <c r="AX49" s="4" t="inlineStr">
         <is>
           <t>variation, versus designs that do not exist yet</t>
         </is>
       </c>
-      <c r="AW49" s="5" t="inlineStr">
+      <c r="AY49" s="5" t="inlineStr">
         <is>
           <t>Kruthika,
 Put simply. Your software handles variation on designs you already have. This handles designs that do not exist yet.
@@ -11411,12 +11949,12 @@
 Happy to walk you through it. Twenty minutes.</t>
         </is>
       </c>
-      <c r="AX49" s="4" t="inlineStr">
+      <c r="AZ49" s="4" t="inlineStr">
         <is>
           <t>is the round trip a cost, or just the work?</t>
         </is>
       </c>
-      <c r="AY49" s="5" t="inlineStr">
+      <c r="BA49" s="5" t="inlineStr">
         <is>
           <t>Kruthika,
 Last one, promise.
@@ -11592,48 +12130,62 @@
           <t>hope@theperfectrug.com</t>
         </is>
       </c>
-      <c r="AL50" s="2" t="inlineStr"/>
+      <c r="AL50" s="2" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
       <c r="AM50" s="2" t="inlineStr">
         <is>
-          <t>SITE_MATCH: Match — custom-sized rugs match company</t>
+          <t>SITE_MATCH: Match — brand and custom rug products align with company</t>
         </is>
       </c>
       <c r="AN50" s="2" t="inlineStr">
         <is>
-          <t>CUSTOM_OFFERING: Yes — select size, material, color, border; 1000+ materials; custom shapes — /shop-custom-area-rugs</t>
+          <t>CUSTOM_OFFERING: Yes — custom sizing "down to the inch", shapes, materials, borders — /perfectfit</t>
         </is>
       </c>
       <c r="AO50" s="2" t="inlineStr">
         <is>
-          <t>VISUAL_TOOL: Basic — structured size/material/color picker plus "PerfectFit"; unverified — /perfectfit</t>
+          <t>VISUAL_TOOL: Basic — stepwise picker with size sliders, no live rendering/preview — /perfectfit</t>
         </is>
       </c>
       <c r="AP50" s="2" t="inlineStr">
         <is>
-          <t>HOOK: "custom-made rugs at reasonable everyday prices rather than custom prices" — /about</t>
+          <t>HOOK: "PerfectFit by The Perfect Rug" — 4-step custom rug configurator (Material, Color, Shape/Size, Border) — /perfectfit</t>
         </is>
       </c>
       <c r="AQ50" s="2" t="inlineStr">
         <is>
-          <t>CLIENT_PROOF: Not found</t>
-        </is>
-      </c>
-      <c r="AR50" s="6" t="inlineStr">
+          <t>CLIENT_PROOF: Featured designer "Shannon Russo Interiors" (NY-based firm) — /shannon-russo-interiors</t>
+        </is>
+      </c>
+      <c r="AR50" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS50" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT50" s="6" t="inlineStr">
         <is>
           <t>HOLD - PARKED</t>
         </is>
       </c>
-      <c r="AS50" s="4" t="inlineStr">
+      <c r="AU50" s="4" t="inlineStr">
         <is>
           <t>Parked niche (rugs / stained glass) — needs Abdullah on rendering fit before send</t>
         </is>
       </c>
-      <c r="AT50" s="4" t="inlineStr">
+      <c r="AV50" s="4" t="inlineStr">
         <is>
           <t>custom prices versus everyday prices</t>
         </is>
       </c>
-      <c r="AU50" s="5" t="inlineStr">
+      <c r="AW50" s="5" t="inlineStr">
         <is>
           <t>Hope,
 The Perfect Rug's whole position is custom at everyday prices rather than custom prices, and you back it with free design consultations.
@@ -11642,12 +12194,12 @@
 Shall I send you the link?</t>
         </is>
       </c>
-      <c r="AV50" s="4" t="inlineStr">
+      <c r="AX50" s="4" t="inlineStr">
         <is>
           <t>content your customers make for you</t>
         </is>
       </c>
-      <c r="AW50" s="5" t="inlineStr">
+      <c r="AY50" s="5" t="inlineStr">
         <is>
           <t>Hope,
 For a content and partnerships role there is a second angle worth more than the first.
@@ -11655,12 +12207,12 @@
 ai.mecartworks.com. Five free previews, no signup wall.</t>
         </is>
       </c>
-      <c r="AX50" s="4" t="inlineStr">
+      <c r="AZ50" s="4" t="inlineStr">
         <is>
           <t>do the consultations still scale?</t>
         </is>
       </c>
-      <c r="AY50" s="5" t="inlineStr">
+      <c r="BA50" s="5" t="inlineStr">
         <is>
           <t>Hope,
 I will park this now.
@@ -11866,22 +12418,32 @@
           <t>CLIENT_PROOF: Alison Lind Interiors, Annali Interiors, Gregory DelliCarpini Jr., @gindesigngroup (Austin TX), @marshallinteriors (San Rafael CA) — /pages/lookbook</t>
         </is>
       </c>
-      <c r="AR51" s="6" t="inlineStr">
+      <c r="AR51" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS51" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT51" s="6" t="inlineStr">
         <is>
           <t>HOLD - PARKED</t>
         </is>
       </c>
-      <c r="AS51" s="4" t="inlineStr">
+      <c r="AU51" s="4" t="inlineStr">
         <is>
           <t>Parked niche (rugs / stained glass) — needs Abdullah on rendering fit before send</t>
         </is>
       </c>
-      <c r="AT51" s="4" t="inlineStr">
+      <c r="AV51" s="4" t="inlineStr">
         <is>
           <t>The Rug Plan, and the customizer</t>
         </is>
       </c>
-      <c r="AU51" s="5" t="inlineStr">
+      <c r="AW51" s="5" t="inlineStr">
         <is>
           <t>Cassie,
 Jubi runs both a real time customizer with 1,200 shades and The Rug Plan, where your studio replies by hand with rugs chosen for someone's room.
@@ -11890,12 +12452,12 @@
 Worth a look as a front end to The Rug Plan?</t>
         </is>
       </c>
-      <c r="AV51" s="4" t="inlineStr">
+      <c r="AX51" s="4" t="inlineStr">
         <is>
           <t>what does The Rug Plan cost per request?</t>
         </is>
       </c>
-      <c r="AW51" s="5" t="inlineStr">
+      <c r="AY51" s="5" t="inlineStr">
         <is>
           <t>Cassie,
 As a founder you will price this in about ten seconds. What does The Rug Plan cost you per request, and what share convert?
@@ -11903,12 +12465,12 @@
 The tool is ai.mecartworks.com. Email code, five previews, free.</t>
         </is>
       </c>
-      <c r="AX51" s="4" t="inlineStr">
+      <c r="AZ51" s="4" t="inlineStr">
         <is>
           <t>what did you learn building yours?</t>
         </is>
       </c>
-      <c r="AY51" s="5" t="inlineStr">
+      <c r="BA51" s="5" t="inlineStr">
         <is>
           <t>Cassie,
 Final one from me.
@@ -12096,22 +12658,32 @@
           <t>CLIENT_PROOF: Pasadena Residence, Wilshire Boulevard Temple, Church of the Resurrection, Unity Temple (Frank Lloyd Wright restoration), St. Paul's Cathedral San Diego; partners Hilton, Gensler, Fender, Ace Hotel, Nickelodeon, JPL — /projects</t>
         </is>
       </c>
-      <c r="AR52" s="6" t="inlineStr">
+      <c r="AR52" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS52" s="2" t="inlineStr">
+        <is>
+          <t>found on SMB fallback</t>
+        </is>
+      </c>
+      <c r="AT52" s="6" t="inlineStr">
         <is>
           <t>HOLD - PARKED</t>
         </is>
       </c>
-      <c r="AS52" s="4" t="inlineStr">
+      <c r="AU52" s="4" t="inlineStr">
         <is>
           <t>Parked niche (rugs / stained glass) — needs Abdullah on rendering fit before send</t>
         </is>
       </c>
-      <c r="AT52" s="4" t="inlineStr">
+      <c r="AV52" s="4" t="inlineStr">
         <is>
           <t>the renaissance piece</t>
         </is>
       </c>
-      <c r="AU52" s="5" t="inlineStr">
+      <c r="AW52" s="5" t="inlineStr">
         <is>
           <t>David,
 The press piece calling stained glass a renaissance and naming Judson as the studio fuelling it is a good problem to have. It brings people who have never ordered stained glass before.
@@ -12120,12 +12692,12 @@
 Would ten minutes be useful?</t>
         </is>
       </c>
-      <c r="AV52" s="4" t="inlineStr">
+      <c r="AX52" s="4" t="inlineStr">
         <is>
           <t>sorting the serious from the curious</t>
         </is>
       </c>
-      <c r="AW52" s="5" t="inlineStr">
+      <c r="AY52" s="5" t="inlineStr">
         <is>
           <t>David,
 To be clear about what it is and is not. It will not design a Judson window. It gets a client to a direction on palette, subject and density before your designers invest hours.
@@ -12133,12 +12705,12 @@
 ai.mecartworks.com, free, five previews, email code.</t>
         </is>
       </c>
-      <c r="AX52" s="4" t="inlineStr">
+      <c r="AZ52" s="4" t="inlineStr">
         <is>
           <t>Unity Temple does not need my help</t>
         </is>
       </c>
-      <c r="AY52" s="5" t="inlineStr">
+      <c r="BA52" s="5" t="inlineStr">
         <is>
           <t>David,
 I will stop bothering you.
@@ -12340,22 +12912,32 @@
           <t>CLIENT_PROOF: Not found — projects shown but venues unnamed — /projects</t>
         </is>
       </c>
-      <c r="AR53" s="6" t="inlineStr">
+      <c r="AR53" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS53" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT53" s="6" t="inlineStr">
         <is>
           <t>HOLD - PARKED</t>
         </is>
       </c>
-      <c r="AS53" s="4" t="inlineStr">
+      <c r="AU53" s="4" t="inlineStr">
         <is>
           <t>Parked niche (rugs / stained glass) — needs Abdullah on rendering fit before send</t>
         </is>
       </c>
-      <c r="AT53" s="4" t="inlineStr">
+      <c r="AV53" s="4" t="inlineStr">
         <is>
           <t>15,000 buildings</t>
         </is>
       </c>
-      <c r="AU53" s="5" t="inlineStr">
+      <c r="AW53" s="5" t="inlineStr">
         <is>
           <t>Kathy,
 Windows in more than 15,000 buildings is a number very few studios can put on a page.
@@ -12364,12 +12946,12 @@
 Would fifteen minutes be useful?</t>
         </is>
       </c>
-      <c r="AV53" s="4" t="inlineStr">
+      <c r="AX53" s="4" t="inlineStr">
         <is>
           <t>the committee that has to agree</t>
         </is>
       </c>
-      <c r="AW53" s="5" t="inlineStr">
+      <c r="AY53" s="5" t="inlineStr">
         <is>
           <t>Kathy,
 The committee point is the one I would stand behind. When everyone in the room looks at the same image, the decision happens in that meeting rather than the one after it.
@@ -12377,12 +12959,12 @@
 ai.mecartworks.com, free, five previews, email code only. Two minutes will tell you whether it is usable at your standard.</t>
         </is>
       </c>
-      <c r="AX53" s="4" t="inlineStr">
+      <c r="AZ53" s="4" t="inlineStr">
         <is>
           <t>no is a reasonable answer here</t>
         </is>
       </c>
-      <c r="AY53" s="5" t="inlineStr">
+      <c r="BA53" s="5" t="inlineStr">
         <is>
           <t>Kathy,
 Leaving this alone now.
@@ -12565,22 +13147,32 @@
           <t>CLIENT_PROOF: Not found — claims "thousands of only the finest projects" but names none</t>
         </is>
       </c>
-      <c r="AR54" s="6" t="inlineStr">
+      <c r="AR54" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS54" s="2" t="inlineStr">
+        <is>
+          <t>found on SMB fallback</t>
+        </is>
+      </c>
+      <c r="AT54" s="6" t="inlineStr">
         <is>
           <t>HOLD - PARKED</t>
         </is>
       </c>
-      <c r="AS54" s="4" t="inlineStr">
+      <c r="AU54" s="4" t="inlineStr">
         <is>
           <t>Parked niche (rugs / stained glass) — needs Abdullah on rendering fit before send</t>
         </is>
       </c>
-      <c r="AT54" s="4" t="inlineStr">
+      <c r="AV54" s="4" t="inlineStr">
         <is>
           <t>four generations, one slow step</t>
         </is>
       </c>
-      <c r="AU54" s="5" t="inlineStr">
+      <c r="AW54" s="5" t="inlineStr">
         <is>
           <t>Gary,
 A hundred and one years and four generations. Franklin has outlasted most of the industry it started in.
@@ -12589,12 +13181,12 @@
 Worth a quick call to find out?</t>
         </is>
       </c>
-      <c r="AV54" s="4" t="inlineStr">
+      <c r="AX54" s="4" t="inlineStr">
         <is>
           <t>making custom cheaper to quote</t>
         </is>
       </c>
-      <c r="AW54" s="5" t="inlineStr">
+      <c r="AY54" s="5" t="inlineStr">
         <is>
           <t>Gary,
 Being realistic about your business. Most of Franklin's revenue is supply, and custom sits alongside it.
@@ -12602,12 +13194,12 @@
 ai.mecartworks.com, five free previews, email code only.</t>
         </is>
       </c>
-      <c r="AX54" s="4" t="inlineStr">
+      <c r="AZ54" s="4" t="inlineStr">
         <is>
           <t>since 1924, without my advice</t>
         </is>
       </c>
-      <c r="AY54" s="5" t="inlineStr">
+      <c r="BA54" s="5" t="inlineStr">
         <is>
           <t>Gary,
 Last email on this.
@@ -12757,22 +13349,32 @@
           <t>CLIENT_PROOF: Not found — first-name testimonials only</t>
         </is>
       </c>
-      <c r="AR55" s="3" t="inlineStr">
+      <c r="AR55" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="AS55" s="2" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
         <is>
           <t>NO EMAIL</t>
         </is>
       </c>
-      <c r="AS55" s="4" t="inlineStr">
+      <c r="AU55" s="4" t="inlineStr">
         <is>
           <t>No work email on this row — LinkedIn or enrichment needed</t>
         </is>
       </c>
-      <c r="AT55" s="4" t="inlineStr"/>
-      <c r="AU55" s="5" t="inlineStr"/>
       <c r="AV55" s="4" t="inlineStr"/>
       <c r="AW55" s="5" t="inlineStr"/>
       <c r="AX55" s="4" t="inlineStr"/>
       <c r="AY55" s="5" t="inlineStr"/>
+      <c r="AZ55" s="4" t="inlineStr"/>
+      <c r="BA55" s="5" t="inlineStr"/>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
@@ -12932,48 +13534,62 @@
           <t>theresa@tlcstainedglass.com</t>
         </is>
       </c>
-      <c r="AL56" s="2" t="inlineStr"/>
+      <c r="AL56" s="2" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
       <c r="AM56" s="2" t="inlineStr">
         <is>
-          <t>SITE_MATCH: Match — "Custom transoms, cabinet doors, privacy windows, hanging panels" — /commissions/</t>
+          <t>SITE_MATCH: Match — stained glass studio/gallery matches company name and industry</t>
         </is>
       </c>
       <c r="AN56" s="2" t="inlineStr">
         <is>
-          <t>CUSTOM_OFFERING: Yes — same phrase — /commissions/</t>
+          <t>CUSTOM_OFFERING: Yes — “custom stained glass creations” tailored to client style — /commissions</t>
         </is>
       </c>
       <c r="AO56" s="2" t="inlineStr">
         <is>
-          <t>VISUAL_TOOL: Basic — portfolio thumbnails only — /work/</t>
+          <t>VISUAL_TOOL: None — no configurator or design preview tool found — /commissions</t>
         </is>
       </c>
       <c r="AP56" s="2" t="inlineStr">
         <is>
-          <t>HOOK: "Dabble in a 1400-year-old art form" — workshops — /classes-and-workshops/</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="AQ56" s="2" t="inlineStr">
         <is>
-          <t>CLIENT_PROOF: Not found — an HGTV feature is mentioned but not detailed</t>
-        </is>
-      </c>
-      <c r="AR56" s="3" t="inlineStr">
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AR56" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS56" s="2" t="inlineStr">
+        <is>
+          <t>found on SMB fallback</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
         </is>
       </c>
-      <c r="AS56" s="4" t="inlineStr">
+      <c r="AU56" s="4" t="inlineStr">
         <is>
           <t>Audit verdict DROP — One-person studio. Same two failures as row 47</t>
         </is>
       </c>
-      <c r="AT56" s="4" t="inlineStr"/>
-      <c r="AU56" s="5" t="inlineStr"/>
       <c r="AV56" s="4" t="inlineStr"/>
       <c r="AW56" s="5" t="inlineStr"/>
       <c r="AX56" s="4" t="inlineStr"/>
       <c r="AY56" s="5" t="inlineStr"/>
+      <c r="AZ56" s="4" t="inlineStr"/>
+      <c r="BA56" s="5" t="inlineStr"/>
     </row>
     <row r="57" ht="92" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
@@ -13167,22 +13783,32 @@
           <t>CLIENT_PROOF: Not found — inspiration galleries by room type, no attribution</t>
         </is>
       </c>
-      <c r="AR57" s="7" t="inlineStr">
+      <c r="AR57" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS57" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT57" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS57" s="4" t="inlineStr">
+      <c r="AU57" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT57" s="4" t="inlineStr">
+      <c r="AV57" s="4" t="inlineStr">
         <is>
           <t>a set builder for dinnerware, not for tile</t>
         </is>
       </c>
-      <c r="AU57" s="5" t="inlineStr">
+      <c r="AW57" s="5" t="inlineStr">
         <is>
           <t>Anna,
 Heath built a set builder for dinnerware. Start building, save 10%, watch it come together.
@@ -13191,12 +13817,12 @@
 Worth seeing the parallel?</t>
         </is>
       </c>
-      <c r="AV57" s="4" t="inlineStr">
+      <c r="AX57" s="4" t="inlineStr">
         <is>
           <t>Seeds of Summer, on someone's actual wall</t>
         </is>
       </c>
-      <c r="AW57" s="5" t="inlineStr">
+      <c r="AY57" s="5" t="inlineStr">
         <is>
           <t>Anna,
 Seeds of Summer is the case in point. Moodier pinks and reds, launched in April, and the hard part is getting someone to picture a whole wall of it from a swatch.
@@ -13204,12 +13830,12 @@
 ai.mecartworks.com, free, five previews, email code only.</t>
         </is>
       </c>
-      <c r="AX57" s="4" t="inlineStr">
+      <c r="AZ57" s="4" t="inlineStr">
         <is>
           <t>one for the list</t>
         </is>
       </c>
-      <c r="AY57" s="5" t="inlineStr">
+      <c r="BA57" s="5" t="inlineStr">
         <is>
           <t>Anna,
 I will drop it here.
@@ -13353,48 +13979,62 @@
         </is>
       </c>
       <c r="AK58" s="2" t="inlineStr"/>
-      <c r="AL58" s="2" t="inlineStr"/>
+      <c r="AL58" s="2" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
       <c r="AM58" s="2" t="inlineStr">
         <is>
-          <t>SITE_MATCH: Match — "Native Tile uses time-honored methods, refined with years of experience, to create tile infused with unique inspiration" — /</t>
+          <t>SITE_MATCH: Match — handmade ceramic tile manufacturer matches Native Tile</t>
         </is>
       </c>
       <c r="AN58" s="2" t="inlineStr">
         <is>
-          <t>CUSTOM_OFFERING: Yes — "Let us create tile to help beautify your living space" — /</t>
+          <t>CUSTOM_OFFERING: Yes — choose technique series, glaze/color, and patterns; call to customize — /our-collection</t>
         </is>
       </c>
       <c r="AO58" s="2" t="inlineStr">
         <is>
-          <t>VISUAL_TOOL: None — static galleries and case study images — /our-collection/, /case-studies/</t>
+          <t>VISUAL_TOOL: None — PDF catalogs only, no interactive configurator — /our-collection</t>
         </is>
       </c>
       <c r="AP58" s="2" t="inlineStr">
         <is>
-          <t>HOOK: Voyage LA interview, Diana Mausser: "Every aspect of our tile manufacturing is done at our studio in Old Torrance, so we are in control of...quality" — external press</t>
+          <t>"Over 1,100 patterns" across technique series like Malibu, Vintage California, Tunisian, Relief — /our-collection</t>
         </is>
       </c>
       <c r="AQ58" s="2" t="inlineStr">
         <is>
-          <t>CLIENT_PROOF: Eight named residential projects (Bauer/Muller, Casa de Sueños, Gibbings, Iida, Rudolph, Shoemaker, Smart residences) plus Four Seasons Biltmore Hotel — /case-studies/</t>
-        </is>
-      </c>
-      <c r="AR58" s="3" t="inlineStr">
+          <t>Four Seasons Biltmore Hotel — /case-studies</t>
+        </is>
+      </c>
+      <c r="AR58" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="AS58" s="2" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+      <c r="AT58" s="3" t="inlineStr">
         <is>
           <t>NO EMAIL</t>
         </is>
       </c>
-      <c r="AS58" s="4" t="inlineStr">
+      <c r="AU58" s="4" t="inlineStr">
         <is>
           <t>No work email on this row — LinkedIn or enrichment needed</t>
         </is>
       </c>
-      <c r="AT58" s="4" t="inlineStr"/>
-      <c r="AU58" s="5" t="inlineStr"/>
       <c r="AV58" s="4" t="inlineStr"/>
       <c r="AW58" s="5" t="inlineStr"/>
       <c r="AX58" s="4" t="inlineStr"/>
       <c r="AY58" s="5" t="inlineStr"/>
+      <c r="AZ58" s="4" t="inlineStr"/>
+      <c r="BA58" s="5" t="inlineStr"/>
     </row>
     <row r="59" ht="92" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
@@ -13558,48 +14198,62 @@
           <t>jamie@ziatile.com</t>
         </is>
       </c>
-      <c r="AL59" s="2" t="inlineStr"/>
+      <c r="AL59" s="2" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
       <c r="AM59" s="2" t="inlineStr">
         <is>
-          <t>SITE_MATCH: Match — "Handmade Artisanal Tile and Stone from Around the World" — zellige, ceramics, marble, terrazzo — /collections/all</t>
+          <t>SITE_MATCH: Match — brand and tile products align with Zia Tile</t>
         </is>
       </c>
       <c r="AN59" s="2" t="inlineStr">
         <is>
-          <t>CUSTOM_OFFERING: No — curated pre-designed collections; no custom-configuration language anywhere in nav or product pages</t>
+          <t>CUSTOM_OFFERING: Unclear — no explicit custom sizes/colors mentioned; handmade Zellige varies — /collections/zellige</t>
         </is>
       </c>
       <c r="AO59" s="2" t="inlineStr">
         <is>
-          <t>VISUAL_TOOL: Basic — colour, material, shape and space filters — /collections/all</t>
+          <t>VISUAL_TOOL: Basic — filter/browse by color, pattern, shape (no live preview) — /collections/zellige</t>
         </is>
       </c>
       <c r="AP59" s="2" t="inlineStr">
         <is>
-          <t>HOOK: "All designed in Los Angeles and crafted by artisans around the globe" — /collections/all</t>
+          <t>"Field Trip: Japan" collection — /collections/all (highlighted line)</t>
         </is>
       </c>
       <c r="AQ59" s="2" t="inlineStr">
         <is>
-          <t>CLIENT_PROOF: Not found</t>
-        </is>
-      </c>
-      <c r="AR59" s="7" t="inlineStr">
+          <t>CLIENT_PROOF: Not found — no named clients/venues on Hospitality or Trade pages</t>
+        </is>
+      </c>
+      <c r="AR59" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS59" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT59" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS59" s="4" t="inlineStr">
+      <c r="AU59" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT59" s="4" t="inlineStr">
+      <c r="AV59" s="4" t="inlineStr">
         <is>
           <t>designed in LA, crafted everywhere</t>
         </is>
       </c>
-      <c r="AU59" s="5" t="inlineStr">
+      <c r="AW59" s="5" t="inlineStr">
         <is>
           <t>Jamie,
 Zia's line, designed in Los Angeles and crafted by artisans around the globe, is a curated position rather than a made to order one. The filters on the site reflect that and they work well.
@@ -13608,12 +14262,12 @@
 Worth two minutes of a marketing director's time?</t>
         </is>
       </c>
-      <c r="AV59" s="4" t="inlineStr">
+      <c r="AX59" s="4" t="inlineStr">
         <is>
           <t>a discovery tool, not a design service</t>
         </is>
       </c>
-      <c r="AW59" s="5" t="inlineStr">
+      <c r="AY59" s="5" t="inlineStr">
         <is>
           <t>Jamie,
 To be clear, I am not suggesting Zia moves into custom. The curated position is the brand and it is working.
@@ -13621,12 +14275,12 @@
 ai.mecartworks.com, five previews, email code, no subscription.</t>
         </is>
       </c>
-      <c r="AX59" s="4" t="inlineStr">
+      <c r="AZ59" s="4" t="inlineStr">
         <is>
           <t>maybe the filters already do this</t>
         </is>
       </c>
-      <c r="AY59" s="5" t="inlineStr">
+      <c r="BA59" s="5" t="inlineStr">
         <is>
           <t>Jamie,
 One last note.
@@ -13840,22 +14494,32 @@
           <t>CLIENT_PROOF: Not found — designer testimonials (Mark, Natalie, Jeff, Stephanie, J Ray Design Studio) but no named venue or project</t>
         </is>
       </c>
-      <c r="AR60" s="7" t="inlineStr">
+      <c r="AR60" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS60" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT60" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS60" s="4" t="inlineStr">
+      <c r="AU60" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT60" s="4" t="inlineStr">
+      <c r="AV60" s="4" t="inlineStr">
         <is>
           <t>the Gilded print in Reflections</t>
         </is>
       </c>
-      <c r="AU60" s="5" t="inlineStr">
+      <c r="AW60" s="5" t="inlineStr">
         <is>
           <t>Lindsay,
 The Gilded print technology in the Reflections Collection, with fine gold accents and reflective detail, is the kind of thing that has to be seen rather than described. A photo does not carry it.
@@ -13864,12 +14528,12 @@
 Worth 15 minutes?</t>
         </is>
       </c>
-      <c r="AV60" s="4" t="inlineStr">
+      <c r="AX60" s="4" t="inlineStr">
         <is>
           <t>for a 15 person studio, rounds are margin</t>
         </is>
       </c>
-      <c r="AW60" s="5" t="inlineStr">
+      <c r="AY60" s="5" t="inlineStr">
         <is>
           <t>Lindsay,
 What it is worth to a fifteen person studio. Rounds are your margin.
@@ -13877,12 +14541,12 @@
 It lives at ai.mecartworks.com. Five free previews, no password. Two minutes will tell you whether it does the Gilded finish justice, and I suspect that is the real test.</t>
         </is>
       </c>
-      <c r="AX60" s="4" t="inlineStr">
+      <c r="AZ60" s="4" t="inlineStr">
         <is>
           <t>every tool has to earn its place</t>
         </is>
       </c>
-      <c r="AY60" s="5" t="inlineStr">
+      <c r="BA60" s="5" t="inlineStr">
         <is>
           <t>Lindsay,
 Closing the loop and stopping.
@@ -14082,22 +14746,32 @@
           <t>CLIENT_PROOF: Hard Rock Hotel Casino and Spa, Philadelphia Wings, Rubin Creative; X-Men Times Square billboard, Madonna concert advertising at The Met Philadelphia — /</t>
         </is>
       </c>
-      <c r="AR61" s="3" t="inlineStr">
+      <c r="AR61" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS61" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT61" s="3" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
         </is>
       </c>
-      <c r="AS61" s="4" t="inlineStr">
+      <c r="AU61" s="4" t="inlineStr">
         <is>
           <t>Audit verdict DROP — Signage/print shop. Wrong buyer, wrong workflow</t>
         </is>
       </c>
-      <c r="AT61" s="4" t="inlineStr"/>
-      <c r="AU61" s="5" t="inlineStr"/>
       <c r="AV61" s="4" t="inlineStr"/>
       <c r="AW61" s="5" t="inlineStr"/>
       <c r="AX61" s="4" t="inlineStr"/>
       <c r="AY61" s="5" t="inlineStr"/>
+      <c r="AZ61" s="4" t="inlineStr"/>
+      <c r="BA61" s="5" t="inlineStr"/>
     </row>
     <row r="62" ht="92" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -14269,48 +14943,62 @@
           <t>hneurer@areaenvironments.com</t>
         </is>
       </c>
-      <c r="AL62" s="2" t="inlineStr"/>
+      <c r="AL62" s="2" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
       <c r="AM62" s="2" t="inlineStr">
         <is>
-          <t>SITE_MATCH: Match — "Fine art wallcoverings for commercial and residential spaces" — /</t>
+          <t>SITE_MATCH: Match — brand and fine art wallcoverings align with company</t>
         </is>
       </c>
       <c r="AN62" s="2" t="inlineStr">
         <is>
-          <t>CUSTOM_OFFERING: Yes — "Can I bring my own artwork? Yes. If you have a piece, a photograph, or a concept, we'll build the wallcovering around it" — /faqs</t>
+          <t>CUSTOM_OFFERING: Yes — "Commissioned Art, Client-Provided Art, Catalog Alterations" offered — /custom</t>
         </is>
       </c>
       <c r="AO62" s="2" t="inlineStr">
         <is>
-          <t>VISUAL_TOOL: None — galleries and collections, no preview or configurator — /ordersamples</t>
+          <t>VISUAL_TOOL: None — custom design handled via consultation/file submission, no online configurator — /custom</t>
         </is>
       </c>
       <c r="AP62" s="2" t="inlineStr">
         <is>
-          <t>HOOK: "Every artist earns a royalty on every wallcovering sold in their name. When you specify an Area wallcovering the person who created the art gets paid" — /faqs</t>
+          <t>HOOK: "Custom wallpaper for Christoph Niemann exhibition at ZieherSmith Gallery, Nashville" — /custom</t>
         </is>
       </c>
       <c r="AQ62" s="2" t="inlineStr">
         <is>
-          <t>CLIENT_PROOF: Not found — Residential and Commercial portfolio categories, no named projects — /residential, /commercial</t>
-        </is>
-      </c>
-      <c r="AR62" s="7" t="inlineStr">
+          <t>CLIENT_PROOF: Dropbox Headquarters, Equinox Hotel NYC, Radisson Hotel Nashville — /commercial</t>
+        </is>
+      </c>
+      <c r="AR62" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS62" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT62" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS62" s="4" t="inlineStr">
+      <c r="AU62" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT62" s="4" t="inlineStr">
+      <c r="AV62" s="4" t="inlineStr">
         <is>
           <t>approving a wall they have never seen</t>
         </is>
       </c>
-      <c r="AU62" s="5" t="inlineStr">
+      <c r="AW62" s="5" t="inlineStr">
         <is>
           <t>Heather,
 Area sells to the trade only, and your FAQ says if someone brings a piece or a photograph, you will build the wallcovering around it.
@@ -14319,25 +15007,25 @@
 We built the AI studio MEC Artworks put on their site. Want me to run one of your collections through it and send you the result?</t>
         </is>
       </c>
-      <c r="AV62" s="4" t="inlineStr">
+      <c r="AX62" s="4" t="inlineStr">
         <is>
           <t>the feature wall that became an accent</t>
         </is>
       </c>
-      <c r="AW62" s="5" t="inlineStr">
+      <c r="AY62" s="5" t="inlineStr">
         <is>
           <t>Heather,
 One thing I would guess at. How often does a custom project come back smaller than it started?
 Not lost, just trimmed. A feature wall becomes an accent panel. That trim is almost always uncertainty rather than budget, and it is worth counting, because it never shows up as a lost sale in any report.
-ai.mecartworks.com. ai.mecartworks.com. Five previews, free, nothing to subscribe to. Upload a room, describe the piece, see it in place.</t>
-        </is>
-      </c>
-      <c r="AX62" s="4" t="inlineStr">
+ai.mecartworks.com. Five previews, free, nothing to subscribe to. Upload a room, describe the piece, see it in place.</t>
+        </is>
+      </c>
+      <c r="AZ62" s="4" t="inlineStr">
         <is>
           <t>how do your designers show it now?</t>
         </is>
       </c>
-      <c r="AY62" s="5" t="inlineStr">
+      <c r="BA62" s="5" t="inlineStr">
         <is>
           <t>Heather,
 That is everything from me.
@@ -14513,10 +15201,14 @@
           <t>benjamin@mosaicartstudio.us</t>
         </is>
       </c>
-      <c r="AL63" s="2" t="inlineStr"/>
+      <c r="AL63" s="2" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
       <c r="AM63" s="2" t="inlineStr">
         <is>
-          <t>SITE_MATCH: Inaccessible — domain does not resolve (getaddrinfo ENOTFOUND)</t>
+          <t>SITE_MATCH: Inaccessible — live domain returns no content; only archived cached version found</t>
         </is>
       </c>
       <c r="AN63" s="2" t="inlineStr">
@@ -14531,7 +15223,7 @@
       </c>
       <c r="AP63" s="2" t="inlineStr">
         <is>
-          <t>HOOK: N/A</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="AQ63" s="2" t="inlineStr">
@@ -14539,22 +15231,32 @@
           <t>CLIENT_PROOF: N/A</t>
         </is>
       </c>
-      <c r="AR63" s="3" t="inlineStr">
+      <c r="AR63" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS63" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT63" s="3" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
         </is>
       </c>
-      <c r="AS63" s="4" t="inlineStr">
+      <c r="AU63" s="4" t="inlineStr">
         <is>
           <t>Audit verdict DROP — Mosaic Studio UK - DNS dead. Resolves the FLAGGED item in S7.5</t>
         </is>
       </c>
-      <c r="AT63" s="4" t="inlineStr"/>
-      <c r="AU63" s="5" t="inlineStr"/>
       <c r="AV63" s="4" t="inlineStr"/>
       <c r="AW63" s="5" t="inlineStr"/>
       <c r="AX63" s="4" t="inlineStr"/>
       <c r="AY63" s="5" t="inlineStr"/>
+      <c r="AZ63" s="4" t="inlineStr"/>
+      <c r="BA63" s="5" t="inlineStr"/>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
@@ -14718,22 +15420,32 @@
           <t>CLIENT_PROOF: Not found</t>
         </is>
       </c>
-      <c r="AR64" s="3" t="inlineStr">
+      <c r="AR64" s="2" t="inlineStr">
+        <is>
+          <t>NO CONTACT</t>
+        </is>
+      </c>
+      <c r="AS64" s="2" t="inlineStr">
+        <is>
+          <t>both people searches failed. Needs manual sourcing or LinkedIn</t>
+        </is>
+      </c>
+      <c r="AT64" s="3" t="inlineStr">
         <is>
           <t>NO EMAIL</t>
         </is>
       </c>
-      <c r="AS64" s="4" t="inlineStr">
+      <c r="AU64" s="4" t="inlineStr">
         <is>
           <t>No work email on this row — LinkedIn or enrichment needed</t>
         </is>
       </c>
-      <c r="AT64" s="4" t="inlineStr"/>
-      <c r="AU64" s="5" t="inlineStr"/>
       <c r="AV64" s="4" t="inlineStr"/>
       <c r="AW64" s="5" t="inlineStr"/>
       <c r="AX64" s="4" t="inlineStr"/>
       <c r="AY64" s="5" t="inlineStr"/>
+      <c r="AZ64" s="4" t="inlineStr"/>
+      <c r="BA64" s="5" t="inlineStr"/>
     </row>
     <row r="65" ht="92" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
@@ -14901,48 +15613,62 @@
           <t>susansteinicke@usvinyl.com</t>
         </is>
       </c>
-      <c r="AL65" s="2" t="inlineStr"/>
+      <c r="AL65" s="2" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
       <c r="AM65" s="2" t="inlineStr">
         <is>
-          <t>SITE_MATCH: Match — vinyl wallcovering manufacturer; abstracts, geometrics, organics plus a custom line</t>
+          <t>SITE_MATCH: Match — brand US Vinyl/USV Wallcovering matches company, vinyl wallcovering products for hospitality</t>
         </is>
       </c>
       <c r="AN65" s="2" t="inlineStr">
         <is>
-          <t>CUSTOM_OFFERING: Yes — "Custom Wallcoverings" as its own catalog category — /index.php?option=com_virtuemart&amp;view=category&amp;virtuemart_category_id=4</t>
+          <t>CUSTOM_OFFERING: Yes — dedicated "Custom Wallcoverings" category and upload-your-own-artwork option — /index.php?...virtuemart_category_id=4</t>
         </is>
       </c>
       <c r="AO65" s="2" t="inlineStr">
         <is>
-          <t>VISUAL_TOOL: Basic — static collection galleries and mood boards, category-level colour/pattern filtering, no preview — virtuemart_category_id=1</t>
+          <t>VISUAL_TOOL: Basic — password-gated file upload form for artwork submission, no live preview (Studio Designs page)</t>
         </is>
       </c>
       <c r="AP65" s="2" t="inlineStr">
         <is>
-          <t>HOOK: Rebrand in progress — "USV Wallcovering Murals Graphics", described as "a new creative direction" beyond hotel standards, expanding into art-community partnerships — /index.php?option=com_content&amp;view=article&amp;id=87&amp;Itemid=540</t>
+          <t>"Choose and upload your original Mural or Digital Print artwork here" — Studio Designs page (/index.php?...virtuemart_category_id=3)</t>
         </is>
       </c>
       <c r="AQ65" s="2" t="inlineStr">
         <is>
-          <t>CLIENT_PROOF: Supplies Marriott, Hilton, IHG, Choice Hotels, Best Western, Red Roof Inn, Starwood — no individual venues named</t>
-        </is>
-      </c>
-      <c r="AR65" s="7" t="inlineStr">
+          <t>CLIENT_PROOF: Hotel brand families listed as clients — Hilton (Hampton, Garden Inn), Marriott (Courtyard, Moxy), IHG (Holiday Inn), Starwood (Sheraton), Choice Hotels, Radisson, Best Western — /index.php?...virtuemart_category_id=2 (Hotel Standards)</t>
+        </is>
+      </c>
+      <c r="AR65" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS65" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT65" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS65" s="4" t="inlineStr">
+      <c r="AU65" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT65" s="4" t="inlineStr">
+      <c r="AV65" s="4" t="inlineStr">
         <is>
           <t>Murals and Graphics, before the first install</t>
         </is>
       </c>
-      <c r="AU65" s="5" t="inlineStr">
+      <c r="AW65" s="5" t="inlineStr">
         <is>
           <t>Susan,
 USV Murals and Graphics is a different sell from hotel standards. Marriott and Hilton buy to spec and know exactly what arrives. Art led work gets bought on how it looks in the room.
@@ -14951,12 +15677,12 @@
 Would it help to see one of your new pieces put into a real hotel corridor? I will send it over.</t>
         </is>
       </c>
-      <c r="AV65" s="4" t="inlineStr">
+      <c r="AX65" s="4" t="inlineStr">
         <is>
           <t>brushed gold, botanical, low contrast</t>
         </is>
       </c>
-      <c r="AW65" s="5" t="inlineStr">
+      <c r="AY65" s="5" t="inlineStr">
         <is>
           <t>Susan,
 Worth adding, it is not a rendering job. Someone types "brushed gold, botanical, low contrast" and gets an original concept, then drops it into a photo of the actual space.
@@ -14964,12 +15690,12 @@
 ai.mecartworks.com, five free previews, email code.</t>
         </is>
       </c>
-      <c r="AX65" s="4" t="inlineStr">
+      <c r="AZ65" s="4" t="inlineStr">
         <is>
           <t>parking this until your launch</t>
         </is>
       </c>
-      <c r="AY65" s="5" t="inlineStr">
+      <c r="BA65" s="5" t="inlineStr">
         <is>
           <t>Susan,
 I will let you get on.
@@ -15173,22 +15899,32 @@
           <t>CLIENT_PROOF: Not found — project slider images, none named</t>
         </is>
       </c>
-      <c r="AR66" s="7" t="inlineStr">
+      <c r="AR66" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="AS66" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="AT66" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="AS66" s="4" t="inlineStr">
+      <c r="AU66" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="AT66" s="4" t="inlineStr">
+      <c r="AV66" s="4" t="inlineStr">
         <is>
           <t>no two tiles alike</t>
         </is>
       </c>
-      <c r="AU66" s="5" t="inlineStr">
+      <c r="AW66" s="5" t="inlineStr">
         <is>
           <t>Bardia,
 Kimia's line about no two tiles being exactly alike, with subtle variation in colour and texture, is the honest way to sell handmade tile.
@@ -15197,12 +15933,12 @@
 Would you take a look?</t>
         </is>
       </c>
-      <c r="AV66" s="4" t="inlineStr">
+      <c r="AX66" s="4" t="inlineStr">
         <is>
           <t>character on a wall, inconsistency on a sample</t>
         </is>
       </c>
-      <c r="AW66" s="5" t="inlineStr">
+      <c r="AY66" s="5" t="inlineStr">
         <is>
           <t>Bardia,
 The specific problem with handmade. Variation reads as character across a whole wall and as inconsistency on a single sample.
@@ -15210,12 +15946,12 @@
 ai.mecartworks.com, free to try, five previews, email code.</t>
         </is>
       </c>
-      <c r="AX66" s="4" t="inlineStr">
+      <c r="AZ66" s="4" t="inlineStr">
         <is>
           <t>the sample to wall gap</t>
         </is>
       </c>
-      <c r="AY66" s="5" t="inlineStr">
+      <c r="BA66" s="5" t="inlineStr">
         <is>
           <t>Bardia,
 Last word from me.
@@ -15377,22 +16113,32 @@
           <t>CLIENT_PROOF: N/A</t>
         </is>
       </c>
-      <c r="AR67" s="3" t="inlineStr">
+      <c r="AR67" s="2" t="inlineStr">
+        <is>
+          <t>NO CONTACT</t>
+        </is>
+      </c>
+      <c r="AS67" s="2" t="inlineStr">
+        <is>
+          <t>both people searches failed. Needs manual sourcing or LinkedIn</t>
+        </is>
+      </c>
+      <c r="AT67" s="3" t="inlineStr">
         <is>
           <t>NO EMAIL</t>
         </is>
       </c>
-      <c r="AS67" s="4" t="inlineStr">
+      <c r="AU67" s="4" t="inlineStr">
         <is>
           <t>No work email on this row — LinkedIn or enrichment needed</t>
         </is>
       </c>
-      <c r="AT67" s="4" t="inlineStr"/>
-      <c r="AU67" s="5" t="inlineStr"/>
       <c r="AV67" s="4" t="inlineStr"/>
       <c r="AW67" s="5" t="inlineStr"/>
       <c r="AX67" s="4" t="inlineStr"/>
       <c r="AY67" s="5" t="inlineStr"/>
+      <c r="AZ67" s="4" t="inlineStr"/>
+      <c r="BA67" s="5" t="inlineStr"/>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
@@ -15564,25 +16310,35 @@
           <t>CLIENT_PROOF: N/A</t>
         </is>
       </c>
-      <c r="AR68" s="3" t="inlineStr">
+      <c r="AR68" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="AS68" s="2" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+      <c r="AT68" s="3" t="inlineStr">
         <is>
           <t>NO EMAIL</t>
         </is>
       </c>
-      <c r="AS68" s="4" t="inlineStr">
+      <c r="AU68" s="4" t="inlineStr">
         <is>
           <t>No work email on this row — LinkedIn or enrichment needed</t>
         </is>
       </c>
-      <c r="AT68" s="4" t="inlineStr"/>
-      <c r="AU68" s="5" t="inlineStr"/>
       <c r="AV68" s="4" t="inlineStr"/>
       <c r="AW68" s="5" t="inlineStr"/>
       <c r="AX68" s="4" t="inlineStr"/>
       <c r="AY68" s="5" t="inlineStr"/>
+      <c r="AZ68" s="4" t="inlineStr"/>
+      <c r="BA68" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AY68"/>
+  <autoFilter ref="A1:BA68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15593,7 +16349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -15604,14 +16360,16 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="68" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
     <col width="68" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="68" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="68" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -15657,40 +16415,50 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>contact_status</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>contact_note</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>send_status</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>send_note</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>email_1_subject</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>email_1_body</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>email_2_subject</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>email_2_body</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>email_3_subject</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>email_3_body</t>
         </is>
@@ -15735,22 +16503,32 @@
           <t>http://www.areaenvironments.com</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>approving a wall they have never seen</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>Heather,
 Area sells to the trade only, and your FAQ says if someone brings a piece or a photograph, you will build the wallcovering around it.
@@ -15759,25 +16537,25 @@
 We built the AI studio MEC Artworks put on their site. Want me to run one of your collections through it and send you the result?</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>the feature wall that became an accent</t>
         </is>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="P2" s="5" t="inlineStr">
         <is>
           <t>Heather,
 One thing I would guess at. How often does a custom project come back smaller than it started?
 Not lost, just trimmed. A feature wall becomes an accent panel. That trim is almost always uncertainty rather than budget, and it is worth counting, because it never shows up as a lost sale in any report.
-ai.mecartworks.com. ai.mecartworks.com. Five previews, free, nothing to subscribe to. Upload a room, describe the piece, see it in place.</t>
-        </is>
-      </c>
-      <c r="O2" s="4" t="inlineStr">
+ai.mecartworks.com. Five previews, free, nothing to subscribe to. Upload a room, describe the piece, see it in place.</t>
+        </is>
+      </c>
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>how do your designers show it now?</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr">
+      <c r="R2" s="5" t="inlineStr">
         <is>
           <t>Heather,
 That is everything from me.
@@ -15824,22 +16602,32 @@
           <t>http://poolmosaics.com</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>found on SMB fallback</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>your artists, working step by step</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>Sal,
 Your own site says your ceramic artists work with the customer step by step to create the custom piece. Logos, mascots, family crests.
@@ -15848,12 +16636,12 @@
 Happy to show you myself. Would fifteen minutes work?</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>software for your artists, software for your customer</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>Sal,
 The difference in one line. Your software is a tool for your artists. This one is a tool for your customer.
@@ -15861,12 +16649,12 @@
 Screen share, 15 minutes, no deck. Want me to send times?</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>wrapping this up</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>Sal,
 I will close this off.
@@ -15913,22 +16701,32 @@
           <t>http://www.glamora.it</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>your Bespoke Design Service, before the first sketch</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>Verena,
 Glamora offers a Bespoke Design Service to professionals. An architect brings a project, your studio designs to it.
@@ -15937,12 +16735,12 @@
 Would it be useful to see it against one of your collections?</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>turning the first meeting into a decision</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>Verena,
 Worth adding, because "AI" says nothing useful on its own. There is no CAD and no drawing. Someone describes the piece by colour, mood and scale, gets an original concept, then sees it in the room.
@@ -15950,12 +16748,12 @@
 ai.mecartworks.com. Five free previews after a one time code.</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>do you show them anything in meeting one?</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="R4" s="5" t="inlineStr">
         <is>
           <t>Verena,
 This is the last one.
@@ -16002,22 +16800,32 @@
           <t>http://www.heathceramics.com</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>a set builder for dinnerware, not for tile</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>Anna,
 Heath built a set builder for dinnerware. Start building, save 10%, watch it come together.
@@ -16026,12 +16834,12 @@
 Worth seeing the parallel?</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>Seeds of Summer, on someone's actual wall</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="P5" s="5" t="inlineStr">
         <is>
           <t>Anna,
 Seeds of Summer is the case in point. Moodier pinks and reds, launched in April, and the hard part is getting someone to picture a whole wall of it from a swatch.
@@ -16039,12 +16847,12 @@
 ai.mecartworks.com, free, five previews, email code only.</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>one for the list</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="R5" s="5" t="inlineStr">
         <is>
           <t>Anna,
 I will drop it here.
@@ -16097,22 +16905,32 @@
           <t>http://www.lookwalls.com</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>the Gilded print in Reflections</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>Lindsay,
 The Gilded print technology in the Reflections Collection, with fine gold accents and reflective detail, is the kind of thing that has to be seen rather than described. A photo does not carry it.
@@ -16121,12 +16939,12 @@
 Worth 15 minutes?</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>for a 15 person studio, rounds are margin</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="P6" s="5" t="inlineStr">
         <is>
           <t>Lindsay,
 What it is worth to a fifteen person studio. Rounds are your margin.
@@ -16134,12 +16952,12 @@
 It lives at ai.mecartworks.com. Five free previews, no password. Two minutes will tell you whether it does the Gilded finish justice, and I suspect that is the real test.</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>every tool has to earn its place</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr">
+      <c r="R6" s="5" t="inlineStr">
         <is>
           <t>Lindsay,
 Closing the loop and stopping.
@@ -16186,22 +17004,32 @@
           <t>http://newravenna.com/</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>your concept board team</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Stephenie,
 New Ravenna's bespoke route starts with photographs, fabric swatches, sometimes a magazine clipping, and your team turning that into a mosaic concept before anything is cut.
@@ -16210,12 +17038,12 @@
 I would rather show you than send a competitor's link. Free for fifteen minutes this week?</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>photographs, swatches, clippings</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="P7" s="5" t="inlineStr">
         <is>
           <t>Stephenie,
 How it actually works. Someone types "warm terracotta, geometric, Moorish influence" and gets an original concept, then sees it on a photo of the real wall.
@@ -16223,12 +17051,12 @@
 Fifteen minutes on a screen share and you would know. Want me to propose a time?</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>how does the first pass work now?</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr">
+      <c r="R7" s="5" t="inlineStr">
         <is>
           <t>Stephenie,
 I will leave this alone now.
@@ -16275,22 +17103,32 @@
           <t>http://www.usvinyl.com</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>Murals and Graphics, before the first install</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="N8" s="5" t="inlineStr">
         <is>
           <t>Susan,
 USV Murals and Graphics is a different sell from hotel standards. Marriott and Hilton buy to spec and know exactly what arrives. Art led work gets bought on how it looks in the room.
@@ -16299,12 +17137,12 @@
 Would it help to see one of your new pieces put into a real hotel corridor? I will send it over.</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>brushed gold, botanical, low contrast</t>
         </is>
       </c>
-      <c r="N8" s="5" t="inlineStr">
+      <c r="P8" s="5" t="inlineStr">
         <is>
           <t>Susan,
 Worth adding, it is not a rendering job. Someone types "brushed gold, botanical, low contrast" and gets an original concept, then drops it into a photo of the actual space.
@@ -16312,12 +17150,12 @@
 ai.mecartworks.com, five free previews, email code.</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>parking this until your launch</t>
         </is>
       </c>
-      <c r="P8" s="5" t="inlineStr">
+      <c r="R8" s="5" t="inlineStr">
         <is>
           <t>Susan,
 I will let you get on.
@@ -16364,22 +17202,32 @@
           <t>www.aquablumosaics.com</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>Create a Mosaic, before the drawing</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>Michael,
 Your Create a Mosaic service is why I am writing. A homeowner or a builder describes what they want in the pool, and your team turns it into a design.
@@ -16388,12 +17236,12 @@
 I would rather walk you through it than send you a competitor's link. Can I book fifteen minutes?</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>selling the finished pool, not the drawing</t>
         </is>
       </c>
-      <c r="N9" s="5" t="inlineStr">
+      <c r="P9" s="5" t="inlineStr">
         <is>
           <t>Michael,
 How it works. Someone types "deep blue, geometric, Mediterranean" and gets an original mosaic concept, then it is placed on a photo of the real pool.
@@ -16401,12 +17249,12 @@
 Fifteen minutes on a screen share, no deck. Shall I send two or three times that suit you?</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>if custom pools already close fast</t>
         </is>
       </c>
-      <c r="P9" s="5" t="inlineStr">
+      <c r="R9" s="5" t="inlineStr">
         <is>
           <t>Michael,
 That is me done.
@@ -16453,22 +17301,32 @@
           <t>http://www.artistictile.com</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>what Tailored To asks of a client</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="N10" s="5" t="inlineStr">
         <is>
           <t>Colleen,
 Tailored To is a real bespoke programme. Custom cutting and finishing, not a size option with a nicer name.
@@ -16477,12 +17335,12 @@
 I would rather walk you through it than send a competitor's link. Open to a short call?</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>a better lead than a sample request</t>
         </is>
       </c>
-      <c r="N10" s="5" t="inlineStr">
+      <c r="P10" s="5" t="inlineStr">
         <is>
           <t>Colleen,
 From a marketing seat there is a second angle here. This is content as much as it is a tool.
@@ -16490,12 +17348,12 @@
 Fifteen minutes on a screen share and you would know whether it is worth raising internally. Want me to send a couple of times?</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="Q10" s="4" t="inlineStr">
         <is>
           <t>not adding to your inbox</t>
         </is>
       </c>
-      <c r="P10" s="5" t="inlineStr">
+      <c r="R10" s="5" t="inlineStr">
         <is>
           <t>Colleen,
 Last one, then I am out of your inbox.
@@ -16546,22 +17404,32 @@
           <t>http://derbypottery.com</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>found on SMB fallback</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>the New Orleans street tiles</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>Mark,
 Making the city's letter and number tiles since 2003 is a hard credential to argue with.
@@ -16570,12 +17438,12 @@
 Worth two minutes of an owner's time?</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <t>specialty glazing, undecided customers</t>
         </is>
       </c>
-      <c r="N11" s="5" t="inlineStr">
+      <c r="P11" s="5" t="inlineStr">
         <is>
           <t>Mark,
 The useful detail. No drawing, no software to learn. A customer types "Victorian, deep green, geometric border" and sees it on their own floor.
@@ -16584,12 +17452,12 @@
 If it does not do your glazes justice, I would want to know that too.</t>
         </is>
       </c>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>one more tool to evaluate</t>
         </is>
       </c>
-      <c r="P11" s="5" t="inlineStr">
+      <c r="R11" s="5" t="inlineStr">
         <is>
           <t>Mark,
 Signing off on this one.
@@ -16632,22 +17500,32 @@
           <t>https://fancywalls.eu/</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>your private label partners, and their customers</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="N12" s="5" t="inlineStr">
         <is>
           <t>Ivars,
 Fancy Walls already sells its capability onward. Private label, dropship, one to two day turnaround. That is a harder business to build than a shop.
@@ -16656,12 +17534,12 @@
 Want me to show you where it would sit inside a private label flow?</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>two days to print, three weeks to decide</t>
         </is>
       </c>
-      <c r="N12" s="5" t="inlineStr">
+      <c r="P12" s="5" t="inlineStr">
         <is>
           <t>Ivars,
 More concrete. A shopper types what they want, gets an original design back, and sees it on a photo of their room. No drawing, no designer, no brief.
@@ -16669,12 +17547,12 @@
 ai.mecartworks.com, five free previews, email code.</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>is choosing really the slow part?</t>
         </is>
       </c>
-      <c r="P12" s="5" t="inlineStr">
+      <c r="R12" s="5" t="inlineStr">
         <is>
           <t>Ivars,
 I will stop here.
@@ -16725,22 +17603,32 @@
           <t>http://www.hakatai.com/Company-profile-W1C31.aspx</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>found on SMB fallback</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>custom mosaic murals, before the layout</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr">
         <is>
           <t>Christina,
 Hakatai does custom designed glass tile installations. Mosaic murals and uncut custom patterns, not only stock series.
@@ -16749,12 +17637,12 @@
 Happy to walk you through it instead. Fifteen minutes on a call?</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <t>clients who can see it approve the bigger piece</t>
         </is>
       </c>
-      <c r="N13" s="5" t="inlineStr">
+      <c r="P13" s="5" t="inlineStr">
         <is>
           <t>Christina,
 The money point, plainly. A client who can see the finished wall does not need to hedge. The ones who cannot see it protect themselves by ordering less.
@@ -16762,12 +17650,12 @@
 I would rather demo it than send you to a competitor's site. Fifteen minutes, screen share. Want a couple of times?</t>
         </is>
       </c>
-      <c r="O13" s="4" t="inlineStr">
+      <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>one last note</t>
         </is>
       </c>
-      <c r="P13" s="5" t="inlineStr">
+      <c r="R13" s="5" t="inlineStr">
         <is>
           <t>Christina,
 Closing this out.
@@ -16810,22 +17698,32 @@
           <t>https://www.inkiostrobianco.com</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>progetti su misura, before the render</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="N14" s="5" t="inlineStr">
         <is>
           <t>Paolo,
 Inkiostro Bianco offers progetti su misura, and with a 3D lead in the room you are already making visuals to sell them.
@@ -16834,12 +17732,12 @@
 Not a replacement for your 3D work. A filter in front of it. Worth a look?</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>a 3D lead's read on the output</t>
         </is>
       </c>
-      <c r="N14" s="5" t="inlineStr">
+      <c r="P14" s="5" t="inlineStr">
         <is>
           <t>Paolo,
 You would judge this faster than anyone I could send it to, so I will be direct about what I want.
@@ -16848,12 +17746,12 @@
 ai.mecartworks.com, free, five previews, email code.</t>
         </is>
       </c>
-      <c r="O14" s="4" t="inlineStr">
+      <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>if the 3D queue is never a queue</t>
         </is>
       </c>
-      <c r="P14" s="5" t="inlineStr">
+      <c r="R14" s="5" t="inlineStr">
         <is>
           <t>Paolo,
 I will let this go.
@@ -16904,22 +17802,32 @@
           <t>http://www.kibaktile.com/</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>found on SMB fallback</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>before the meeting gets booked</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>Carli,
 Kibak offers custom tile and custom murals, and the site invites people to book a meeting to talk the project through.
@@ -16928,12 +17836,12 @@
 Would that be more useful before the meeting than during it?</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="O15" s="4" t="inlineStr">
         <is>
           <t>refining, not interpreting</t>
         </is>
       </c>
-      <c r="N15" s="5" t="inlineStr">
+      <c r="P15" s="5" t="inlineStr">
         <is>
           <t>Carli,
 Concretely. The customer books the meeting already holding a picture of what they want, placed in their own space.
@@ -16941,12 +17849,12 @@
 ai.mecartworks.com, five previews, email code, no subscription.</t>
         </is>
       </c>
-      <c r="O15" s="4" t="inlineStr">
+      <c r="Q15" s="4" t="inlineStr">
         <is>
           <t>a solution looking for a problem?</t>
         </is>
       </c>
-      <c r="P15" s="5" t="inlineStr">
+      <c r="R15" s="5" t="inlineStr">
         <is>
           <t>Carli,
 I will leave this with you.
@@ -16993,22 +17901,32 @@
           <t>http://www.mercurymosaics.com</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>your consultants, and the first ten minutes</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="N16" s="5" t="inlineStr">
         <is>
           <t>Randi,
 Create Your Blend lets a customer pick colours for diamond tiles, and you have a director of design consultants. That combination tells me plenty of custom work still starts as a conversation rather than a selector.
@@ -17017,12 +17935,12 @@
 Would it help your consultants to see it?</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>refining instead of guessing</t>
         </is>
       </c>
-      <c r="N16" s="5" t="inlineStr">
+      <c r="P16" s="5" t="inlineStr">
         <is>
           <t>Randi,
 For a consulting team, the value is in what the first call starts from.
@@ -17030,12 +17948,12 @@
 ai.mecartworks.com. Free, five previews, code by email.</t>
         </is>
       </c>
-      <c r="O16" s="4" t="inlineStr">
+      <c r="Q16" s="4" t="inlineStr">
         <is>
           <t>closing the loop</t>
         </is>
       </c>
-      <c r="P16" s="5" t="inlineStr">
+      <c r="R16" s="5" t="inlineStr">
         <is>
           <t>Randi,
 Last note.
@@ -17082,22 +18000,32 @@
           <t>https://mooremerkowitztile.com</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>found on SMB fallback</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>19 collections, one decision</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="N17" s="5" t="inlineStr">
         <is>
           <t>Neil,
 Nineteen design collections in the Molding and Trim series is a lot of choice, and choice is exactly what stalls a tile decision.
@@ -17106,12 +18034,12 @@
 Worth a couple of minutes?</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>let the customer do the narrowing</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="P17" s="5" t="inlineStr">
         <is>
           <t>Neil,
 The practical version. The customer narrows it themselves, on screen, before they contact you.
@@ -17119,12 +18047,12 @@
 ai.mecartworks.com, no cost, five previews, code by email. Two minutes will tell you whether it handles your glazes properly.</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr">
+      <c r="Q17" s="4" t="inlineStr">
         <is>
           <t>when choosing eats a week</t>
         </is>
       </c>
-      <c r="P17" s="5" t="inlineStr">
+      <c r="R17" s="5" t="inlineStr">
         <is>
           <t>Neil,
 Ending it here.
@@ -17175,22 +18103,32 @@
           <t>https://www.mosaicslab.com</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>found on SMB fallback</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>the free design consultation</t>
         </is>
       </c>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="N18" s="5" t="inlineStr">
         <is>
           <t>Chad,
 Mosaics Lab offers a free design consultation on custom work. A customer sends a photo or a painting, and your team turns it into a mosaic concept.
@@ -17199,12 +18137,12 @@
 Rather than point you at a competitor's site, can I walk you through it?</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>how many consultations turn into orders?</t>
         </is>
       </c>
-      <c r="N18" s="5" t="inlineStr">
+      <c r="P18" s="5" t="inlineStr">
         <is>
           <t>Chad,
 The number I would want if I ran your business: what share of free consultations become paid mosaics?
@@ -17213,12 +18151,12 @@
 Want a couple of times?</t>
         </is>
       </c>
-      <c r="O18" s="4" t="inlineStr">
+      <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>owners know where the time leaks</t>
         </is>
       </c>
-      <c r="P18" s="5" t="inlineStr">
+      <c r="R18" s="5" t="inlineStr">
         <is>
           <t>Chad,
 No more from me after this.
@@ -17265,22 +18203,32 @@
           <t>http://www.motawi.com</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Project Tile, and what comes before it</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>Justin,
 Project Tile is a smart piece of work. Customers planning a backsplash or a fireplace with your patterns instead of guessing at them.
@@ -17289,12 +18237,12 @@
 Worth seeing how it might sit in front of Project Tile?</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>an art director's verdict in two minutes</t>
         </is>
       </c>
-      <c r="N19" s="5" t="inlineStr">
+      <c r="P19" s="5" t="inlineStr">
         <is>
           <t>Justin,
 As an art director you will spot the flaws faster than I could list them, so here is the honest ask.
@@ -17303,12 +18251,12 @@
 Find it at ai.mecartworks.com. One code by email unlocks five previews.</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr">
+      <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>generated design might be exactly wrong for Motawi</t>
         </is>
       </c>
-      <c r="P19" s="5" t="inlineStr">
+      <c r="R19" s="5" t="inlineStr">
         <is>
           <t>Justin,
 I will leave this here.
@@ -17359,22 +18307,32 @@
           <t>http://www.oceansideglasstile.com</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>found on SMB fallback</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>the Special Order Program</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="N20" s="5" t="inlineStr">
         <is>
           <t>Sean,
 Oceanside's Special Order Program and the Uniquely Oceanside collaboration both let a client customise before the tile ships.
@@ -17383,12 +18341,12 @@
 Can I walk you through it? Fifteen minutes.</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>unlimited possibilities, one decision</t>
         </is>
       </c>
-      <c r="N20" s="5" t="inlineStr">
+      <c r="P20" s="5" t="inlineStr">
         <is>
           <t>Sean,
 Where it fits Oceanside. Unlimited combinations is a great selling line right up to the moment a client has to pick one, and then it becomes the reason they delay.
@@ -17396,12 +18354,12 @@
 I would rather show you directly than send a competitor's link. A quick screen share is all it takes. Want me to send times?</t>
         </is>
       </c>
-      <c r="O20" s="4" t="inlineStr">
+      <c r="Q20" s="4" t="inlineStr">
         <is>
           <t>thirty years of recycled glass</t>
         </is>
       </c>
-      <c r="P20" s="5" t="inlineStr">
+      <c r="R20" s="5" t="inlineStr">
         <is>
           <t>Sean,
 Final note.
@@ -17448,22 +18406,32 @@
           <t>http://www.prattandlarson.com</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>serendipity, minus the shipping time</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t>Susanne,
 Your InLine Design Cards are a genuinely good idea. Physical cards so someone can experiment and let serendipity do its work.
@@ -17472,12 +18440,12 @@
 Worth showing you the parallel?</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="O21" s="4" t="inlineStr">
         <is>
           <t>customers who experiment specify bigger</t>
         </is>
       </c>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="P21" s="5" t="inlineStr">
         <is>
           <t>Susanne,
 What it is worth to you. Customers who experiment buy with more confidence and specify larger areas. Your cards prove you already believe that, or you would not have made them.
@@ -17485,12 +18453,12 @@
 Find it at ai.mecartworks.com. An email code gets you five previews. Two minutes will tell you whether it belongs next to the cards or nowhere near them.</t>
         </is>
       </c>
-      <c r="O21" s="4" t="inlineStr">
+      <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>if the cards are working, ignore me</t>
         </is>
       </c>
-      <c r="P21" s="5" t="inlineStr">
+      <c r="R21" s="5" t="inlineStr">
         <is>
           <t>Susanne,
 I will stop chasing this.
@@ -17537,22 +18505,32 @@
           <t>https://www.sicis.com</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>your design service for architects</t>
         </is>
       </c>
-      <c r="L22" s="5" t="inlineStr">
+      <c r="N22" s="5" t="inlineStr">
         <is>
           <t>Andrea,
 Sicis runs a design service for architects, soluzioni su misura across mosaic, glass and interiors.
@@ -17561,12 +18539,12 @@
 Worth walking you through?</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>one image that works as a proposal and as content</t>
         </is>
       </c>
-      <c r="N22" s="5" t="inlineStr">
+      <c r="P22" s="5" t="inlineStr">
         <is>
           <t>Andrea,
 For your side of the business specifically. The output is shareable, not just usable.
@@ -17574,12 +18552,12 @@
 Fifteen minutes on a screen share and you would see whether the quality is up to the brand.</t>
         </is>
       </c>
-      <c r="O22" s="4" t="inlineStr">
+      <c r="Q22" s="4" t="inlineStr">
         <is>
           <t>Sicis may not need generated imagery</t>
         </is>
       </c>
-      <c r="P22" s="5" t="inlineStr">
+      <c r="R22" s="5" t="inlineStr">
         <is>
           <t>Andrea,
 I will leave it there.
@@ -17627,22 +18605,32 @@
           <t>thekimiatile.com</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>no two tiles alike</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="N23" s="5" t="inlineStr">
         <is>
           <t>Bardia,
 Kimia's line about no two tiles being exactly alike, with subtle variation in colour and texture, is the honest way to sell handmade tile.
@@ -17651,12 +18639,12 @@
 Would you take a look?</t>
         </is>
       </c>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="O23" s="4" t="inlineStr">
         <is>
           <t>character on a wall, inconsistency on a sample</t>
         </is>
       </c>
-      <c r="N23" s="5" t="inlineStr">
+      <c r="P23" s="5" t="inlineStr">
         <is>
           <t>Bardia,
 The specific problem with handmade. Variation reads as character across a whole wall and as inconsistency on a single sample.
@@ -17664,12 +18652,12 @@
 ai.mecartworks.com, free to try, five previews, email code.</t>
         </is>
       </c>
-      <c r="O23" s="4" t="inlineStr">
+      <c r="Q23" s="4" t="inlineStr">
         <is>
           <t>the sample to wall gap</t>
         </is>
       </c>
-      <c r="P23" s="5" t="inlineStr">
+      <c r="R23" s="5" t="inlineStr">
         <is>
           <t>Bardia,
 Last word from me.
@@ -17716,22 +18704,32 @@
           <t>http://www.bisazza.com</t>
         </is>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>the Bisazza App, and the consultation behind it</t>
         </is>
       </c>
-      <c r="L24" s="5" t="inlineStr">
+      <c r="N24" s="5" t="inlineStr">
         <is>
           <t>Paolo,
 Bisazza already runs a space configurator and a free Design Studio consultation for custom mosaic work. That is further along than most of this industry.
@@ -17740,12 +18738,12 @@
 Worth a look as a front end to the Design Studio?</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>where the Design Studio hours go</t>
         </is>
       </c>
-      <c r="N24" s="5" t="inlineStr">
+      <c r="P24" s="5" t="inlineStr">
         <is>
           <t>Paolo,
 Framing it for your side. The app handles configuration. The studio handles creation. The gap between them is paid human time, and it scales linearly with demand.
@@ -17753,12 +18751,12 @@
 I would rather show you than send a link. Fifteen minutes on a screen share. Want a couple of times?</t>
         </is>
       </c>
-      <c r="O24" s="4" t="inlineStr">
+      <c r="Q24" s="4" t="inlineStr">
         <is>
           <t>have you looked at generated design already?</t>
         </is>
       </c>
-      <c r="P24" s="5" t="inlineStr">
+      <c r="R24" s="5" t="inlineStr">
         <is>
           <t>Paolo,
 Closing this off.
@@ -17805,22 +18803,32 @@
           <t>http://www.fireclaytile.com</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>your Mosaic Visualizer, one step earlier</t>
         </is>
       </c>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="N25" s="5" t="inlineStr">
         <is>
           <t>Samantha,
 Fireclay's Mosaic Visualizer is one of the few real ones in this industry. Most tile brands still ship a photo gallery and call it a tool.
@@ -17829,12 +18837,12 @@
 Would it be useful to see how it sits in front of the Visualizer?</t>
         </is>
       </c>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="O25" s="4" t="inlineStr">
         <is>
           <t>the Foundry launch and the like that but requests</t>
         </is>
       </c>
-      <c r="N25" s="5" t="inlineStr">
+      <c r="P25" s="5" t="inlineStr">
         <is>
           <t>Samantha,
 The Foundry Collection is a good example of the gap. A launch creates demand for a look, and the requests that follow are always "like that, but".
@@ -17842,12 +18850,12 @@
 It is at ai.mecartworks.com. Five previews, no cost, code by email. You would know inside two minutes whether the output clears Fireclay's bar.</t>
         </is>
       </c>
-      <c r="O25" s="4" t="inlineStr">
+      <c r="Q25" s="4" t="inlineStr">
         <is>
           <t>one for the roadmap file</t>
         </is>
       </c>
-      <c r="P25" s="5" t="inlineStr">
+      <c r="R25" s="5" t="inlineStr">
         <is>
           <t>Samantha,
 This is my last email on it.
@@ -17894,22 +18902,32 @@
           <t>https://instabilelab.com/it/</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>Real Wall and Live Room, one step earlier</t>
         </is>
       </c>
-      <c r="L26" s="5" t="inlineStr">
+      <c r="N26" s="5" t="inlineStr">
         <is>
           <t>Giulia,
 Real Wall and Live Room put Instabilelab ahead of most of this industry. Plenty of wallcovering brands still ship a static gallery and call it a tool.
@@ -17918,12 +18936,12 @@
 Would it be useful to see how it sits in front of Real Wall?</t>
         </is>
       </c>
-      <c r="M26" s="4" t="inlineStr">
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>the visitor your configurators never meet</t>
         </is>
       </c>
-      <c r="N26" s="5" t="inlineStr">
+      <c r="P26" s="5" t="inlineStr">
         <is>
           <t>Giulia,
 To be concrete. Someone types "ochre, oversized botanical, matte" and gets an original design, then sees it on their wall. Your configurators handle everything after that.
@@ -17931,12 +18949,12 @@
 You will find it at ai.mecartworks.com. Five previews, no cost.</t>
         </is>
       </c>
-      <c r="O26" s="4" t="inlineStr">
+      <c r="Q26" s="4" t="inlineStr">
         <is>
           <t>you built configurators. what did you learn?</t>
         </is>
       </c>
-      <c r="P26" s="5" t="inlineStr">
+      <c r="R26" s="5" t="inlineStr">
         <is>
           <t>Giulia,
 Final email from me.
@@ -17987,22 +19005,32 @@
           <t>http://www.senecatiles.com</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>found on SMB fallback</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="L27" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="M27" s="4" t="inlineStr">
         <is>
           <t>the Handmold Mini Panels</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr">
+      <c r="N27" s="5" t="inlineStr">
         <is>
           <t>Connie,
 Seneca brought the Handmold Mini Panels back by popular demand. That tells me your specifiers respond to seeing the real thing in front of them, which is worth knowing about your own market.
@@ -18011,12 +19039,12 @@
 I could not tell from your site how much custom work Seneca takes on. Open to a short call?</t>
         </is>
       </c>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="O27" s="4" t="inlineStr">
         <is>
           <t>a straight question about how Seneca sells</t>
         </is>
       </c>
-      <c r="N27" s="5" t="inlineStr">
+      <c r="P27" s="5" t="inlineStr">
         <is>
           <t>Connie,
 Being honest about why I am asking. Your site is clear on collections and quiet on how far you will go on a custom request.
@@ -18025,12 +19053,12 @@
 ai.mecartworks.com shows what I mean in two minutes.</t>
         </is>
       </c>
-      <c r="O27" s="4" t="inlineStr">
+      <c r="Q27" s="4" t="inlineStr">
         <is>
           <t>the Mini Panels run</t>
         </is>
       </c>
-      <c r="P27" s="5" t="inlineStr">
+      <c r="R27" s="5" t="inlineStr">
         <is>
           <t>Connie,
 One more and then I am done.
@@ -18077,22 +19105,32 @@
           <t>https://www.ziatile.com</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="L28" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr">
+      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>designed in LA, crafted everywhere</t>
         </is>
       </c>
-      <c r="L28" s="5" t="inlineStr">
+      <c r="N28" s="5" t="inlineStr">
         <is>
           <t>Jamie,
 Zia's line, designed in Los Angeles and crafted by artisans around the globe, is a curated position rather than a made to order one. The filters on the site reflect that and they work well.
@@ -18101,12 +19139,12 @@
 Worth two minutes of a marketing director's time?</t>
         </is>
       </c>
-      <c r="M28" s="4" t="inlineStr">
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>a discovery tool, not a design service</t>
         </is>
       </c>
-      <c r="N28" s="5" t="inlineStr">
+      <c r="P28" s="5" t="inlineStr">
         <is>
           <t>Jamie,
 To be clear, I am not suggesting Zia moves into custom. The curated position is the brand and it is working.
@@ -18114,12 +19152,12 @@
 ai.mecartworks.com, five previews, email code, no subscription.</t>
         </is>
       </c>
-      <c r="O28" s="4" t="inlineStr">
+      <c r="Q28" s="4" t="inlineStr">
         <is>
           <t>maybe the filters already do this</t>
         </is>
       </c>
-      <c r="P28" s="5" t="inlineStr">
+      <c r="R28" s="5" t="inlineStr">
         <is>
           <t>Jamie,
 One last note.
@@ -18170,22 +19208,32 @@
           <t>http://finerworks.com</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>found on SMB fallback</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J29" s="4" t="inlineStr">
+      <c r="L29" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="M29" s="4" t="inlineStr">
         <is>
           <t>the commission your artists cannot preview</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="N29" s="5" t="inlineStr">
         <is>
           <t>James,
 FinerWorks is built for the artist who already has the file. Drag it in, live preview, COA on the way out. That is a clean pipeline and it shows.
@@ -18194,12 +19242,12 @@
 Worth showing you?</t>
         </is>
       </c>
-      <c r="M29" s="4" t="inlineStr">
+      <c r="O29" s="4" t="inlineStr">
         <is>
           <t>a COA for a piece that does not exist yet</t>
         </is>
       </c>
-      <c r="N29" s="5" t="inlineStr">
+      <c r="P29" s="5" t="inlineStr">
         <is>
           <t>James,
 The practical version. The buyer types what they want, gets an original concept, then sees it on their own wall before the artist starts painting.
@@ -18208,12 +19256,12 @@
 I would value your read on the output quality.</t>
         </is>
       </c>
-      <c r="O29" s="4" t="inlineStr">
+      <c r="Q29" s="4" t="inlineStr">
         <is>
           <t>one for the roadmap</t>
         </is>
       </c>
-      <c r="P29" s="5" t="inlineStr">
+      <c r="R29" s="5" t="inlineStr">
         <is>
           <t>James,
 I will leave it here.
@@ -18260,22 +19308,32 @@
           <t>http://www.limitlesswalls.com</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="L30" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr">
+      <c r="M30" s="4" t="inlineStr">
         <is>
           <t>the customer who has nothing to upload</t>
         </is>
       </c>
-      <c r="L30" s="5" t="inlineStr">
+      <c r="N30" s="5" t="inlineStr">
         <is>
           <t>Stacy,
 Your GO CUSTOM flow is better than most. Upload, crop, resize, live pricing, done.
@@ -18284,25 +19342,25 @@
 Want me to send you a short walkthrough?</t>
         </is>
       </c>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="O30" s="4" t="inlineStr">
         <is>
           <t>when there is nothing to put in the box</t>
         </is>
       </c>
-      <c r="N30" s="5" t="inlineStr">
+      <c r="P30" s="5" t="inlineStr">
         <is>
           <t>Stacy,
 Here is the part that matters for you. Someone types "brushed sage, large botanical, low contrast" and gets an original design. Not a stock search result. Then they upload their room and see it hanging there.
 One thing you can check today without me: pull your search log for the last month and count the queries that returned nothing. That number is the size of this gap, and it costs you nothing to find out.
-The tool is at ai.mecartworks.com. ai.mecartworks.com, five previews free, email verification only.</t>
-        </is>
-      </c>
-      <c r="O30" s="4" t="inlineStr">
+The tool is at ai.mecartworks.com. Five previews free, email verification only.</t>
+        </is>
+      </c>
+      <c r="Q30" s="4" t="inlineStr">
         <is>
           <t>how do you convert the no image visitor?</t>
         </is>
       </c>
-      <c r="P30" s="5" t="inlineStr">
+      <c r="R30" s="5" t="inlineStr">
         <is>
           <t>Stacy,
 I will stop emailing after this one.
@@ -18353,22 +19411,32 @@
           <t>http://www.megaprint.com</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>found on SMB fallback</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="L31" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K31" s="4" t="inlineStr">
+      <c r="M31" s="4" t="inlineStr">
         <is>
           <t>the step before the 48 inch panels</t>
         </is>
       </c>
-      <c r="L31" s="5" t="inlineStr">
+      <c r="N31" s="5" t="inlineStr">
         <is>
           <t>Tim,
 MegaPrint prints removable custom wallpaper on 48 inch panels, two to three weeks, and the customer supplies the artwork.
@@ -18377,12 +19445,12 @@
 Want me to run your own lobby through it and send you the result?</t>
         </is>
       </c>
-      <c r="M31" s="4" t="inlineStr">
+      <c r="O31" s="4" t="inlineStr">
         <is>
           <t>before the artwork file exists</t>
         </is>
       </c>
-      <c r="N31" s="5" t="inlineStr">
+      <c r="P31" s="5" t="inlineStr">
         <is>
           <t>Tim,
 To be clear about what it does, since "AI design" means very little on its own.
@@ -18391,12 +19459,12 @@
 ai.mecartworks.com. Email code, five previews, nothing to cancel.</t>
         </is>
       </c>
-      <c r="O31" s="4" t="inlineStr">
+      <c r="Q31" s="4" t="inlineStr">
         <is>
           <t>parking this with you</t>
         </is>
       </c>
-      <c r="P31" s="5" t="inlineStr">
+      <c r="R31" s="5" t="inlineStr">
         <is>
           <t>Tim,
 Last one from me.
@@ -18443,22 +19511,32 @@
           <t>https://www.photowall.com/us</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>HAS EMAIL</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>found on main search</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr">
         <is>
           <t>SEND</t>
         </is>
       </c>
-      <c r="J32" s="4" t="inlineStr">
+      <c r="L32" s="4" t="inlineStr">
         <is>
           <t>Cleared: audit KEEP/FLAG, revenue gate passed, email domain matches</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr">
+      <c r="M32" s="4" t="inlineStr">
         <is>
           <t>your simulator, for designs that do not exist yet</t>
         </is>
       </c>
-      <c r="L32" s="5" t="inlineStr">
+      <c r="N32" s="5" t="inlineStr">
         <is>
           <t>Jennifer,
 Photowall's Try Before You Buy simulator already does the hard half. The customer sees the design on their own wall before they buy.
@@ -18467,12 +19545,12 @@
 Want to see how the two steps fit together?</t>
         </is>
       </c>
-      <c r="M32" s="4" t="inlineStr">
+      <c r="O32" s="4" t="inlineStr">
         <is>
           <t>thousands of designs, still no match</t>
         </is>
       </c>
-      <c r="N32" s="5" t="inlineStr">
+      <c r="P32" s="5" t="inlineStr">
         <is>
           <t>Jennifer,
 The mechanic in one line. Someone describes the design in ordinary words, gets an original back, then previews it in their own room. Same last step as yours. Different first step.
@@ -18480,12 +19558,12 @@
 ai.mecartworks.com, email code, five previews, no card.</t>
         </is>
       </c>
-      <c r="O32" s="4" t="inlineStr">
+      <c r="Q32" s="4" t="inlineStr">
         <is>
           <t>does no close match show in your search data?</t>
         </is>
       </c>
-      <c r="P32" s="5" t="inlineStr">
+      <c r="R32" s="5" t="inlineStr">
         <is>
           <t>Jennifer,
 Last note from me.
@@ -18496,7 +19574,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P32"/>
+  <autoFilter ref="A1:R32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20291,4 +21369,1271 @@
   <autoFilter ref="A1:J37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>niche</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Annual Revenue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Combined Full Name</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Title People</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Linkedin Url People</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Find people at company</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Find people at company (SMB)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>contact_status</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>contact_note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Carreaux du Nord</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://carreauxdunord.com</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Decorative / Artisan Tile</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>1M-5M</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Ned Guyette</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Co‑founder/Owner</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>❌ No people found</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>✅ 1 decision maker found</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Craig Bragdy Design</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://craigbragdydesign.com</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Mosaic / Pool</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>25M-75M</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abby Humphreys </t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>✅ Found 1 people</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Giffywalls</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://giffywalls.com</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Murals &amp; Wallpaper</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>500K-1M</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Dipan Patel</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder/Owner</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>❌ No people found</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>✅ 1 decision maker found</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>JILL CAMPION HANDMADE TILE LIMIT</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>jillcampion.com</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>English Handmade Tile.
+Heritage ceramics, handmade in Staffordshire.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>500K-1M</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Pamela Campion</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Director / Owner</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>❌ No people found</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>✅ 1 decision maker found</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Magic Murals</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://magicmurals.com</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Murals &amp; Wallpaper</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1M-5M</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Mike Fleming</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mike-fleming-b1104411</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>❌ No people found</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>✅ 1 decision maker found</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Native Tile</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>https://nativetile.com</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Ceramic Tile</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5M-10M</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Diana Mausser</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Owner/Founder</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/diana-mausser-297652123</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>❌ No people found</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>✅ 1 decision maker found</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>North Prairie Tileworks</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>https://handmadetile.com</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Decorative / Artisan Tile</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1M-5M</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Roger Mayland</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/roger-mayland-26b78321</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>❌ No people found</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>✅ 1 decision maker found</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>RTK Studios</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>https://rtkstudios.com</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Decorative / Artisan Tile</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1M-5M</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Richard Keit</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>❌ No people found</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>✅ 1 decision maker found</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Ravenstone Tiles</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>https://ravenstonetiles.com</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Decorative / Artisan Tile</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>500K-1M</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Laura Reutter</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Owner / Artist</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>❌ No people found</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>✅ 1 decision maker found</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Shard Glass Studio</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>https://shardglassstudio.com</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Stained Glass</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Lauren Delsignore</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Artist &amp; Owner</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>❌ No people found</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>✅ 1 decision maker found</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Sonoma Tilemakers</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>https://sonomatilemakers.com</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Decorative / Artisan Tile</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>25M-75M</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Jon Gray</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Owner / Partner</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>❌ No people found</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>✅ 1 decision maker found</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Tabarka Studio</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>https://tabarkastudio.com</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Decorative / Artisan Tile</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5M-10M</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Meir Zenati</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; Creative Director</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>❌ No people found</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>✅ 1 decision maker found</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Tempest Tileworks</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>https://tempesttileworks.com</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Decorative / Artisan Tile</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>500K-1M</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Leigh Odell</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Co-owner</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>❌ No people found</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>✅ 1 decision maker found</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Tiles of Ezra</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>https://tilesofezra.com</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Decorative / Artisan Tile</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>5M-10M</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Georgia Ezra </t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>✅ Found 1 people</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Wall &amp; Deco</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>https://wallanddeco.com</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Murals &amp; Wallpaper</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10M-25M</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jasmine Kaur </t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>✅ Found 1 people</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>cle tile</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>https://cletile.com</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Decorative / Artisan Tile</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sydney Turturro </t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>✅ Found 3 people</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>NAME, NO EMAIL</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>contact identified. Run the email waterfall (S7.7 step 7) on this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Bigmural Design Studio</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>bigmural.com</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Big Mural Design Studio specializes in murals of all styles and sizes for residential and commercial properties.  We can create hand painted murals or digital designs (to be applied as wallpaper) to complement any decorative scheme.   We love what we do and we want you to enjoy our designs as well! Our business is located in Orlando and our designs can be found throughout the United States.</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1M-5M</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>❌ No people found</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>❌ No decision makers found</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>NO CONTACT</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>both people searches failed. Needs manual sourcing or LinkedIn</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Country Floors</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>https://countryfloors.com</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Decorative / Artisan Tile</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>200M-500M</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>❌ No people found</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>❌ No decision makers found</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>NO CONTACT</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>both people searches failed. Needs manual sourcing or LinkedIn</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Mosaics Lab</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>mosaicslab.com</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Mosaics Lab is a mosaic studio that offers unique, unordinary and fully customizable handmade tiled masterpieces for proud homeowners.
+We’re committed to bringing you high-end mosaics that you’ll be excited to display. So if you find yourself bragging about your new art to strangers in the streets, buses and waiting rooms, then we’ll have done our job right.
+Why Mosaics Lab? We believe in the potential of your space, and we’re here to help transform it into a high-quality work of art.
+We create art for you to walk all over, splash all over, lean all over and look all over. We invest in quality, handcrafted tiles, offer infinite designs through customization, deliver to your doorstep and offer great customer service, so you’ll love every bit of your mosaic.
+Products: marble, glass and stone mosaics, mosaic murals, mosaic floors, mosaic rugs, mosaic borders and tiles, backsplash, countertops and counter cover, water features, pool, and furniture. 
+Follow us on IG/FB: @MosaicsLab</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1M-5M</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>❌ No people found</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>❌ No decision makers found</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>NO CONTACT</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>both people searches failed. Needs manual sourcing or LinkedIn</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Murals Your Way</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>https://muralsyourway.com</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Murals &amp; Wallpaper</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>5M-10M</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>❌ No people found</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>❌ No decision makers found</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>NO CONTACT</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>both people searches failed. Needs manual sourcing or LinkedIn</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>WallpaperMural.com</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>https://wallpapermural.com</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Murals &amp; Wallpaper</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>500K-1M</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>❌ No people found</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>❌ No decision makers found</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>NO CONTACT</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>both people searches failed. Needs manual sourcing or LinkedIn</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L22"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/gtm/mec/MEC_Outreach_Ready.xlsx
+++ b/gtm/mec/MEC_Outreach_Ready.xlsx
@@ -13376,7 +13376,7 @@
       <c r="AZ55" s="4" t="inlineStr"/>
       <c r="BA55" s="5" t="inlineStr"/>
     </row>
-    <row r="56" ht="18" customHeight="1">
+    <row r="56" ht="92" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
           <t>TLC Stained Glass</t>
@@ -13574,22 +13574,57 @@
           <t>found on SMB fallback</t>
         </is>
       </c>
-      <c r="AT56" s="3" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
+      <c r="AT56" s="6" t="inlineStr">
+        <is>
+          <t>HOLD - OFF ICP</t>
         </is>
       </c>
       <c r="AU56" s="4" t="inlineStr">
         <is>
-          <t>Audit verdict DROP — One-person studio. Same two failures as row 47</t>
-        </is>
-      </c>
-      <c r="AV56" s="4" t="inlineStr"/>
-      <c r="AW56" s="5" t="inlineStr"/>
-      <c r="AX56" s="4" t="inlineStr"/>
-      <c r="AY56" s="5" t="inlineStr"/>
-      <c r="AZ56" s="4" t="inlineStr"/>
-      <c r="BA56" s="5" t="inlineStr"/>
+          <t>Copy written on request, but this row failed a S7.4 gate: One-person studio. Same two failures as row 47. Decide deliberately before sending.</t>
+        </is>
+      </c>
+      <c r="AV56" s="4" t="inlineStr">
+        <is>
+          <t>the commission nobody can picture yet</t>
+        </is>
+      </c>
+      <c r="AW56" s="5" t="inlineStr">
+        <is>
+          <t>Theresa,
+TLC makes custom transoms, cabinet doors, privacy windows and hanging panels. All of it made to the client's own style.
+A stained glass commission is one of the hardest things to sell, because the client is agreeing to something they cannot see. Light, colour and scale all change once it is in the opening, and most people cannot hold that in their head. So they order the small panel instead of the transom.
+We built the AI studio that MEC Artworks uses. Someone describes the piece and sees it set into a photo of the actual window.
+Would that be useful before you quote?</t>
+        </is>
+      </c>
+      <c r="AX56" s="4" t="inlineStr">
+        <is>
+          <t>small panel instead of the transom</t>
+        </is>
+      </c>
+      <c r="AY56" s="5" t="inlineStr">
+        <is>
+          <t>Theresa,
+The practical bit. The client types "deep blues, geometric, morning light" and sees it in their own window before you cut anything.
+For a studio your size the value is not speed. It is that you stop spending unpaid hours on people who were never going to commit, and the ones who do commit ask for the bigger piece because they can see it.
+ai.mecartworks.com. Five previews, free, code by email.</t>
+        </is>
+      </c>
+      <c r="AZ56" s="4" t="inlineStr">
+        <is>
+          <t>a one person studio has no spare hours</t>
+        </is>
+      </c>
+      <c r="BA56" s="5" t="inlineStr">
+        <is>
+          <t>Theresa,
+I will not email again after this.
+Running a studio single handed means every hour spent explaining a design to someone is an hour not spent making glass. If you have already found a way around that, I would like to hear it.
+If not, ai.mecartworks.com is the example.
+A 1400 year old craft is a good thing to be keeping alive.</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="92" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
@@ -14556,7 +14591,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="18" customHeight="1">
+    <row r="61" ht="92" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Big Mountain Imaging</t>
@@ -14756,22 +14791,57 @@
           <t>found on main search</t>
         </is>
       </c>
-      <c r="AT61" s="3" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
+      <c r="AT61" s="6" t="inlineStr">
+        <is>
+          <t>HOLD - OFF ICP</t>
         </is>
       </c>
       <c r="AU61" s="4" t="inlineStr">
         <is>
-          <t>Audit verdict DROP — Signage/print shop. Wrong buyer, wrong workflow</t>
-        </is>
-      </c>
-      <c r="AV61" s="4" t="inlineStr"/>
-      <c r="AW61" s="5" t="inlineStr"/>
-      <c r="AX61" s="4" t="inlineStr"/>
-      <c r="AY61" s="5" t="inlineStr"/>
-      <c r="AZ61" s="4" t="inlineStr"/>
-      <c r="BA61" s="5" t="inlineStr"/>
+          <t>Copy written on request, but this row failed a S7.4 gate: Signage/print shop. Wrong buyer, wrong workflow. Decide deliberately before sending.</t>
+        </is>
+      </c>
+      <c r="AV61" s="4" t="inlineStr">
+        <is>
+          <t>signing off a wall you have not seen</t>
+        </is>
+      </c>
+      <c r="AW61" s="5" t="inlineStr">
+        <is>
+          <t>Patrick,
+Big Mountain does grand format work where the client sees the result only once it is installed. Your own testimonial says it: opening a property is hard enough without worrying about the graphics.
+That is the whole risk in large format. A proof on a screen is not the same as a wall, and by the time anyone can judge it properly the print run is already paid for.
+We built the AI studio that MEC Artworks uses. Someone describes the graphic and sees it placed in a photo of the real space, at real scale.
+Would that help before a print run gets committed?</t>
+        </is>
+      </c>
+      <c r="AX61" s="4" t="inlineStr">
+        <is>
+          <t>a proof is not a wall</t>
+        </is>
+      </c>
+      <c r="AY61" s="5" t="inlineStr">
+        <is>
+          <t>Patrick,
+As art director you will know the specific failure I mean. Colour and scale read completely differently at eight feet than they do on a monitor, and the client only finds that out on install day.
+Showing it in the actual space beforehand takes that argument off the table, and it protects the schedule as much as the artwork.
+ai.mecartworks.com, five previews, free, code by email.</t>
+        </is>
+      </c>
+      <c r="AZ61" s="4" t="inlineStr">
+        <is>
+          <t>install day is the wrong time to find out</t>
+        </is>
+      </c>
+      <c r="BA61" s="5" t="inlineStr">
+        <is>
+          <t>Patrick,
+That is my last email on this.
+A shop that has done Hard Rock and a Times Square billboard has clearly solved approvals well enough to keep those clients.
+If showing work at scale before printing is ever useful, ai.mecartworks.com is the example.
+Thanks for reading.</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="92" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -15035,7 +15105,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="18" customHeight="1">
+    <row r="63" ht="92" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Mosaic Studio</t>
@@ -15241,22 +15311,57 @@
           <t>found on main search</t>
         </is>
       </c>
-      <c r="AT63" s="3" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
+      <c r="AT63" s="6" t="inlineStr">
+        <is>
+          <t>HOLD - OFF ICP</t>
         </is>
       </c>
       <c r="AU63" s="4" t="inlineStr">
         <is>
-          <t>Audit verdict DROP — Mosaic Studio UK - DNS dead. Resolves the FLAGGED item in S7.5</t>
-        </is>
-      </c>
-      <c r="AV63" s="4" t="inlineStr"/>
-      <c r="AW63" s="5" t="inlineStr"/>
-      <c r="AX63" s="4" t="inlineStr"/>
-      <c r="AY63" s="5" t="inlineStr"/>
-      <c r="AZ63" s="4" t="inlineStr"/>
-      <c r="BA63" s="5" t="inlineStr"/>
+          <t>Copy written on request, but this row failed a S7.4 gate: Mosaic Studio UK - DNS dead. Resolves the FLAGGED item in S7.5. Decide deliberately before sending.</t>
+        </is>
+      </c>
+      <c r="AV63" s="4" t="inlineStr">
+        <is>
+          <t>what people make before they book</t>
+        </is>
+      </c>
+      <c r="AW63" s="5" t="inlineStr">
+        <is>
+          <t>Ben,
+Mosaic Art Studio has grown from one rented room to six studios and a run of pop ups, teaching Turkish mosaic lamp and ceramic work across the country.
+The thing that stops someone booking is not price. It is that they cannot picture what they will walk out with, and a gallery of other people's finished lamps is somebody else's taste, not theirs.
+We built the AI studio that MEC Artworks uses. Someone describes the colours and pattern they like and sees a version of it before they book.
+Worth a look for the booking page?</t>
+        </is>
+      </c>
+      <c r="AX63" s="4" t="inlineStr">
+        <is>
+          <t>a booking page that shows their own idea</t>
+        </is>
+      </c>
+      <c r="AY63" s="5" t="inlineStr">
+        <is>
+          <t>Ben,
+Where I think this fits your operations rather than your marketing.
+Corporate and private group bookings are the hard ones to close, because the organiser is choosing on behalf of other people and cannot show them anything. Letting them generate a version of what the group would make turns a maybe into a date in the diary.
+ai.mecartworks.com, five previews, free, code by email.</t>
+        </is>
+      </c>
+      <c r="AZ63" s="4" t="inlineStr">
+        <is>
+          <t>six studios and ten pop ups</t>
+        </is>
+      </c>
+      <c r="BA63" s="5" t="inlineStr">
+        <is>
+          <t>Ben,
+I will stop after this one.
+Going from one rented room to six studios in a few years means you already understand what makes people book, better than a cold email will.
+If the booking step ever needs a visual, ai.mecartworks.com is the example.
+Good luck with the next pop up.</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
@@ -19690,14 +19795,14 @@
           <t>http://www.bigmountain.com</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>HOLD - OFF ICP</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>Audit verdict DROP — Signage/print shop. Wrong buyer, wrong workflow</t>
+          <t>Copy written on request, but this row failed a S7.4 gate: Signage/print shop. Wrong buyer, wrong workflow. Decide deliberately before sending.</t>
         </is>
       </c>
     </row>
@@ -19740,14 +19845,14 @@
           <t>http://www.mosaic-studio.co.uk</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>HOLD - OFF ICP</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>Audit verdict DROP — Mosaic Studio UK - DNS dead. Resolves the FLAGGED item in S7.5</t>
+          <t>Copy written on request, but this row failed a S7.4 gate: Mosaic Studio UK - DNS dead. Resolves the FLAGGED item in S7.5. Decide deliberately before sending.</t>
         </is>
       </c>
     </row>
@@ -19792,14 +19897,14 @@
           <t>http://tlcstainedglass.com</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>HOLD - OFF ICP</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Audit verdict DROP — One-person studio. Same two failures as row 47</t>
+          <t>Copy written on request, but this row failed a S7.4 gate: One-person studio. Same two failures as row 47. Decide deliberately before sending.</t>
         </is>
       </c>
     </row>
